--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.1" customWidth="1" min="1" max="1"/>
@@ -1951,83 +1951,369 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TS.Log.009</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>TC.Log.009.001</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Login menggunakan akun Google yang sudah terhubung (linked)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>User login memakai tombol "Masuk dengan Google" dengan akun Google yang sudah terhubung ke akun terdaftar.</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>User punya akun terdaftar dan sudah menghubungkan (link) akun Google-nya sebelumnya.</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman login.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Halaman login tampil dengan tombol "Masuk dengan Google".</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Masuk dengan Google.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>User diarahkan ke halaman otorisasi Google.</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Pilih/otorisasi akun Google yang sudah terhubung.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Google mengembalikan user ke sistem (callback).</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses callback Google.</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>User berhasil login dan diarahkan ke dashboard sesuai perannya.</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TS.Log.010</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>TC.Log.010.001</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Login menggunakan akun Google yang belum terdaftar</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>User login memakai tombol "Masuk dengan Google" dengan akun Google yang belum pernah terhubung/terdaftar di sistem.</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Akun Google yang dipakai tidak cocok dengan id_google atau email manapun di database.</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman login.</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Halaman login tampil.</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Masuk dengan Google.</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>User diarahkan ke halaman otorisasi Google.</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Otorisasi dengan akun Google yang belum terdaftar.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Google mengembalikan user ke sistem (callback).</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses callback Google.</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Akun Google ini belum terdaftar", user diarahkan ke halaman daftar, tidak login.</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="89">
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="F17:F20"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="G25:G28"/>
+    <mergeCell ref="G51:G54"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="C36:C38"/>
     <mergeCell ref="E36:E38"/>
     <mergeCell ref="E43:E46"/>
     <mergeCell ref="G43:G46"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="D51:D54"/>
     <mergeCell ref="G39:G42"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="B21:B24"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="C29:C32"/>
-    <mergeCell ref="D21:D24"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="A25:A28"/>
     <mergeCell ref="E29:E32"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="B36:B38"/>
     <mergeCell ref="E13:E16"/>
     <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C9:C12"/>
     <mergeCell ref="G13:G16"/>
     <mergeCell ref="B17:B20"/>
-    <mergeCell ref="E9:E12"/>
     <mergeCell ref="D17:D20"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B39:B42"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="E9:E12"/>
     <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="F13:F16"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="F51:F54"/>
     <mergeCell ref="C39:C42"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A29:A32"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="G25:G28"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="D43:D46"/>
-    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="D9:D12"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="F9:F12"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D39:D42"/>
     <mergeCell ref="F39:F42"/>
     <mergeCell ref="A43:A46"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="D29:D32"/>
     <mergeCell ref="F29:F32"/>
-    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="E51:E54"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A47:A50"/>
     <mergeCell ref="E21:E24"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="G21:G24"/>
     <mergeCell ref="F33:F35"/>
-    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="B25:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2039,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.1" customWidth="1" min="1" max="1"/>
@@ -5603,8 +5889,280 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>TS.Reg.024</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>TC.Reg.024.001</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Lengkapi pendaftaran siswa menggunakan tombol Daftar dengan Google</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Siswa melengkapi pendaftaran memakai akun Google alih-alih isi email/password manual.</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah lolos verifikasi identitas (step 1).</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman lengkapi pendaftaran.</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Halaman step 2 tampil, ada tombol "Daftar dengan Google".</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Daftar dengan Google.</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>User diarahkan ke halaman otorisasi Google.</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
+      <c r="G112" s="8" t="n"/>
+      <c r="H112" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Otorisasi dengan akun Google.</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Google mengembalikan user ke sistem (callback).</t>
+        </is>
+      </c>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="9" t="n"/>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
+      <c r="H113" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses callback Google.</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Akun berhasil diaktifkan (status registered), email &amp; id Google akun tersimpan, user langsung login dan diarahkan ke dashboard siswa.</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>TS.Reg.025</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>TC.Reg.025.001</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Lengkapi pendaftaran guru menggunakan tombol Daftar dengan Google</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Guru melengkapi pendaftaran memakai akun Google, lalu diminta melengkapi nomor telepon.</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Guru sudah lolos verifikasi identitas (step 1).</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman lengkapi pendaftaran.</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>Halaman step 2 tampil, ada tombol "Daftar dengan Google".</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="n"/>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Daftar dengan Google.</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>User diarahkan ke halaman otorisasi Google.</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n"/>
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="8" t="n"/>
+      <c r="H116" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Otorisasi dengan akun Google.</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>Akun berhasil diaktifkan, sistem meminta nomor telepon (karena peran guru).</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
+      <c r="H117" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Isi nomor telepon yang valid dan submit.</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>Nomor telepon tersimpan di profil guru, user diarahkan ke dashboard wali kelas.</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="187">
+  <mergeCells count="201">
     <mergeCell ref="C98:C101"/>
     <mergeCell ref="D60:D63"/>
     <mergeCell ref="F60:F63"/>
@@ -5630,6 +6188,7 @@
     <mergeCell ref="C56:C59"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F110:F113"/>
     <mergeCell ref="E76:E77"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="G76:G77"/>
@@ -5638,6 +6197,7 @@
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="D78:D81"/>
     <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E110:E113"/>
     <mergeCell ref="A17:A20"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="C60:C63"/>
@@ -5689,13 +6249,16 @@
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="C76:C77"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C114:C117"/>
     <mergeCell ref="B60:B63"/>
+    <mergeCell ref="E114:E117"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="F102:F105"/>
     <mergeCell ref="G64:G67"/>
     <mergeCell ref="C106:C109"/>
     <mergeCell ref="D25:D28"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G114:G117"/>
     <mergeCell ref="C48:C51"/>
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="A4:E4"/>
@@ -5705,12 +6268,15 @@
     <mergeCell ref="D64:D67"/>
     <mergeCell ref="A68:A71"/>
     <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
     <mergeCell ref="E106:E109"/>
+    <mergeCell ref="D110:D113"/>
     <mergeCell ref="G106:G109"/>
     <mergeCell ref="F48:F51"/>
     <mergeCell ref="A52:A55"/>
     <mergeCell ref="B94:B97"/>
     <mergeCell ref="E17:E20"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="G17:G20"/>
     <mergeCell ref="C43:C47"/>
     <mergeCell ref="E35:E38"/>
@@ -5722,6 +6288,7 @@
     <mergeCell ref="D76:D77"/>
     <mergeCell ref="F76:F77"/>
     <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="E60:E63"/>
     <mergeCell ref="E9:E12"/>
@@ -5738,6 +6305,7 @@
     <mergeCell ref="A29:A32"/>
     <mergeCell ref="D68:D71"/>
     <mergeCell ref="C72:C75"/>
+    <mergeCell ref="G110:G113"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="C13:C16"/>
@@ -5753,6 +6321,7 @@
     <mergeCell ref="D94:D97"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A114:A117"/>
     <mergeCell ref="F78:F81"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="E33:E34"/>
@@ -5781,9 +6350,12 @@
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="F56:F59"/>
     <mergeCell ref="G29:G32"/>
+    <mergeCell ref="C110:C113"/>
     <mergeCell ref="F106:F109"/>
     <mergeCell ref="B76:B77"/>
     <mergeCell ref="G35:G38"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D114:D117"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="B43:B47"/>
     <mergeCell ref="D35:D38"/>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lokasi Absen" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WhatsApp API" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profil Admin" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Siswa" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Guru" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2326,6 +2328,1862 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Impor Data Siswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Admin &gt; Data Siswa &gt; Impor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah file xlsx valid lalu mengimpor siswa baru</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah template xlsx berisi baris siswa yang lengkap dan valid, lalu menjalankan impor.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Admin sudah login.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa, unggah file xlsx sesuai template.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>File diterima, diarahkan ke halaman pratinjau berisi baris yang akan diimpor.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Impor pada halaman pratinjau.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa baru tersimpan sesuai data pada file, diarahkan ke daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.002</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah file dengan format bukan xlsx/xls</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah file PDF sebagai file impor siswa.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pilih file berformat PDF pada form unggah impor siswa.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>File dipilih.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Unggah.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi format file harus xlsx/xls, file tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.003</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Admin submit unggah impor siswa tanpa memilih file</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Admin klik Unggah tanpa memilih file sama sekali.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Unggah tanpa memilih file.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Field file kosong.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi file wajib diisi, tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.004</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan nama kosong dilewati saat impor siswa</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan kolom Nama kosong.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>File sudah diunggah dan masuk tahap pratinjau.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris bernama kosong.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Baris tersebut dilewati dan dicatat sebagai error "Nama kosong", tidak ada siswa yang tersimpan dari baris ini.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.005</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan NISN kosong dilewati saat impor siswa</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan kolom NISN kosong.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>File sudah diunggah dan masuk tahap pratinjau.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris ber-NISN kosong.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Baris tersebut dilewati dan dicatat sebagai error "NISN kosong", tidak ada siswa yang tersimpan dari baris ini.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.006</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan NIS kosong dilewati saat impor siswa</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan kolom NIS kosong.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>File sudah diunggah dan masuk tahap pratinjau.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris ber-NIS kosong.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Baris tersebut dilewati dan dicatat sebagai error "NIS kosong", tidak ada siswa yang tersimpan dari baris ini.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.007</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan NISN yang sudah ada dianggap data lama, bukan duplikat baru</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan NISN yang sudah dipakai siswa yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Sudah ada siswa dengan NISN tersebut di database.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris ber-NISN yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Sistem mendeteksi NISN sudah terdaftar.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Data profil siswa yang sudah ada diperbarui (NIS/kelas), tidak membuat akun siswa baru/duplikat.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.008</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Impor siswa otomatis membuat kelas yang belum ada</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan nama kelas yang belum terdaftar di sistem.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Kelas pada baris tersebut belum ada di database.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris berisi nama kelas baru.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Kelas baru otomatis tercipta dan siswa terhubung ke kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportSiswa.009</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportSiswa.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Akses halaman pratinjau impor siswa tanpa mengunggah file terlebih dahulu</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengakses langsung halaman pratinjau tanpa proses unggah file.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Belum ada file yang diunggah pada sesi berjalan.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Akses langsung halaman pratinjau impor siswa.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Sistem mendeteksi tidak ada file pada sesi.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>User diarahkan kembali ke halaman impor siswa.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="68">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Impor Data Guru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Admin &gt; Data Guru &gt; Impor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah file xlsx valid lalu mengimpor guru baru</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah template xlsx format baru (kolom Tipe) berisi baris guru yang lengkap dan valid, lalu menjalankan impor.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Admin sudah login.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru, unggah file xlsx sesuai template.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>File diterima, diarahkan ke halaman pratinjau berisi baris yang akan diimpor.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Impor pada halaman pratinjau.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Guru baru tersimpan dengan peran sesuai kolom Tipe (Wali Kelas/BK/Kesiswaan), diarahkan ke daftar guru.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.002</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah file dengan format bukan xlsx/xls</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengunggah file PDF sebagai file impor guru.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pilih file berformat PDF pada form unggah impor guru.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>File dipilih.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Unggah.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi format file harus xlsx/xls, file tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.003</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Admin submit unggah impor guru tanpa memilih file</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Admin klik Unggah tanpa memilih file sama sekali.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Unggah tanpa memilih file.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Field file kosong.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi file wajib diisi, tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.004</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan nama kosong dilewati saat impor guru</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan kolom Nama kosong.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>File sudah diunggah dan masuk tahap pratinjau.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris bernama kosong.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Baris tersebut dilewati dan dicatat sebagai error "Nama kosong", tidak ada guru yang tersimpan dari baris ini.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.005</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan NIP kosong dilewati saat impor guru</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan kolom NIP kosong.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>File sudah diunggah dan masuk tahap pratinjau.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris ber-NIP kosong.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Baris tersebut dilewati dan dicatat sebagai error "NIP kosong, guru harus didaftarkan manual oleh admin", tidak ada guru yang tersimpan dari baris ini.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.006</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Baris dengan NIP yang sudah ada dianggap data lama, bukan duplikat baru</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris dengan NIP yang sudah dipakai guru yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Sudah ada guru dengan NIP tersebut di database.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris ber-NIP yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Sistem mendeteksi NIP sudah terdaftar.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Guru dianggap sudah ada (existing), tidak membuat akun guru baru/duplikat.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.007</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Baris wali kelas otomatis menjadikan guru sebagai wali kelas terkait</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>File impor berisi baris guru bertipe Wali Kelas dengan nama kelas.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor dengan baris bertipe Wali Kelas dan nama kelas.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses baris demi baris, kelas dibuat bila belum ada.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyelesaikan proses impor.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Guru tersimpan dan otomatis diset sebagai wali_kelas_id pada kelas terkait.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.008</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Format kolom lama (Walas) tetap dikenali sistem</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>File impor menggunakan format lama dengan kolom "Walas" alih-alih "Nama"/"Tipe".</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>File memakai heading kolom format lama (Walas, NIP, Kelas).</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Unggah file dengan format kolom lama.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Sistem mendeteksi format lama secara otomatis.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Jalankan impor.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Guru tersimpan dengan peran wali_kelas, tetap kompatibel dengan format lama.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.ImportGuru.009</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.ImportGuru.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Akses halaman pratinjau impor guru tanpa mengunggah file terlebih dahulu</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Admin mengakses langsung halaman pratinjau tanpa proses unggah file.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Belum ada file yang diunggah pada sesi berjalan.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Akses langsung halaman pratinjau impor guru.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Sistem mendeteksi tidak ada file pada sesi.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>User diarahkan kembali ke halaman impor guru.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="68">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -18,6 +18,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profil Admin" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Siswa" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Guru" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitor Absensi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Wali" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poin Pelanggaran Wali" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pengajuan Poin Wali" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4184,6 +4188,3928 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Memonitor Absensi Kelas Perwalian</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Wali Kelas &gt; Kelas Saya</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, State Transition Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas melihat status absensi dan daftar siswa kelas sendiri hari ini</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka halaman Kelas Saya, sistem menampilkan ringkasan status absensi hari ini dan daftar siswa.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Halaman tampil dengan ringkasan status absensi dan daftar siswa hari ini.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas tanpa kelas perwalian tetap melihat halaman kosong</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Guru berperan wali kelas tapi belum ditugaskan ke kelas manapun membuka halaman Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Guru belum punya kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Halaman tampil kosong (bukan error), tidak ada data siswa.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengisi status absensi siswa yang belum ada record hari ini</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengisi status absensi manual untuk siswa yang belum tercatat hari ini.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Belum ada record absensi untuk siswa tsb hari ini.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pilih status absensi (misal Hadir) untuk siswa.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Simpan.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Record absensi baru berhasil dibuat dengan status yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.004</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.004.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengubah status absensi siswa yang recordnya sudah ada hari ini</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengubah status absensi siswa yang sudah tercatat hari ini ke status lain.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Sudah ada record absensi untuk siswa tsb hari ini.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Ubah status absensi siswa yang sudah tercatat ke status lain.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Simpan.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Record yang sudah ada ter-update (bukan bikin record baru/duplikat).</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.005</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.005.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas tidak bisa mengubah absensi siswa dari kelas lain</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba mengubah status absensi siswa yang bukan dari kelas perwaliannya.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa target berada di kelas yang berbeda.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Kirim permintaan ubah status absensi untuk siswa kelas lain.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memvalidasi kepemilikan kelas.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403), status absensi tidak berubah.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.006</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.006.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas tidak bisa mengubah absensi pada hari akhir pekan</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba mengubah status absensi pada hari Sabtu/Minggu.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal saat ini jatuh pada akhir pekan.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Kirim permintaan ubah status absensi saat akhir pekan.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memvalidasi hari.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absensi hanya tersedia pada hari Senin sampai Jumat", status tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.007</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.007.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Status absensi yang bukan salah satu dari 5 pilihan ditolak</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengirim nilai status yang tidak termasuk hadir/terlambat/izin/sakit/alpha.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Kirim status absensi dengan nilai tidak valid.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Simpan.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi status tidak valid, tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.008</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.008.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas melihat detail siswa kelas sendiri</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka detail salah satu siswa di kelas perwaliannya.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Klik salah satu siswa di daftar Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Halaman detail siswa tampil lengkap (biodata, pelanggaran disetujui, riwayat absensi).</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.009</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.009.001</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas tidak bisa melihat detail siswa kelas lain</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba membuka detail siswa yang bukan dari kelas perwaliannya.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Siswa target berada di kelas yang berbeda.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Akses langsung halaman detail siswa kelas lain.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memvalidasi kepemilikan kelas.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403).</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.010</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.010.001</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint status absensi (polling) mengembalikan data yang benar</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memanggil endpoint status-absensi untuk polling data terbaru.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Ada siswa dengan status absensi tercatat hari ini.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Panggil endpoint status-absensi.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Sistem mengembalikan JSON berisi ringkasan statistik dan daftar status per siswa yang sesuai data terbaru.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.011</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.011.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Transisi state Kosong ke Ada setelah update absensi valid</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Dari kondisi belum ada record absensi hari ini (Kosong), wali kelas mengisi status valid.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Belum ada record absensi untuk siswa hari ini (state Kosong).</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Pastikan belum ada record absensi siswa hari ini.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>State Kosong.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Isi dan simpan status absensi valid.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>State berpindah menjadi Ada, record baru tercipta.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.012</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.012.001</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>State tetap Ada dan status ter-replace saat diupdate ulang</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Dari kondisi sudah Ada dengan status A, wali kelas mengubah ke status B.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>State sudah Ada dengan status tertentu.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Pastikan record absensi siswa hari ini sudah Ada.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>State Ada.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Ubah status ke nilai lain dan simpan.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>State tetap Ada, tapi status ter-replace (bukan record baru).</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.013</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.013.001</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>State tetap Ada saat percobaan update di akhir pekan diblokir</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Dari kondisi Ada, wali kelas mencoba update saat akhir pekan.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>State sudah Ada; hari ini akhir pekan.</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Pastikan record absensi siswa hari ini sudah Ada.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>State Ada.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Coba ubah status saat akhir pekan.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>State tetap Ada tidak berubah, permintaan diblokir (no-op aman).</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitorAbsensi.014</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitorAbsensi.014.001</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>State tetap Kosong saat percobaan update di akhir pekan diblokir</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Dari kondisi Kosong, wali kelas mencoba update saat akhir pekan.</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>State masih Kosong; hari ini akhir pekan.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Pastikan belum ada record absensi siswa hari ini.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>State Kosong.</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Coba isi status saat akhir pekan.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>State tetap Kosong, permintaan diblokir (no-op aman).</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="75">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Merekap Laporan Absensi Kelas Perwalian</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Wali Kelas &gt; Rekap Absensi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas melihat rekap absensi dengan rentang tanggal default</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka halaman rekap absensi tanpa filter, sistem pakai rentang default (awal bulan sampai hari ini).</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Rekap Absensi tanpa mengisi filter.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Rekap tampil dengan rentang tanggal awal bulan berjalan sampai hari ini.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Filter bulan meng-override rentang mulai/selesai</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengisi filter bulan sekaligus mulai/selesai, filter bulan yang dipakai.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Isi filter bulan dan filter mulai/selesai yang berbeda bulan.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Rekap mengikuti rentang bulan, bukan mulai/selesai.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.003</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.003.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Filter berdasarkan siswa tertentu</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas memfilter rekap ke satu siswa spesifik.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Pilih satu siswa pada filter.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Rekap hanya menampilkan siswa yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.004</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.004.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Filter berdasarkan status absensi</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas memfilter rekap berdasarkan status tertentu (misal alpha).</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Pilih filter status alpha.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Rekap hanya menampilkan siswa dengan status tsb dalam rentang yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.005</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.005.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Ekspor Excel ditolak untuk wali kelas tanpa kelas perwalian</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Guru berperan wali kelas tanpa kelas perwalian mencoba ekspor Excel.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Guru belum punya kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Akses langsung endpoint ekspor Excel.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memvalidasi kepemilikan kelas.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403).</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.006</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.006.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Ekspor PDF ditolak untuk wali kelas tanpa kelas perwalian</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Guru berperan wali kelas tanpa kelas perwalian mencoba ekspor PDF.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Guru belum punya kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Akses langsung endpoint ekspor PDF.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memvalidasi kepemilikan kelas.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403).</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.007</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.007.001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal selesai sebelum mulai ditolak</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengisi tanggal selesai yang lebih awal dari tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai lebih akhir dari tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal selesai harus setelah/sama dengan mulai, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.008</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.008.001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Format tanggal yang salah ditolak</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengisi tanggal dengan format selain YYYY-MM-DD.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai dengan format salah, misal DD-MM-YYYY.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi format tanggal tidak valid, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.009</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.009.001</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Filter siswa dengan identitas yang tidak ada ditolak</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengirim filter siswa dengan NISN yang tidak terdaftar.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Kirim filter siswa dengan NISN yang tidak ada di database.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi siswa tidak valid, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.010</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.010.001</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Ekspor Excel berhasil</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengekspor rekap absensi ke Excel untuk rentang yang dipilih.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Ekspor Excel.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>File Excel rekap berhasil diunduh.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.011</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.011.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Ekspor PDF berhasil</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengekspor rekap absensi ke PDF untuk rentang yang dipilih.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Ekspor PDF.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>File PDF rekap berhasil diunduh.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.012</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.012.001</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Batas tanggal selesai sama dengan mulai (boundary tepat sama)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal selesai diisi tepat sama dengan tanggal mulai — tepat di batas yang diperbolehkan.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai dan selesai dengan nilai yang sama.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal lolos validasi (batas atas diperbolehkan), rekap tampil.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>TS.RekapAbsensi.013</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>TC.RekapAbsensi.013.001</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Batas tanggal selesai satu hari sebelum mulai (boundary di bawah batas)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal selesai diisi tepat 1 hari sebelum tanggal mulai — tepat di bawah batas yang diperbolehkan.</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal selesai 1 hari sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal selesai tidak valid, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="61">
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Memantau Poin Pelanggaran Kelas Perwalian</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Wali Kelas &gt; Poin Pelanggaran</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas melihat pelanggaran yang disetujui untuk kelas sendiri</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka halaman Poin Pelanggaran kelasnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran siswa berstatus disetujui di kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Daftar pelanggaran siswa yang sudah disetujui tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas tanpa kelas perwalian tetap melihat halaman kosong</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Guru berperan wali kelas tanpa kelas perwalian membuka halaman Poin Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Guru belum punya kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Halaman tampil kosong (bukan error).</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Filter berdasarkan siswa tertentu</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas memfilter daftar pelanggaran ke satu siswa spesifik.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pilih satu siswa pada filter.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran siswa yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Filter berdasarkan kategori pelanggaran</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas memfilter daftar pelanggaran berdasarkan kategori.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Pilih filter kategori (misal ringan).</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran kategori tsb.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Filter berdasarkan rentang tanggal pelanggaran</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas memfilter daftar pelanggaran berdasarkan rentang tanggal.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Isi filter dari tanggal dan sampai tanggal.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran dalam rentang tsb.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Pelanggaran berstatus menunggu/ditolak tidak ikut ditampilkan</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran berstatus menunggu ACC dan ditolak untuk siswa yang sama, keduanya tidak boleh muncul.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran berstatus disetujui, menunggu ACC, dan ditolak untuk kelas yang sama.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Cuma pelanggaran berstatus disetujui yang muncul; yang menunggu ACC dan ditolak tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Pelanggaran kelas lain tidak ikut ditampilkan</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran disetujui milik siswa dari kelas lain, tidak boleh ikut tampil di kelas sendiri.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran disetujui di kelas lain.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran kelas sendiri yang tampil, pelanggaran kelas lain tidak ikut muncul.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.PoinPelanggaran.008</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.PoinPelanggaran.008.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Daftar pelanggaran dipaginasi 25 per halaman</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Ada lebih dari 25 data pelanggaran disetujui di kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Ada 26 data pelanggaran disetujui di kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Halaman pertama menampilkan tepat 25 data, total keseluruhan tetap 26 (bisa lanjut ke halaman berikutnya).</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Mengajukan Penambahan Poin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Wali Kelas &gt; Pengajuan Poin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengajukan penambahan poin untuk siswa kelas sendiri</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengajukan penambahan poin dengan alasan untuk siswa di kelas perwaliannya.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa terdaftar di kelas perwalian wali kelas.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka form Ajukan Penambahan Poin, pilih siswa dan isi alasan.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Pengajuan tersimpan berstatus menunggu ACC, jumlah poin masih kosong (diisi kesiswaan nanti), saldo poin siswa belum berubah.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.002</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas tidak bisa mengajukan untuk siswa kelas lain</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba mengajukan penambahan poin untuk siswa yang bukan dari kelas perwaliannya.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa target berada di kelas yang berbeda.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan untuk siswa kelas lain.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memvalidasi kepemilikan kelas.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403), pengajuan tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.003</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Alasan pengajuan kosong ditolak</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengirim pengajuan tanpa mengisi alasan.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Biarkan field alasan kosong.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Field alasan kosong.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi alasan wajib diisi, pengajuan tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.004</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Identitas siswa yang tidak ada ditolak</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengirim NISN siswa yang tidak terdaftar di database.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Isi NISN yang tidak ada di database.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi siswa tidak valid, pengajuan tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.005</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Identitas siswa kosong ditolak</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas mengirim pengajuan tanpa memilih siswa.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Biarkan field siswa kosong.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Field kosong.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi siswa wajib dipilih, pengajuan tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.006</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Daftar pengajuan hanya menampilkan milik wali kelas sendiri</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Ada pengajuan milik wali kelas lain, tidak boleh ikut tampil di daftar wali kelas ini.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Ada pengajuan poin dari wali kelas lain.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman daftar pengajuan poin.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Hanya pengajuan yang diajukan sendiri yang tampil.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.007</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.007.001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Daftar pengajuan bisa difilter berdasarkan status</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Wali kelas memfilter daftar pengajuan berdasarkan status menunggu ACC.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Ada pengajuan dengan status berbeda-beda.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Pilih filter status Menunggu ACC.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pengajuan berstatus tsb.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.008</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.008.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Form pengajuan tanpa kelas perwalian menampilkan daftar siswa kosong</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Guru berperan wali kelas tanpa kelas perwalian membuka form Ajukan Penambahan Poin.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Guru belum punya kelas perwalian.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Buka form Ajukan Penambahan Poin.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Daftar pilihan siswa kosong (bukan error).</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.009</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.009.001</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Percobaan mengirim jumlah poin langsung diabaikan sistem</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Form pengajuan memang tidak punya field jumlah poin; percobaan mengirimnya lewat bypass tetap diabaikan.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan dengan field jumlah poin tambahan secara manual.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Request diproses.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyimpan pengajuan.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Pengajuan tersimpan berstatus menunggu ACC, jumlah poin tetap kosong — nilai kiriman diabaikan sepenuhnya (kesiswaan yang menentukan nanti, bukan wali kelas).</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.010</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.010.001</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Batas panjang maksimum alasan (boundary di atas 1000 karakter)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Alasan diisi 1001 karakter — tepat di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Isi alasan dengan 1001 karakter.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi alasan maksimal 1000 karakter, pengajuan tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>TS.PengajuanPoinWali.011</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>TC.PengajuanPoinWali.011.001</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Batas panjang maksimum alasan (boundary tepat 1000 karakter)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Alasan diisi tepat 1000 karakter — tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Isi alasan dengan tepat 1000 karakter.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Kirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Alasan lolos validasi maksimum, pengajuan berhasil tersimpan.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="61">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -22,6 +22,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Wali" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poin Pelanggaran Wali" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pengajuan Poin Wali" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jenis Pelanggaran" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Siswa" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pelanggaran Siswa Kesiswaan" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tata Tertib Kesiswaan" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan Pelanggaran" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8110,6 +8115,4749 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Mengelola Data Poin Pelanggaran</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Jenis Pelanggaran</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menambahkan jenis pelanggaran baru dengan data valid</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi form tambah jenis pelanggaran dengan nama, kategori, dan poin yang valid.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan sudah login.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Form tampil dengan field nama, kategori, poin, keterangan, status aktif.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Ringan, isi poin 10.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Semua field menerima input.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran berhasil tersimpan, diarahkan ke daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.002</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.002.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menambahkan jenis pelanggaran dengan nama yang sudah dipakai</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi nama jenis pelanggaran yang sudah ada di database.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Sudah ada jenis pelanggaran lain dengan nama tersebut.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Form tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Isi nama yang sudah dipakai jenis pelanggaran lain.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Field nama menerima input.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi nama sudah digunakan, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.003</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.003.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menambahkan jenis pelanggaran dengan kategori tidak valid</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengirim kategori di luar 4 pilihan yang tersedia (light/medium/heavy/severe).</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Kirim data tambah jenis pelanggaran dengan kategori = "extreme".</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Field kategori menerima input.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi kategori tidak valid, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.004</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.004.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menambahkan jenis pelanggaran dengan poin di luar rentang kategori</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi poin 60 untuk kategori Ringan yang seharusnya bernilai 5-25.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Form tampil.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Pilih kategori Ringan, isi poin 60.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi poin harus berada di antara 5 sampai 25, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.005</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.005.001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memperbarui jenis pelanggaran</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengubah nama dan poin jenis pelanggaran yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Data jenis pelanggaran sudah ada.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Edit Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Form edit tampil terisi data lama.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Ubah nama dan poin.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input baru.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Perbarui.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran berhasil diperbarui.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.006</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.006.001</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memperbarui nama jenis pelanggaran menjadi nama milik jenis lain</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengubah nama jenis pelanggaran menjadi nama yang sudah dipakai jenis pelanggaran lain.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Ada 2 jenis pelanggaran berbeda di database.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Edit Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Form edit tampil.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Ubah nama menjadi nama milik jenis pelanggaran lain.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Field nama menerima input.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Perbarui.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi nama sudah digunakan, data tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.007</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.007.001</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menonaktifkan jenis pelanggaran lewat update, bukan menghapus</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengubah status aktif menjadi nonaktif tanpa menghapus data.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran berstatus aktif.</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Edit Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Form edit tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Matikan toggle status aktif.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Field status menerima input nonaktif.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Perbarui.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Status berubah menjadi nonaktif, data tetap ada di database (tidak terhapus).</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.008</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.008.001</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus jenis pelanggaran yang belum pernah dipakai</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus jenis pelanggaran yang belum pernah dicatat di data pelanggaran siswa manapun.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran belum pernah dipakai.</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Muncul konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran berhasil terhapus dari database.</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.009</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.009.001</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus jenis pelanggaran yang sudah dipakai pada catatan pelanggaran siswa</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencoba menghapus jenis pelanggaran yang sudah pernah dicatat pada pelanggaran siswa.</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran sudah dipakai minimal satu catatan pelanggaran siswa.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris jenis pelanggaran yang sudah dipakai.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Muncul konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan error jenis pelanggaran sudah dipakai dan disarankan dinonaktifkan, data tidak terhapus.</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.010</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.010.001</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar jenis pelanggaran berdasarkan kategori</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar jenis pelanggaran dengan kategori Ringan.</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Ada jenis pelanggaran dengan kategori berbeda-beda.</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Daftar Jenis Pelanggaran, pilih filter kategori Ringan.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan jenis pelanggaran kategori ringan.</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.011</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.011.001</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar jenis pelanggaran berdasarkan status aktif/nonaktif</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar jenis pelanggaran dengan status nonaktif.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Ada jenis pelanggaran aktif dan nonaktif.</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Daftar Jenis Pelanggaran, pilih filter status Nonaktif.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan jenis pelanggaran yang berstatus nonaktif.</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.012</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.012.001</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah poin kategori Ringan (boundary di bawah 5)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Poin diisi 4 untuk kategori Ringan — tepat di bawah batas bawah 5.</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Isi poin 4 untuk kategori Ringan.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Field poin menerima input.</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi poin harus 5-25, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.013</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.013.001</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah poin kategori Ringan (boundary tepat 5)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Poin diisi tepat 5 untuk kategori Ringan — tepat di batas bawah.</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Isi poin tepat 5 untuk kategori Ringan.</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Field poin menerima input.</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Poin lolos validasi minimum, jenis pelanggaran tersimpan.</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.014</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.014.001</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas poin kategori Ringan (boundary tepat 25)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Poin diisi tepat 25 untuk kategori Ringan — tepat di batas atas.</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Isi poin tepat 25 untuk kategori Ringan.</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Field poin menerima input.</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Poin lolos validasi maksimum, jenis pelanggaran tersimpan.</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.015</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.015.001</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas poin kategori Ringan (boundary di atas 25)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Poin diisi 26 untuk kategori Ringan — tepat di atas batas atas 25.</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Isi poin 26 untuk kategori Ringan.</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Field poin menerima input.</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi poin harus 5-25, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.016</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.016.001</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Batas panjang maksimum nama jenis pelanggaran (boundary tepat 255 karakter)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Nama diisi tepat 255 karakter — tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Isi nama jenis pelanggaran tepat 255 karakter.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Field nama menerima input.</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Nama lolos validasi maksimum, jenis pelanggaran tersimpan.</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TS.JenisPelanggaran.017</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>TC.JenisPelanggaran.017.001</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Batas panjang maksimum nama jenis pelanggaran (boundary di atas 255 karakter)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Nama diisi 256 karakter — tepat di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Isi nama jenis pelanggaran 256 karakter.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Field nama menerima input.</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi nama melebihi batas maksimum, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="110">
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="D35:D36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Monitoring Poin Pelanggaran Seluruh Siswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Monitoring Siswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitoringSiswa.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitoringSiswa.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan melihat daftar monitoring siswa dari seluruh sekolah tanpa batas kelas/tingkat</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka halaman monitoring dan melihat siswa dari semua tingkat kelas.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Ada siswa terdaftar di kelas tingkat 10 dan tingkat 12.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Daftar siswa dari seluruh tingkat kelas tampil sekaligus, tidak dibatasi tingkat/kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitoringSiswa.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitoringSiswa.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar monitoring berdasarkan nama siswa</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencari siswa berdasarkan kata kunci nama.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Ada beberapa siswa dengan nama berbeda.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring Siswa, isi kata kunci pencarian nama.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan siswa yang namanya cocok dengan kata kunci.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitoringSiswa.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitoringSiswa.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar monitoring berdasarkan kelas</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar monitoring dengan memilih satu kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Ada siswa dari lebih dari satu kelas.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring Siswa, pilih filter kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan siswa dari kelas yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitoringSiswa.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitoringSiswa.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan melihat detail monitoring siswa berisi agregat poin dan absensi</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka detail seorang siswa untuk melihat ringkasan poin dan riwayat absensi.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Data siswa sudah ada.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Klik nama siswa pada daftar monitoring.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Halaman detail siswa tampil berisi biodata, agregat poin pelanggaran/pengajuan poin, dan 30 riwayat absensi terakhir.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.MonitoringSiswa.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.MonitoringSiswa.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Halaman detail monitoring menyediakan tautan untuk mencatat pelanggaran baru</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan melihat tombol/tautan catat pelanggaran baru pada halaman detail siswa.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Data siswa sudah ada.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman detail monitoring siswa.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Tersedia tautan menuju form catat pelanggaran baru untuk siswa yang sedang dilihat.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Monitoring Poin Pelanggaran Seluruh Siswa (Catat Pelanggaran)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Pelanggaran Siswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran siswa manapun tanpa batas kelas, langsung berstatus disetujui</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran baru untuk siswa dari kelas manapun.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Data siswa dan jenis pelanggaran aktif sudah ada.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Catat Pelanggaran, pilih siswa dari kelas manapun.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Form menerima input siswa tanpa batasan kelas kesiswaan sendiri.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Pilih jenis pelanggaran aktif dan isi tanggal.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersimpan dengan status langsung disetujui (approved), tanpa alur pengajuan.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.002</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.002.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran menggunakan jenis pelanggaran yang nonaktif</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memilih jenis pelanggaran yang statusnya sudah nonaktif.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Ada jenis pelanggaran berstatus nonaktif.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Kirim data catat pelanggaran dengan jenis pelanggaran nonaktif.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi jenis pelanggaran tidak aktif dan tidak dapat dipilih, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.003</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.003.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran dengan jenis pelanggaran yang tidak ada</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengirim jenis_pelanggaran_id yang tidak ada di database.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Kirim data catat pelanggaran dengan jenis_pelanggaran_id tidak valid.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi jenis pelanggaran tidak valid, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.004</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.004.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran untuk siswa (NISN) yang tidak ada</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengirim profil_siswa_id (NISN) yang tidak ada di database.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Kirim data catat pelanggaran dengan NISN tidak terdaftar.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi siswa tidak valid, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.005</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.005.001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran dengan tanggal pelanggaran di masa depan</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi tanggal pelanggaran setelah hari ini.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Form tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal pelanggaran besok (setelah hari ini).</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Field tanggal menerima input.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal tidak boleh melebihi hari ini, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.006</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.006.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memperbarui catatan pelanggaran siswa</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengubah catatan pada pelanggaran siswa yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Data pelanggaran siswa sudah ada.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Edit Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Form edit tampil terisi data lama.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Ubah catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input baru.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Perbarui.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Catatan pelanggaran berhasil diperbarui.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.007</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.007.001</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mempertahankan jenis pelanggaran nonaktif yang sedang dipakai saat update</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memperbarui catatan pelanggaran tanpa mengganti jenis pelanggaran yang kini sudah nonaktif.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran yang sedang dipakai pada catatan ini baru saja dinonaktifkan.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Edit Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Form edit tampil, jenis pelanggaran nonaktif yang sedang dipakai tetap muncul sebagai pilihan.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Simpan tanpa mengganti jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Field jenis pelanggaran tetap menunjuk ke jenis yang sama.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Perbarui.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Update berhasil meski jenis pelanggaran berstatus nonaktif, karena itu adalah jenis yang sedang dipakai catatan ini.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.008</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.008.001</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus catatan pelanggaran siswa</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus satu catatan pelanggaran siswa.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Data pelanggaran siswa sudah ada.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Muncul konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Catatan pelanggaran berhasil terhapus dari database.</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.009</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.009.001</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter daftar catatan pelanggaran berdasarkan kelas, kategori, jenis, tanggal, dan status</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menerapkan filter kelas, kategori, jenis pelanggaran, tanggal, dan status pada daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Ada catatan pelanggaran dari kelas dan kategori yang berbeda-beda.</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Daftar Pelanggaran Siswa, terapkan filter kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan catatan dari kelas yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Ganti filter ke kategori tertentu.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan catatan dengan kategori yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Ganti filter ke jenis pelanggaran, tanggal, dan status tertentu satu per satu.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Daftar ter-filter sesuai masing-masing kriteria yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.010</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.010.001</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas tanggal pelanggaran (boundary tepat hari ini)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal pelanggaran diisi tepat hari ini — tepat di batas atas yang diperbolehkan.</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal pelanggaran dengan tanggal hari ini.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Field tanggal menerima input.</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal lolos validasi batas atas, pelanggaran tersimpan.</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>TS.PelanggaranSiswaKesiswaan.011</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>TC.PelanggaranSiswaKesiswaan.011.001</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas tanggal pelanggaran (boundary 1 hari setelah hari ini)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal pelanggaran diisi besok — tepat 1 hari di atas batas atas.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal pelanggaran dengan tanggal besok.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Field tanggal menerima input.</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal tidak boleh melebihi hari ini, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="82">
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B9:B11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Mengunggah Berkas Tata Tertib Sekolah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Tata Tertib</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis, State Transition Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas PDF tata tertib baru</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi judul dan mengunggah berkas PDF tata tertib.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan sudah login.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Form unggah tata tertib tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Isi judul dan pilih berkas PDF.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Berkas tata tertib berhasil tersimpan dan tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.002</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.002.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah tata tertib tanpa mengisi judul</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas PDF tanpa mengisi judul.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib, biarkan judul kosong.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Field judul kosong.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Pilih berkas PDF dan klik Upload.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi judul wajib diisi, berkas tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.003</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.003.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas yang bukan PDF</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memilih berkas berformat selain PDF (misal .docx).</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib, isi judul.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Field judul menerima input.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Pilih berkas berformat .docx dan klik Upload.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi berkas harus PDF, berkas tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.004</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.004.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah tata tertib tanpa memilih berkas</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengirim form tanpa memilih berkas PDF sama sekali.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib, isi judul, jangan pilih berkas.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Field berkas kosong.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi berkas PDF wajib diunggah, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.005</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.005.001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus tata tertib beserta berkasnya di storage</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus satu tata tertib dari daftar.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Tata tertib dengan berkas PDF sudah ada.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris tata tertib.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Muncul konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Konfirmasi hapus.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Data tata tertib terhapus dari database beserta berkas PDF-nya di storage.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.006</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.006.001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan melihat daftar tata tertib yang sudah diunggah</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka halaman daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Ada tata tertib yang sudah diunggah sebelumnya.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Daftar tata tertib yang pernah diunggah tampil lengkap dengan status draft/aktif.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.007</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Batas panjang maksimum judul tata tertib (boundary tepat 200 karakter)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Judul diisi tepat 200 karakter — tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Isi judul tepat 200 karakter, pilih berkas PDF.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Judul lolos validasi maksimum, tata tertib tersimpan.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.008</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Batas panjang maksimum judul tata tertib (boundary di atas 200 karakter)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Judul diisi 201 karakter — tepat di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Isi judul 201 karakter, pilih berkas PDF.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi judul melebihi batas maksimum, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.009</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Batas ukuran maksimum berkas PDF (boundary tepat 10240 KB)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Berkas PDF berukuran tepat 10240 KB (10 MB) — tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran tepat 10240 KB.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Ukuran berkas lolos validasi maksimum, tata tertib tersimpan.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.010</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.010.001</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Batas ukuran maksimum berkas PDF (boundary di atas 10240 KB)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Berkas PDF berukuran 10241 KB — tepat di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran 10241 KB.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi ukuran PDF melebihi 10 MB, data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.011</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.011.001</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Mengunggah tata tertib baru sebagai aktif otomatis menonaktifkan tata tertib yang sebelumnya aktif</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah tata tertib baru dengan opsi publikasikan dicentang, sementara ada tata tertib lain yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Ada satu tata tertib berstatus aktif (published).</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib, isi judul dan berkas baru, centang Publikasikan.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Tata tertib baru langsung berstatus aktif, tata tertib lama yang sebelumnya aktif otomatis berubah menjadi draft.</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.012</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.012.001</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Mempublikasikan tata tertib berstatus draft membuatnya aktif dan menonaktifkan yang lain</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menekan tombol Publikasikan pada tata tertib berstatus draft, sementara ada tata tertib lain yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Ada satu tata tertib aktif dan satu tata tertib draft.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Publikasikan pada tata tertib berstatus draft.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses perubahan status.</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyimpan perubahan.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Tata tertib yang dipilih berubah menjadi aktif, tata tertib yang sebelumnya aktif otomatis berubah menjadi draft.</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.013</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.013.001</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Menonaktifkan tata tertib yang aktif mengembalikannya menjadi draft</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan menekan tombol Nonaktifkan pada tata tertib yang sedang berstatus aktif.</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Tata tertib berstatus aktif (published).</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Nonaktifkan pada tata tertib yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses perubahan status.</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Sistem menyimpan perubahan.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Status tata tertib berubah kembali menjadi draft.</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TS.TataTertibKesiswaan.014</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>TC.TataTertibKesiswaan.014.001</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Mengunggah tata tertib baru sebagai draft tidak mengganggu tata tertib yang sedang aktif</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah tata tertib baru tanpa mencentang opsi publikasikan, sementara ada tata tertib lain yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>State Transition Testing</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Ada satu tata tertib berstatus aktif.</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Tata Tertib, isi judul dan berkas baru, jangan centang Publikasikan.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Upload.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Tata tertib baru tersimpan berstatus draft, tata tertib lama yang sedang aktif tetap aktif tanpa perubahan.</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="96">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="D35:D36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12160,6 +16908,1018 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Merekap Laporan Poin Pelanggaran Seluruh Siswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Laporan Pelanggaran</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan melihat laporan pelanggaran dari seluruh sekolah tanpa batas tingkat</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka halaman laporan dan melihat pelanggaran dari semua tingkat kelas.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Ada catatan pelanggaran dari siswa tingkat 10 dan tingkat 12.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Daftar pelanggaran dari seluruh tingkat kelas tampil sekaligus.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan berdasarkan rentang tanggal mulai dan selesai</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi filter tanggal mulai dan selesai pada halaman laporan.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran di dalam dan di luar rentang tanggal yang akan difilter.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, isi tanggal mulai dan selesai.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran dalam rentang tanggal yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan berdasarkan kelas</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan memilih satu kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran dari lebih dari satu kelas.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, pilih filter kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran dari kelas yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan berdasarkan tingkat</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan memilih satu tingkat kelas tertentu.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran dari tingkat kelas yang berbeda-beda.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, pilih filter tingkat tertentu.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran dari siswa tingkat yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan berdasarkan kategori pelanggaran</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan memilih kategori pelanggaran tertentu.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran dari kategori yang berbeda-beda.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, pilih filter kategori tertentu.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran dengan kategori yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan berdasarkan status</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan memilih status disetujui.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Ada pelanggaran dengan status berbeda-beda.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, pilih filter status Disetujui.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Daftar hanya menampilkan pelanggaran berstatus disetujui.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan kelas_id yang tidak ada</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengirim kelas_id yang tidak ada di database sebagai filter.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Kirim request laporan dengan kelas_id tidak valid.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi kelas tidak ditemukan, laporan tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.008</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.008.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan tingkat yang tidak valid</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengirim nilai tingkat di luar pilihan 10/11/12.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Kirim request laporan dengan tingkat = "13".</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Sistem memproses request.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tingkat tidak valid, laporan tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.009</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.009.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan memfilter laporan dengan tanggal selesai sebelum tanggal mulai</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi tanggal selesai yang lebih awal daripada tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, isi tanggal mulai dan tanggal selesai yang lebih awal.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal selesai tidak boleh sebelum tanggal mulai, laporan tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.010</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.010.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengekspor laporan pelanggaran ke Excel</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunduh laporan pelanggaran dalam format Excel beserta sisa poin per siswa.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Ada data pelanggaran yang sesuai dengan filter aktif.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, klik tombol Export Excel.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Berkas Excel berhasil terunduh berisi data pelanggaran dan sisa poin tiap siswa.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.011</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.011.001</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengekspor laporan pelanggaran ke PDF</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunduh laporan pelanggaran dalam format PDF.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Ada data pelanggaran yang sesuai dengan filter aktif.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Laporan Pelanggaran, klik tombol Export PDF.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Berkas PDF berhasil terunduh berisi ringkasan data pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.012</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.012.001</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal (boundary tanggal selesai sama dengan tanggal mulai)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal selesai diisi sama persis dengan tanggal mulai — tepat di batas yang diperbolehkan.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai dan tanggal selesai dengan tanggal yang sama.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Filter lolos validasi, laporan tampil tanpa error.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.LaporanPelanggaran.013</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.LaporanPelanggaran.013.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal (boundary tanggal selesai 1 hari sebelum tanggal mulai)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Tanggal selesai diisi 1 hari sebelum tanggal mulai — tepat di bawah batas yang diperbolehkan.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai, lalu isi tanggal selesai 1 hari sebelumnya.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Field menerima input.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Terapkan filter.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal selesai tidak boleh sebelum tanggal mulai, laporan tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A6:K7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -27,6 +27,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pelanggaran Siswa Kesiswaan" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tata Tertib Kesiswaan" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan Pelanggaran" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Absensi Bk" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Poin Bk" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Bk" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,12 +669,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.001</t>
+          <t>TS.LOG.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.001.001</t>
+          <t>TC.LOG.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -802,12 +805,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.002</t>
+          <t>TS.LOG.002</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.002.001</t>
+          <t>TC.LOG.002.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -938,12 +941,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.003</t>
+          <t>TS.LOG.003</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.003.001</t>
+          <t>TC.LOG.003.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1074,12 +1077,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.004</t>
+          <t>TS.LOG.004</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.004.001</t>
+          <t>TC.LOG.004.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1210,12 +1213,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.005</t>
+          <t>TS.LOG.005</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.005.001</t>
+          <t>TC.LOG.005.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1346,12 +1349,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.006</t>
+          <t>TS.LOG.006</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.006.001</t>
+          <t>TC.LOG.006.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1482,12 +1485,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.007</t>
+          <t>TS.LOG.007</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.007.001</t>
+          <t>TC.LOG.007.001</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1591,12 +1594,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.007</t>
+          <t>TS.LOG.007</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.007.002</t>
+          <t>TC.LOG.007.002</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1700,12 +1703,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.008</t>
+          <t>TS.LOG.008</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.008.001</t>
+          <t>TC.LOG.008.001</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1836,12 +1839,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.008</t>
+          <t>TS.LOG.008</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.008.002</t>
+          <t>TC.LOG.008.002</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1972,12 +1975,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.009</t>
+          <t>TS.LOG.009</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.009.001</t>
+          <t>TC.LOG.009.001</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2108,12 +2111,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TS.Log.010</t>
+          <t>TS.LOG.010</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>TC.Log.010.001</t>
+          <t>TC.LOG.010.001</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -2455,12 +2458,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.001</t>
+          <t>TS.IMS.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.001.001</t>
+          <t>TC.IMS.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2537,12 +2540,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.002</t>
+          <t>TS.IMS.002</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.002.001</t>
+          <t>TC.IMS.002.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2619,12 +2622,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.003</t>
+          <t>TS.IMS.003</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.003.001</t>
+          <t>TC.IMS.003.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2701,12 +2704,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.004</t>
+          <t>TS.IMS.004</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.004.001</t>
+          <t>TC.IMS.004.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2783,12 +2786,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.005</t>
+          <t>TS.IMS.005</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.005.001</t>
+          <t>TC.IMS.005.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2865,12 +2868,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.006</t>
+          <t>TS.IMS.006</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.006.001</t>
+          <t>TC.IMS.006.001</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2947,12 +2950,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.007</t>
+          <t>TS.IMS.007</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.007.001</t>
+          <t>TC.IMS.007.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3029,12 +3032,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.008</t>
+          <t>TS.IMS.008</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.008.001</t>
+          <t>TC.IMS.008.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3111,12 +3114,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportSiswa.009</t>
+          <t>TS.IMS.009</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportSiswa.009.001</t>
+          <t>TC.IMS.009.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3383,12 +3386,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.001</t>
+          <t>TS.IMG.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.001.001</t>
+          <t>TC.IMG.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3465,12 +3468,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.002</t>
+          <t>TS.IMG.002</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.002.001</t>
+          <t>TC.IMG.002.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3547,12 +3550,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.003</t>
+          <t>TS.IMG.003</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.003.001</t>
+          <t>TC.IMG.003.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -3629,12 +3632,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.004</t>
+          <t>TS.IMG.004</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.004.001</t>
+          <t>TC.IMG.004.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3711,12 +3714,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.005</t>
+          <t>TS.IMG.005</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.005.001</t>
+          <t>TC.IMG.005.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -3793,12 +3796,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.006</t>
+          <t>TS.IMG.006</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.006.001</t>
+          <t>TC.IMG.006.001</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3875,12 +3878,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.007</t>
+          <t>TS.IMG.007</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.007.001</t>
+          <t>TC.IMG.007.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3957,12 +3960,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.008</t>
+          <t>TS.IMG.008</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.008.001</t>
+          <t>TC.IMG.008.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -4039,12 +4042,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.ImportGuru.009</t>
+          <t>TS.IMG.009</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.ImportGuru.009.001</t>
+          <t>TC.IMG.009.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4311,12 +4314,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.001</t>
+          <t>TS.MOA.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.001.001</t>
+          <t>TC.MOA.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4366,12 +4369,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.002</t>
+          <t>TS.MOA.002</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.002.001</t>
+          <t>TC.MOA.002.001</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4421,12 +4424,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.003</t>
+          <t>TS.MOA.003</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.003.001</t>
+          <t>TC.MOA.003.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -4503,12 +4506,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.004</t>
+          <t>TS.MOA.004</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.004.001</t>
+          <t>TC.MOA.004.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4585,12 +4588,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.005</t>
+          <t>TS.MOA.005</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.005.001</t>
+          <t>TC.MOA.005.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4667,12 +4670,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.006</t>
+          <t>TS.MOA.006</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.006.001</t>
+          <t>TC.MOA.006.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -4749,12 +4752,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.007</t>
+          <t>TS.MOA.007</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.007.001</t>
+          <t>TC.MOA.007.001</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -4831,12 +4834,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.008</t>
+          <t>TS.MOA.008</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.008.001</t>
+          <t>TC.MOA.008.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -4886,12 +4889,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.009</t>
+          <t>TS.MOA.009</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.009.001</t>
+          <t>TC.MOA.009.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -4968,12 +4971,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.010</t>
+          <t>TS.MOA.010</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.010.001</t>
+          <t>TC.MOA.010.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -5023,12 +5026,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.011</t>
+          <t>TS.MOA.011</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.011.001</t>
+          <t>TC.MOA.011.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -5105,12 +5108,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.012</t>
+          <t>TS.MOA.012</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.012.001</t>
+          <t>TC.MOA.012.001</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5187,12 +5190,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.013</t>
+          <t>TS.MOA.013</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.013.001</t>
+          <t>TC.MOA.013.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5269,12 +5272,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitorAbsensi.014</t>
+          <t>TS.MOA.014</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitorAbsensi.014.001</t>
+          <t>TC.MOA.014.001</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5548,12 +5551,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.001</t>
+          <t>TS.REA.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.001.001</t>
+          <t>TC.REA.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5603,12 +5606,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.002</t>
+          <t>TS.REA.002</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.002.001</t>
+          <t>TC.REA.002.001</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5685,12 +5688,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.003</t>
+          <t>TS.REA.003</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.003.001</t>
+          <t>TC.REA.003.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -5740,12 +5743,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.004</t>
+          <t>TS.REA.004</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.004.001</t>
+          <t>TC.REA.004.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5795,12 +5798,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.005</t>
+          <t>TS.REA.005</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.005.001</t>
+          <t>TC.REA.005.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -5877,12 +5880,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.006</t>
+          <t>TS.REA.006</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.006.001</t>
+          <t>TC.REA.006.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -5959,12 +5962,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.007</t>
+          <t>TS.REA.007</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.007.001</t>
+          <t>TC.REA.007.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6041,12 +6044,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.008</t>
+          <t>TS.REA.008</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.008.001</t>
+          <t>TC.REA.008.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -6123,12 +6126,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.009</t>
+          <t>TS.REA.009</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.009.001</t>
+          <t>TC.REA.009.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -6205,12 +6208,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.010</t>
+          <t>TS.REA.010</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.010.001</t>
+          <t>TC.REA.010.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -6260,12 +6263,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.011</t>
+          <t>TS.REA.011</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.011.001</t>
+          <t>TC.REA.011.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -6315,12 +6318,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.012</t>
+          <t>TS.REA.012</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.012.001</t>
+          <t>TC.REA.012.001</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -6397,12 +6400,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TS.RekapAbsensi.013</t>
+          <t>TS.REA.013</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TC.RekapAbsensi.013.001</t>
+          <t>TC.REA.013.001</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -6662,12 +6665,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.001</t>
+          <t>TS.PPW.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.001.001</t>
+          <t>TC.PPW.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6717,12 +6720,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.002</t>
+          <t>TS.PPW.002</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.002.001</t>
+          <t>TC.PPW.002.001</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6772,12 +6775,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.003</t>
+          <t>TS.PPW.003</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.003.001</t>
+          <t>TC.PPW.003.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -6827,12 +6830,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.004</t>
+          <t>TS.PPW.004</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.004.001</t>
+          <t>TC.PPW.004.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -6882,12 +6885,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.005</t>
+          <t>TS.PPW.005</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.005.001</t>
+          <t>TC.PPW.005.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -6937,12 +6940,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.006</t>
+          <t>TS.PPW.006</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.006.001</t>
+          <t>TC.PPW.006.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -6992,12 +6995,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.007</t>
+          <t>TS.PPW.007</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.007.001</t>
+          <t>TC.PPW.007.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -7047,12 +7050,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.PoinPelanggaran.008</t>
+          <t>TS.PPW.008</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.PoinPelanggaran.008.001</t>
+          <t>TC.PPW.008.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -7229,12 +7232,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.001</t>
+          <t>TS.PGP.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.001.001</t>
+          <t>TC.PGP.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -7311,12 +7314,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.002</t>
+          <t>TS.PGP.002</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.002.001</t>
+          <t>TC.PGP.002.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -7393,12 +7396,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.003</t>
+          <t>TS.PGP.003</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.003.001</t>
+          <t>TC.PGP.003.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -7475,12 +7478,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.004</t>
+          <t>TS.PGP.004</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.004.001</t>
+          <t>TC.PGP.004.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -7557,12 +7560,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.005</t>
+          <t>TS.PGP.005</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.005.001</t>
+          <t>TC.PGP.005.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -7639,12 +7642,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.006</t>
+          <t>TS.PGP.006</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.006.001</t>
+          <t>TC.PGP.006.001</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -7694,12 +7697,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.007</t>
+          <t>TS.PGP.007</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.007.001</t>
+          <t>TC.PGP.007.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -7749,12 +7752,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.008</t>
+          <t>TS.PGP.008</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.008.001</t>
+          <t>TC.PGP.008.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -7804,12 +7807,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.009</t>
+          <t>TS.PGP.009</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.009.001</t>
+          <t>TC.PGP.009.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -7886,12 +7889,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.010</t>
+          <t>TS.PGP.010</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.010.001</t>
+          <t>TC.PGP.010.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -7968,12 +7971,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TS.PengajuanPoinWali.011</t>
+          <t>TS.PGP.011</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TC.PengajuanPoinWali.011.001</t>
+          <t>TC.PGP.011.001</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -8233,12 +8236,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.001</t>
+          <t>TS.JNP.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.001.001</t>
+          <t>TC.JNP.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -8342,12 +8345,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.002</t>
+          <t>TS.JNP.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.002.001</t>
+          <t>TC.JNP.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -8451,12 +8454,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.003</t>
+          <t>TS.JNP.003</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.003.001</t>
+          <t>TC.JNP.003.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -8533,12 +8536,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.004</t>
+          <t>TS.JNP.004</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.004.001</t>
+          <t>TC.JNP.004.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -8642,12 +8645,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.005</t>
+          <t>TS.JNP.005</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.005.001</t>
+          <t>TC.JNP.005.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -8751,12 +8754,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.006</t>
+          <t>TS.JNP.006</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.006.001</t>
+          <t>TC.JNP.006.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -8860,12 +8863,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.007</t>
+          <t>TS.JNP.007</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.007.001</t>
+          <t>TC.JNP.007.001</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -8969,12 +8972,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.008</t>
+          <t>TS.JNP.008</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.008.001</t>
+          <t>TC.JNP.008.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -9051,12 +9054,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.009</t>
+          <t>TS.JNP.009</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.009.001</t>
+          <t>TC.JNP.009.001</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -9133,12 +9136,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.010</t>
+          <t>TS.JNP.010</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.010.001</t>
+          <t>TC.JNP.010.001</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -9188,12 +9191,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.011</t>
+          <t>TS.JNP.011</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.011.001</t>
+          <t>TC.JNP.011.001</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -9243,12 +9246,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.012</t>
+          <t>TS.JNP.012</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.012.001</t>
+          <t>TC.JNP.012.001</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -9325,12 +9328,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.013</t>
+          <t>TS.JNP.013</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.013.001</t>
+          <t>TC.JNP.013.001</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -9407,12 +9410,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.014</t>
+          <t>TS.JNP.014</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.014.001</t>
+          <t>TC.JNP.014.001</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -9489,12 +9492,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.015</t>
+          <t>TS.JNP.015</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.015.001</t>
+          <t>TC.JNP.015.001</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9571,12 +9574,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.016</t>
+          <t>TS.JNP.016</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.016.001</t>
+          <t>TC.JNP.016.001</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -9653,12 +9656,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TS.JenisPelanggaran.017</t>
+          <t>TS.JNP.017</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>TC.JenisPelanggaran.017.001</t>
+          <t>TC.JNP.017.001</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -9967,12 +9970,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitoringSiswa.001</t>
+          <t>TS.MOS.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitoringSiswa.001.001</t>
+          <t>TC.MOS.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -10022,12 +10025,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitoringSiswa.002</t>
+          <t>TS.MOS.002</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitoringSiswa.002.001</t>
+          <t>TC.MOS.002.001</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -10077,12 +10080,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitoringSiswa.003</t>
+          <t>TS.MOS.003</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitoringSiswa.003.001</t>
+          <t>TC.MOS.003.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -10132,12 +10135,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitoringSiswa.004</t>
+          <t>TS.MOS.004</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitoringSiswa.004.001</t>
+          <t>TC.MOS.004.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -10187,12 +10190,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.MonitoringSiswa.005</t>
+          <t>TS.MOS.005</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.MonitoringSiswa.005.001</t>
+          <t>TC.MOS.005.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -10369,12 +10372,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.001</t>
+          <t>TS.PSK.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.001.001</t>
+          <t>TC.PSK.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -10478,12 +10481,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.002</t>
+          <t>TS.PSK.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.002.001</t>
+          <t>TC.PSK.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -10560,12 +10563,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.003</t>
+          <t>TS.PSK.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.003.001</t>
+          <t>TC.PSK.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -10642,12 +10645,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.004</t>
+          <t>TS.PSK.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.004.001</t>
+          <t>TC.PSK.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -10724,12 +10727,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.005</t>
+          <t>TS.PSK.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.005.001</t>
+          <t>TC.PSK.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -10833,12 +10836,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.006</t>
+          <t>TS.PSK.006</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.006.001</t>
+          <t>TC.PSK.006.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -10942,12 +10945,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.007</t>
+          <t>TS.PSK.007</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.007.001</t>
+          <t>TC.PSK.007.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -11051,12 +11054,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.008</t>
+          <t>TS.PSK.008</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.008.001</t>
+          <t>TC.PSK.008.001</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -11133,12 +11136,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.009</t>
+          <t>TS.PSK.009</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.009.001</t>
+          <t>TC.PSK.009.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -11242,12 +11245,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.010</t>
+          <t>TS.PSK.010</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.010.001</t>
+          <t>TC.PSK.010.001</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -11324,12 +11327,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TS.PelanggaranSiswaKesiswaan.011</t>
+          <t>TS.PSK.011</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TC.PelanggaranSiswaKesiswaan.011.001</t>
+          <t>TC.PSK.011.001</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -11610,12 +11613,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.001</t>
+          <t>TS.TTK.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.001.001</t>
+          <t>TC.TTK.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -11719,12 +11722,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.002</t>
+          <t>TS.TTK.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.002.001</t>
+          <t>TC.TTK.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -11801,12 +11804,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.003</t>
+          <t>TS.TTK.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.003.001</t>
+          <t>TC.TTK.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -11883,12 +11886,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.004</t>
+          <t>TS.TTK.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.004.001</t>
+          <t>TC.TTK.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -11965,12 +11968,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.005</t>
+          <t>TS.TTK.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.005.001</t>
+          <t>TC.TTK.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -12047,12 +12050,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.006</t>
+          <t>TS.TTK.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.006.001</t>
+          <t>TC.TTK.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -12102,12 +12105,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.007</t>
+          <t>TS.TTK.007</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.007.001</t>
+          <t>TC.TTK.007.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -12184,12 +12187,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.008</t>
+          <t>TS.TTK.008</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.008.001</t>
+          <t>TC.TTK.008.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -12266,12 +12269,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.009</t>
+          <t>TS.TTK.009</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.009.001</t>
+          <t>TC.TTK.009.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -12348,12 +12351,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.010</t>
+          <t>TS.TTK.010</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.010.001</t>
+          <t>TC.TTK.010.001</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -12430,12 +12433,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.011</t>
+          <t>TS.TTK.011</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.011.001</t>
+          <t>TC.TTK.011.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -12512,12 +12515,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.012</t>
+          <t>TS.TTK.012</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.012.001</t>
+          <t>TC.TTK.012.001</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -12594,12 +12597,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.013</t>
+          <t>TS.TTK.013</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.013.001</t>
+          <t>TC.TTK.013.001</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -12676,12 +12679,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TS.TataTertibKesiswaan.014</t>
+          <t>TS.TTK.014</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>TC.TataTertibKesiswaan.014.001</t>
+          <t>TC.TTK.014.001</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -12976,12 +12979,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.001</t>
+          <t>TS.REG.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.001.001</t>
+          <t>TC.REG.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -13112,12 +13115,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.002</t>
+          <t>TS.REG.002</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.002.001</t>
+          <t>TC.REG.002.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -13248,12 +13251,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.003</t>
+          <t>TS.REG.003</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.003.001</t>
+          <t>TC.REG.003.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -13384,12 +13387,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.004</t>
+          <t>TS.REG.004</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.004.001</t>
+          <t>TC.REG.004.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -13520,12 +13523,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.005</t>
+          <t>TS.REG.005</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.005.001</t>
+          <t>TC.REG.005.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -13656,12 +13659,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.006</t>
+          <t>TS.REG.006</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.006.001</t>
+          <t>TC.REG.006.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -13792,12 +13795,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.007</t>
+          <t>TS.REG.007</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.007.001</t>
+          <t>TC.REG.007.001</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -13874,12 +13877,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.008</t>
+          <t>TS.REG.008</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.008.001</t>
+          <t>TC.REG.008.001</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -14010,12 +14013,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.009</t>
+          <t>TS.REG.009</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.009.001</t>
+          <t>TC.REG.009.001</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -14146,12 +14149,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.010</t>
+          <t>TS.REG.010</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.010.001</t>
+          <t>TC.REG.010.001</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14309,12 +14312,12 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.011</t>
+          <t>TS.REG.011</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.011.001</t>
+          <t>TC.REG.011.001</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -14445,12 +14448,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.012</t>
+          <t>TS.REG.012</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.012.001</t>
+          <t>TC.REG.012.001</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -14581,12 +14584,12 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.013</t>
+          <t>TS.REG.013</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.013.001</t>
+          <t>TC.REG.013.001</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -14717,12 +14720,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.014</t>
+          <t>TS.REG.014</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.014.001</t>
+          <t>TC.REG.014.001</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -14853,12 +14856,12 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.015</t>
+          <t>TS.REG.015</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.015.001</t>
+          <t>TC.REG.015.001</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -14989,12 +14992,12 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.016</t>
+          <t>TS.REG.016</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.016.001</t>
+          <t>TC.REG.016.001</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -15125,12 +15128,12 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.017</t>
+          <t>TS.REG.017</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.017.001</t>
+          <t>TC.REG.017.001</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -15261,12 +15264,12 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.018</t>
+          <t>TS.REG.018</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.018.001</t>
+          <t>TC.REG.018.001</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -15343,12 +15346,12 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.019</t>
+          <t>TS.REG.019</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.019.001</t>
+          <t>TC.REG.019.001</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -15479,12 +15482,12 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.020</t>
+          <t>TS.REG.020</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.020.001</t>
+          <t>TC.REG.020.001</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -15615,12 +15618,12 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.021</t>
+          <t>TS.REG.021</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.021.001</t>
+          <t>TC.REG.021.001</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -15751,12 +15754,12 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.022</t>
+          <t>TS.REG.022</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.022.001</t>
+          <t>TC.REG.022.001</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -15887,12 +15890,12 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.023</t>
+          <t>TS.REG.023</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.023.001</t>
+          <t>TC.REG.023.001</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -16023,12 +16026,12 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.024</t>
+          <t>TS.REG.024</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.024.001</t>
+          <t>TC.REG.024.001</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -16159,12 +16162,12 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.025</t>
+          <t>TS.REG.025</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.025.001</t>
+          <t>TC.REG.025.001</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -16295,12 +16298,12 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.026</t>
+          <t>TS.REG.026</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.026.001</t>
+          <t>TC.REG.026.001</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -16431,12 +16434,12 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.027</t>
+          <t>TS.REG.027</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.027.001</t>
+          <t>TC.REG.027.001</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -16567,12 +16570,12 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>TS.Reg.028</t>
+          <t>TS.REG.028</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>TC.Reg.028.001</t>
+          <t>TC.REG.028.001</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -17026,12 +17029,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.001</t>
+          <t>TS.LAP.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.001.001</t>
+          <t>TC.LAP.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -17081,12 +17084,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.002</t>
+          <t>TS.LAP.002</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.002.001</t>
+          <t>TC.LAP.002.001</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -17136,12 +17139,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.003</t>
+          <t>TS.LAP.003</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.003.001</t>
+          <t>TC.LAP.003.001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -17191,12 +17194,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.004</t>
+          <t>TS.LAP.004</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.004.001</t>
+          <t>TC.LAP.004.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -17246,12 +17249,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.005</t>
+          <t>TS.LAP.005</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.005.001</t>
+          <t>TC.LAP.005.001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -17301,12 +17304,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.006</t>
+          <t>TS.LAP.006</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.006.001</t>
+          <t>TC.LAP.006.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -17356,12 +17359,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.007</t>
+          <t>TS.LAP.007</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.007.001</t>
+          <t>TC.LAP.007.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -17438,12 +17441,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.008</t>
+          <t>TS.LAP.008</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.008.001</t>
+          <t>TC.LAP.008.001</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -17520,12 +17523,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.009</t>
+          <t>TS.LAP.009</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.009.001</t>
+          <t>TC.LAP.009.001</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -17602,12 +17605,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.010</t>
+          <t>TS.LAP.010</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.010.001</t>
+          <t>TC.LAP.010.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -17657,12 +17660,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.011</t>
+          <t>TS.LAP.011</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.011.001</t>
+          <t>TC.LAP.011.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -17712,12 +17715,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.012</t>
+          <t>TS.LAP.012</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.012.001</t>
+          <t>TC.LAP.012.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -17794,12 +17797,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.LaporanPelanggaran.013</t>
+          <t>TS.LAP.013</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.LaporanPelanggaran.013.001</t>
+          <t>TC.LAP.013.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -17920,6 +17923,1707 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Monitoring Absensi Per Tingkat Kelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : BK &gt; Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>BK melihat siswa tingkat sendiri di halaman monitoring</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka halaman monitoring dan melihat siswa dari tingkat yang dipegangnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login dan sudah dikaitkan admin ke tingkat 10; ada siswa yang terdaftar di tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Daftar siswa tingkat 10 tampil, termasuk siswa yang sudah terdaftar.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>BK tidak melihat siswa dari tingkat lain di halaman monitoring</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka halaman monitoring dan memastikan siswa tingkat lain tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login dan dikaitkan ke tingkat 10; ada siswa terdaftar di tingkat 10 dan di tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Daftar cuma menampilkan siswa tingkat 10, siswa tingkat 11 tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>BK memfilter daftar monitoring berdasarkan nama siswa</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BK mencari siswa tingkat sendiri berdasarkan kata kunci nama.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada dua siswa tingkat 10 dengan nama berbeda.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Ketik sebagian nama salah satu siswa di kolom pencarian, lalu klik Cari.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Daftar cuma menampilkan siswa yang namanya cocok dengan kata kunci.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>BK memfilter daftar monitoring berdasarkan kelas dalam tingkat sendiri</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BK memilih satu kelas tertentu dari tingkat sendiri lewat filter kelas.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada dua siswa dari kelas berbeda dalam tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Pilih salah satu kelas pada filter Kelas, lalu klik Cari.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Daftar cuma menampilkan siswa dari kelas yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>BK melihat detail status dan persentase kehadiran siswa tingkat sendiri</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka detail siswa tingkat sendiri untuk melihat status dan persentase kehadiran.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah absen hadir hari ini.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Klik tautan Detail pada baris siswa tersebut.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Halaman detail siswa tampil berisi status kehadiran hari ini dan persentase kehadiran.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>BK ditolak akses saat membuka detail siswa dari tingkat lain</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BK mencoba membuka detail siswa yang berada di tingkat lain.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa yang terdaftar di tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Buka langsung tautan detail siswa tingkat 11 tersebut.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403 Forbidden).</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.MAB.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.MAB.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>BK yang belum dikaitkan ke tingkat manapun tetap bisa membuka halaman monitoring tanpa error</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BK yang profilnya belum diisi tingkat oleh admin membuka halaman monitoring.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login tapi profilnya belum dikaitkan admin ke tingkat manapun; ada siswa terdaftar di tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Halaman tampil tanpa error, tapi daftar siswa kosong.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Monitoring Poin Pelanggaran Per Tingkat Kelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : BK &gt; Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.MPB.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.MPB.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>BK melihat sisa poin default siswa yang belum pernah dapat pelanggaran</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka halaman monitoring dan melihat sisa poin siswa yang belum pernah dicatat pelanggarannya.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 belum pernah dapat pelanggaran atau pengajuan poin.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Sisa poin siswa tersebut tampil 100.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.MPB.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.MPB.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>BK melihat sisa poin yang sudah dihitung dari pelanggaran dan pengajuan poin disetujui</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka halaman monitoring dan melihat sisa poin siswa yang sudah punya pelanggaran dan pengajuan poin disetujui.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah punya 1 pelanggaran disetujui (potongan 30 poin) dan 1 pengajuan poin disetujui (tambahan 10 poin).</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Monitoring.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Sisa poin siswa tersebut tampil 80 (100 dikurangi 30 lalu ditambah 10).</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.MPB.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.MPB.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>BK melihat detail agregat poin siswa tingkat sendiri</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka detail siswa tingkat sendiri untuk melihat riwayat pelanggaran yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah punya 1 pelanggaran disetujui.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Klik tautan Detail pada baris siswa tersebut.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Halaman detail siswa tampil berisi riwayat pelanggaran yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.MPB.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.MPB.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Halaman detail monitoring BK tidak menyediakan tautan catat pelanggaran baru</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka detail siswa dan memastikan tidak ada tombol untuk mencatat pelanggaran baru (beda dengan kesiswaan).</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah terdaftar.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman detail siswa tersebut.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Tidak ada tombol atau tautan Catat Pelanggaran pada halaman detail.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Merekap Laporan Absensi Per Tingkat Kelas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : BK &gt; Rekap Absensi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>BK melihat rekap absensi siswa dari kelas-kelas dalam tingkat sendiri</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>BK membuka halaman rekap absensi dan melihat rekap siswa tingkat sendiri.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah absen hadir pada hari kerja dalam rentang tanggal default (awal bulan sampai hari ini).</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Rekap absensi siswa tingkat 10 tampil, termasuk siswa tersebut.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>BK yang belum dikaitkan ke tingkat manapun melihat halaman rekap kosong tanpa error</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>BK yang profilnya belum diisi tingkat oleh admin membuka halaman rekap absensi.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login tapi profilnya belum dikaitkan admin ke tingkat manapun.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Halaman menampilkan pesan bahwa akun BK belum dikaitkan dengan tingkat kelas, bukan pesan error.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>BK memfilter rekap berdasarkan status kehadiran</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>BK memfilter rekap absensi supaya cuma menampilkan siswa yang punya catatan alpha.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; satu siswa sudah absen hadir dan satu siswa lain sudah absen alpha pada hari kerja yang sama.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pilih status Alpha pada filter Status, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Rekap cuma menampilkan siswa yang punya catatan alpha, siswa yang hadir tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>BK memfilter rekap berdasarkan siswa tertentu</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BK memilih satu siswa tertentu lewat filter siswa.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada dua siswa tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Pilih salah satu siswa pada filter Siswa, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Rekap cuma menampilkan siswa yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>BK memfilter rekap berdasarkan bulan, menggantikan rentang tanggal default</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>BK memilih bulan tertentu lewat filter bulan, menggantikan rentang mulai/selesai default.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Pilih bulan April 2026 pada filter Bulan, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Rentang tanggal rekap berubah jadi 1 April 2026 sampai 30 April 2026, menggantikan rentang mulai/selesai default.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>BK mengisi tanggal selesai sebelum tanggal mulai</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>BK mengisi tanggal selesai yang lebih awal daripada tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai 10 Juni 2026 dan tanggal selesai 5 Juni 2026, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal selesai harus sama dengan atau setelah tanggal mulai, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>BK mengisi tanggal dengan format yang tidak valid</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>BK mengisi tanggal mulai dengan format yang salah.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai dengan format yang salah, misal "10-06-2026", lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal mulai tidak valid, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.008</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.008.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>BK mengekspor rekap absensi ke Excel</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>BK mengunduh rekap absensi tingkat sendiri dalam format Excel.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa tingkat 10 terdaftar.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Export Excel.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Berkas Excel berhasil terunduh dengan nama berkas sesuai tingkat BK.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.009</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.009.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>BK mengekspor rekap absensi ke PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BK mengunduh rekap absensi tingkat sendiri dalam format PDF.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa tingkat 10 terdaftar.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Export PDF.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Berkas PDF berhasil terunduh.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.010</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.010.001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>BK yang belum dikaitkan ke tingkat manapun ditolak saat mengekspor</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>BK yang profilnya belum diisi tingkat oleh admin mencoba mengekspor rekap absensi.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login tapi profilnya belum dikaitkan admin ke tingkat manapun.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Export Excel.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Akses ditolak (403 Forbidden).</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.011</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.011.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>BK mengganti parameter kelas_id di address bar dengan kelas milik tingkat lain</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>BK mencoba melihat rekap kelas dari tingkat lain dengan mengganti parameter kelas_id di address bar.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa terdaftar di kelas tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Ubah parameter kelas_id di address bar jadi id kelas milik tingkat 11, lalu buka halaman Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Rekap tetap cuma menampilkan kelas-kelas tingkat 10 milik sendiri, siswa tingkat 11 tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.012</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.012.001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal rekap (boundary tanggal selesai sama dengan tanggal mulai)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>BK mengisi tanggal selesai yang sama persis dengan tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai dan tanggal selesai dengan tanggal yang sama, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Filter lolos validasi, rekap tampil tanpa pesan error.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAB.013</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAB.013.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal rekap (boundary tanggal selesai 1 hari sebelum tanggal mulai)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>BK mengisi tanggal selesai 1 hari sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Isi tanggal mulai, lalu isi tanggal selesai 1 hari sebelumnya, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi tanggal selesai tidak boleh sebelum tanggal mulai, rekap tidak diproses.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -18038,12 +19742,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.001</t>
+          <t>TS.SIS.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.001.001</t>
+          <t>TC.SIS.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -18147,12 +19851,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.002</t>
+          <t>TS.SIS.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.002.001</t>
+          <t>TC.SIS.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -18256,12 +19960,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.003</t>
+          <t>TS.SIS.003</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.003.001</t>
+          <t>TC.SIS.003.001</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -18365,12 +20069,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.004</t>
+          <t>TS.SIS.004</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.004.001</t>
+          <t>TC.SIS.004.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -18474,12 +20178,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.005</t>
+          <t>TS.SIS.005</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.005.001</t>
+          <t>TC.SIS.005.001</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -18556,12 +20260,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.006</t>
+          <t>TS.SIS.006</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.006.001</t>
+          <t>TC.SIS.006.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -18638,12 +20342,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.007</t>
+          <t>TS.SIS.007</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.007.001</t>
+          <t>TC.SIS.007.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -18747,12 +20451,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.008</t>
+          <t>TS.SIS.008</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.008.001</t>
+          <t>TC.SIS.008.001</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -18829,12 +20533,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.009</t>
+          <t>TS.SIS.009</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.009.001</t>
+          <t>TC.SIS.009.001</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -18911,12 +20615,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.010</t>
+          <t>TS.SIS.010</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.010.001</t>
+          <t>TC.SIS.010.001</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -18966,12 +20670,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.011</t>
+          <t>TS.SIS.011</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.011.001</t>
+          <t>TC.SIS.011.001</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -19048,12 +20752,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.012</t>
+          <t>TS.SIS.012</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.012.001</t>
+          <t>TC.SIS.012.001</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -19130,12 +20834,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.013</t>
+          <t>TS.SIS.013</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.013.001</t>
+          <t>TC.SIS.013.001</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -19212,12 +20916,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.014</t>
+          <t>TS.SIS.014</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.014.001</t>
+          <t>TC.SIS.014.001</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -19294,12 +20998,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.015</t>
+          <t>TS.SIS.015</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.015.001</t>
+          <t>TC.SIS.015.001</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -19376,12 +21080,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.016</t>
+          <t>TS.SIS.016</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.016.001</t>
+          <t>TC.SIS.016.001</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -19458,12 +21162,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.017</t>
+          <t>TS.SIS.017</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.017.001</t>
+          <t>TC.SIS.017.001</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -19540,12 +21244,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.018</t>
+          <t>TS.SIS.018</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.018.001</t>
+          <t>TC.SIS.018.001</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -19622,12 +21326,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.019</t>
+          <t>TS.SIS.019</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.019.001</t>
+          <t>TC.SIS.019.001</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -19704,12 +21408,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.020</t>
+          <t>TS.SIS.020</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.020.001</t>
+          <t>TC.SIS.020.001</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -19786,12 +21490,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.021</t>
+          <t>TS.SIS.021</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.021.001</t>
+          <t>TC.SIS.021.001</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -19868,12 +21572,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.022</t>
+          <t>TS.SIS.022</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.022.001</t>
+          <t>TC.SIS.022.001</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -19950,12 +21654,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TS.Siswa.023</t>
+          <t>TS.SIS.023</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>TC.Siswa.023.001</t>
+          <t>TC.SIS.023.001</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -20313,12 +22017,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.001</t>
+          <t>TS.GUR.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.001.001</t>
+          <t>TC.GUR.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -20422,12 +22126,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.002</t>
+          <t>TS.GUR.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.002.001</t>
+          <t>TC.GUR.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -20504,12 +22208,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.003</t>
+          <t>TS.GUR.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.003.001</t>
+          <t>TC.GUR.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -20586,12 +22290,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.004</t>
+          <t>TS.GUR.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.004.001</t>
+          <t>TC.GUR.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -20668,12 +22372,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.005</t>
+          <t>TS.GUR.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.005.001</t>
+          <t>TC.GUR.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -20750,12 +22454,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.006</t>
+          <t>TS.GUR.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.006.001</t>
+          <t>TC.GUR.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -20832,12 +22536,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.007</t>
+          <t>TS.GUR.007</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.007.001</t>
+          <t>TC.GUR.007.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -20941,12 +22645,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.008</t>
+          <t>TS.GUR.008</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.008.001</t>
+          <t>TC.GUR.008.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -21023,12 +22727,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.009</t>
+          <t>TS.GUR.009</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.009.001</t>
+          <t>TC.GUR.009.001</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -21105,12 +22809,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.010</t>
+          <t>TS.GUR.010</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.010.001</t>
+          <t>TC.GUR.010.001</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -21160,12 +22864,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.011</t>
+          <t>TS.GUR.011</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.011.001</t>
+          <t>TC.GUR.011.001</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -21242,12 +22946,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.012</t>
+          <t>TS.GUR.012</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.012.001</t>
+          <t>TC.GUR.012.001</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -21324,12 +23028,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.013</t>
+          <t>TS.GUR.013</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.013.001</t>
+          <t>TC.GUR.013.001</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -21406,12 +23110,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.014</t>
+          <t>TS.GUR.014</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.014.001</t>
+          <t>TC.GUR.014.001</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -21488,12 +23192,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.015</t>
+          <t>TS.GUR.015</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.015.001</t>
+          <t>TC.GUR.015.001</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -21570,12 +23274,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.016</t>
+          <t>TS.GUR.016</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.016.001</t>
+          <t>TC.GUR.016.001</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -21652,12 +23356,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.017</t>
+          <t>TS.GUR.017</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.017.001</t>
+          <t>TC.GUR.017.001</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -21734,12 +23438,12 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.018</t>
+          <t>TS.GUR.018</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.018.001</t>
+          <t>TC.GUR.018.001</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -21816,12 +23520,12 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.019</t>
+          <t>TS.GUR.019</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.019.001</t>
+          <t>TC.GUR.019.001</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -21898,12 +23602,12 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TS.Guru.020</t>
+          <t>TS.GUR.020</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TC.Guru.020.001</t>
+          <t>TC.GUR.020.001</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -22240,12 +23944,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.001</t>
+          <t>TS.KEL.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.001.001</t>
+          <t>TC.KEL.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -22349,12 +24053,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.002</t>
+          <t>TS.KEL.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.002.001</t>
+          <t>TC.KEL.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -22431,12 +24135,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.003</t>
+          <t>TS.KEL.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.003.001</t>
+          <t>TC.KEL.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -22513,12 +24217,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.004</t>
+          <t>TS.KEL.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.004.001</t>
+          <t>TC.KEL.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -22595,12 +24299,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.005</t>
+          <t>TS.KEL.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.005.001</t>
+          <t>TC.KEL.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -22677,12 +24381,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.006</t>
+          <t>TS.KEL.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.006.001</t>
+          <t>TC.KEL.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -22786,12 +24490,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.007</t>
+          <t>TS.KEL.007</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.007.001</t>
+          <t>TC.KEL.007.001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -22868,12 +24572,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.008</t>
+          <t>TS.KEL.008</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.008.001</t>
+          <t>TC.KEL.008.001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -22950,12 +24654,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TS.Kelas.009</t>
+          <t>TS.KEL.009</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>TC.Kelas.009.001</t>
+          <t>TC.KEL.009.001</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -23222,12 +24926,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.001</t>
+          <t>TS.WKA.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.001.001</t>
+          <t>TC.WKA.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -23331,12 +25035,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.002</t>
+          <t>TS.WKA.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.002.001</t>
+          <t>TC.WKA.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -23413,12 +25117,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.003</t>
+          <t>TS.WKA.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.003.001</t>
+          <t>TC.WKA.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -23495,12 +25199,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.004</t>
+          <t>TS.WKA.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.004.001</t>
+          <t>TC.WKA.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -23577,12 +25281,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.005</t>
+          <t>TS.WKA.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.005.001</t>
+          <t>TC.WKA.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -23659,12 +25363,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.006</t>
+          <t>TS.WKA.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.006.001</t>
+          <t>TC.WKA.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -23741,12 +25445,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.007</t>
+          <t>TS.WKA.007</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.007.001</t>
+          <t>TC.WKA.007.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -23823,12 +25527,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.WaktuAbsen.008</t>
+          <t>TS.WKA.008</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.WaktuAbsen.008.001</t>
+          <t>TC.WKA.008.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -24088,12 +25792,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.001</t>
+          <t>TS.LKA.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.001.001</t>
+          <t>TC.LKA.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -24197,12 +25901,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.002</t>
+          <t>TS.LKA.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.002.001</t>
+          <t>TC.LKA.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -24279,12 +25983,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.003</t>
+          <t>TS.LKA.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.003.001</t>
+          <t>TC.LKA.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -24361,12 +26065,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.004</t>
+          <t>TS.LKA.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.004.001</t>
+          <t>TC.LKA.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -24443,12 +26147,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.005</t>
+          <t>TS.LKA.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.005.001</t>
+          <t>TC.LKA.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -24525,12 +26229,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.006</t>
+          <t>TS.LKA.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.006.001</t>
+          <t>TC.LKA.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -24607,12 +26311,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.007</t>
+          <t>TS.LKA.007</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.007.001</t>
+          <t>TC.LKA.007.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -24689,12 +26393,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.008</t>
+          <t>TS.LKA.008</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.008.001</t>
+          <t>TC.LKA.008.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -24771,12 +26475,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.009</t>
+          <t>TS.LKA.009</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.009.001</t>
+          <t>TC.LKA.009.001</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -24853,12 +26557,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.010</t>
+          <t>TS.LKA.010</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.010.001</t>
+          <t>TC.LKA.010.001</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -24935,12 +26639,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.011</t>
+          <t>TS.LKA.011</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.011.001</t>
+          <t>TC.LKA.011.001</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -25017,12 +26721,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.012</t>
+          <t>TS.LKA.012</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.012.001</t>
+          <t>TC.LKA.012.001</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -25099,12 +26803,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.013</t>
+          <t>TS.LKA.013</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.013.001</t>
+          <t>TC.LKA.013.001</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -25181,12 +26885,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.014</t>
+          <t>TS.LKA.014</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.014.001</t>
+          <t>TC.LKA.014.001</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -25263,12 +26967,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.015</t>
+          <t>TS.LKA.015</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.015.001</t>
+          <t>TC.LKA.015.001</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -25345,12 +27049,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TS.LokasiAbsen.016</t>
+          <t>TS.LKA.016</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>TC.LokasiAbsen.016.001</t>
+          <t>TC.LKA.016.001</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -25666,12 +27370,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.001</t>
+          <t>TS.WAP.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.001.001</t>
+          <t>TC.WAP.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -25775,12 +27479,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.002</t>
+          <t>TS.WAP.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.002.001</t>
+          <t>TC.WAP.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -25857,12 +27561,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.003</t>
+          <t>TS.WAP.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.003.001</t>
+          <t>TC.WAP.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -25939,12 +27643,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.004</t>
+          <t>TS.WAP.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.004.001</t>
+          <t>TC.WAP.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -26021,12 +27725,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.005</t>
+          <t>TS.WAP.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.005.001</t>
+          <t>TC.WAP.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -26103,12 +27807,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.006</t>
+          <t>TS.WAP.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.006.001</t>
+          <t>TC.WAP.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -26185,12 +27889,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.007</t>
+          <t>TS.WAP.007</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.007.001</t>
+          <t>TC.WAP.007.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -26267,12 +27971,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.008</t>
+          <t>TS.WAP.008</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.008.001</t>
+          <t>TC.WAP.008.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -26349,12 +28053,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.009</t>
+          <t>TS.WAP.009</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.009.001</t>
+          <t>TC.WAP.009.001</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -26431,12 +28135,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.010</t>
+          <t>TS.WAP.010</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.010.001</t>
+          <t>TC.WAP.010.001</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -26513,12 +28217,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.011</t>
+          <t>TS.WAP.011</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.011.001</t>
+          <t>TC.WAP.011.001</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -26595,12 +28299,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.012</t>
+          <t>TS.WAP.012</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.012.001</t>
+          <t>TC.WAP.012.001</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -26677,12 +28381,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.013</t>
+          <t>TS.WAP.013</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.013.001</t>
+          <t>TC.WAP.013.001</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -26759,12 +28463,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TS.WhatsappApi.014</t>
+          <t>TS.WAP.014</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TC.WhatsappApi.014.001</t>
+          <t>TC.WAP.014.001</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -27066,12 +28770,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.001</t>
+          <t>TS.PAD.001</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.001.001</t>
+          <t>TC.PAD.001.001</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -27175,12 +28879,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.002</t>
+          <t>TS.PAD.002</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.002.001</t>
+          <t>TC.PAD.002.001</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -27257,12 +28961,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.003</t>
+          <t>TS.PAD.003</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.003.001</t>
+          <t>TC.PAD.003.001</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -27339,12 +29043,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.004</t>
+          <t>TS.PAD.004</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.004.001</t>
+          <t>TC.PAD.004.001</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -27421,12 +29125,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.005</t>
+          <t>TS.PAD.005</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.005.001</t>
+          <t>TC.PAD.005.001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -27503,12 +29207,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.006</t>
+          <t>TS.PAD.006</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.006.001</t>
+          <t>TC.PAD.006.001</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -27585,12 +29289,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.007</t>
+          <t>TS.PAD.007</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.007.001</t>
+          <t>TC.PAD.007.001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -27667,12 +29371,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.008</t>
+          <t>TS.PAD.008</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.008.001</t>
+          <t>TC.PAD.008.001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -27749,12 +29453,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.009</t>
+          <t>TS.PAD.009</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.009.001</t>
+          <t>TC.PAD.009.001</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -27831,12 +29535,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.010</t>
+          <t>TS.PAD.010</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.010.001</t>
+          <t>TC.PAD.010.001</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -27913,12 +29617,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.011</t>
+          <t>TS.PAD.011</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.011.001</t>
+          <t>TC.PAD.011.001</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -27995,12 +29699,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.012</t>
+          <t>TS.PAD.012</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.012.001</t>
+          <t>TC.PAD.012.001</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -28077,12 +29781,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.013</t>
+          <t>TS.PAD.013</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.013.001</t>
+          <t>TC.PAD.013.001</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -28159,12 +29863,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.014</t>
+          <t>TS.PAD.014</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.014.001</t>
+          <t>TC.PAD.014.001</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -28241,12 +29945,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.015</t>
+          <t>TS.PAD.015</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.015.001</t>
+          <t>TC.PAD.015.001</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -28323,12 +30027,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.016</t>
+          <t>TS.PAD.016</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.016.001</t>
+          <t>TC.PAD.016.001</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -28405,12 +30109,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TS.ProfilAdmin.017</t>
+          <t>TS.PAD.017</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>TC.ProfilAdmin.017.001</t>
+          <t>TC.PAD.017.001</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -30,6 +30,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Absensi Bk" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Poin Bk" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Bk" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absensi Siswa" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riwayat Absensi Siswa" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poin Siswa" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19624,6 +19627,2532 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Melakukan Absensi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Siswa &gt; Absensi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen sebelum jendela waktu absensi dimulai</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengklik tombol Absen Sekarang sebelum jam mulai absen.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login dan memiliki profil siswa; jam saat ini sebelum jam mulai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Absensi, ambil selfie, lalu klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan waktu absen sudah lewat atau belum dimulai, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen setelah jendela waktu absensi berakhir</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengklik tombol Absen Sekarang setelah jam selesai absen.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login dan memiliki profil siswa; jam saat ini sudah lewat jam selesai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Absensi, ambil selfie, lalu klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan waktu absen sudah lewat atau belum dimulai, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa absen setelah lewat batas toleransi telat</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengklik tombol Absen Sekarang setelah lewat batas toleransi telat tapi masih dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; jam saat ini sudah lewat batas toleransi telat tapi masih dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie, lalu klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Absensi tercatat dengan status Terlambat.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen tanpa mengambil selfie</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengklik tombol Absen Sekarang tanpa mengambil foto selfie.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login, sedang dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Klik tombol Absen Sekarang tanpa mengambil foto selfie.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi selfie wajib diambil, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen dengan selfie berformat yang tidak diizinkan</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengunggah berkas selfie berformat PDF, bukan gambar.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login, sedang dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Unggah berkas selfie berformat PDF, lalu klik Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi format foto harus JPEG atau WebP, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa yang belum dikaitkan ke profil siswa manapun mencoba absen</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa yang akunnya belum dikaitkan admin ke profil siswa mencoba mengklik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login tapi akunnya belum dikaitkan admin ke profil siswa manapun.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Absensi dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan profil siswa tidak ditemukan, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengecek lokasi GPS di dalam area absensi</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengizinkan akses lokasi GPS saat berada di dalam area absensi (geofence).</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa berada di dalam area tersebut.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Izinkan akses lokasi GPS di perangkat saat diminta halaman Absensi.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Lokasi dinyatakan berada di dalam area absensi, tombol Absen Sekarang bisa diklik.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.008</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.008.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengecek lokasi GPS di luar area absensi dan di luar toleransi</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengizinkan akses lokasi GPS saat berada jauh di luar area absensi (geofence).</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa berada jauh di luar area tersebut.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Izinkan akses lokasi GPS di perangkat saat diminta halaman Absensi.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Lokasi dinyatakan di luar area absensi, tombol Absen Sekarang dikunci.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.009</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.009.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen tanpa mengizinkan lokasi GPS padahal area absensi sudah dikonfigurasi</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengklik tombol Absen Sekarang tanpa mengizinkan akses lokasi GPS.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa tidak mengizinkan akses lokasi GPS.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang tanpa mengizinkan akses lokasi.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi lokasi GPS wajib diaktifkan, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.010</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.010.001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen dengan lokasi di luar area absensi</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengklik tombol Absen Sekarang saat lokasinya berada di luar area absensi.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa berada di luar area tersebut.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie, lalu klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan lokasi di luar area absensi dan tidak bisa absen, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.011</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.011.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Siswa melihat status absensi hari ini yang sesuai</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka atau memuat ulang halaman Absensi setelah sudah absen hari ini.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah absen hari ini dengan status Hadir.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Buka atau muat ulang halaman Absensi.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Status hari ini yang ditampilkan sesuai dengan catatan absensi yang sudah tersimpan (Hadir).</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.012</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.012.001</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah jendela waktu absensi (boundary tepat di jam mulai)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini tepat sama dengan jam mulai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini tepat sama dengan jam mulai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Absensi berhasil tercatat.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.013</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.013.001</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah jendela waktu absensi (boundary 1 menit sebelum jam mulai)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini 1 menit sebelum jam mulai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini 1 menit sebelum jam mulai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan waktu absen belum dimulai, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.014</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.014.001</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas jendela waktu absensi (boundary tepat di jam selesai)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini tepat sama dengan jam selesai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini tepat sama dengan jam selesai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Absensi berhasil tercatat.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.015</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.015.001</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas jendela waktu absensi (boundary 1 menit setelah jam selesai)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini 1 menit setelah jam selesai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini 1 menit setelah jam selesai jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan waktu absen sudah lewat, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.016</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.016.001</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Batas toleransi telat (boundary tepat di batas, hasilnya Hadir)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini tepat di batas toleransi telat.</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini tepat di batas toleransi telat, masih dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Absensi tercatat dengan status Hadir.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.017</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.017.001</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Batas toleransi telat (boundary 1 menit lewat batas, hasilnya Terlambat)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini 1 menit lewat batas toleransi telat.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Jam saat ini 1 menit lewat batas toleransi telat, masih dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Absensi tercatat dengan status Terlambat.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.018</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.018.001</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Batas ukuran maksimum selfie (boundary tepat 300 KB)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengambil selfie berukuran tepat 300 KB.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sedang dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie berukuran tepat 300 KB, lalu klik Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Absensi berhasil tercatat.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TS.ABS.019</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>TC.ABS.019.001</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Batas ukuran maksimum selfie (boundary di atas 300 KB)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengambil selfie berukuran 301 KB.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sedang dalam jendela waktu absensi.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Ambil selfie berukuran 301 KB, lalu klik Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan validasi ukuran foto melebihi batas maksimum, absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Memantau Riwayat Absensi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Siswa &gt; Riwayat Absensi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa melihat riwayat absensi bulan berjalan tanpa memilih filter bulan</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman riwayat absensi tanpa mengubah filter bulan.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; ada catatan absensi pada bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Catatan absensi bulan berjalan tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa memfilter riwayat absensi berdasarkan bulan tertentu</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa memilih bulan April 2026 lewat filter bulan.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; ada catatan absensi di bulan April 2026 dan di bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Pilih bulan April 2026 pada filter bulan, lalu klik Filter.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Cuma catatan absensi bulan April 2026 yang tampil.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Riwayat absensi tetap tampil bulan berjalan saat parameter bulan tidak valid</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengganti parameter bulan di address bar dengan teks yang bukan format bulan valid.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Ubah parameter bulan di address bar jadi teks yang bukan format bulan valid.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Halaman tetap menampilkan catatan bulan berjalan tanpa error.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa melihat pesan kosong saat belum ada catatan absensi pada bulan tersebut</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman riwayat absensi saat belum ada catatan pada bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; belum ada catatan absensi pada bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Muncul pesan belum ada catatan absensi pada bulan ini.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Riwayat absensi ditampilkan terurut dari tanggal terbaru</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka riwayat absensi yang berisi beberapa catatan dengan tanggal berbeda.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; ada beberapa catatan absensi di bulan berjalan dengan tanggal berbeda.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Catatan absensi tampil terurut dari tanggal terbaru ke yang paling lama.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa cuma melihat riwayat absensi miliknya sendiri, bukan siswa lain</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa login dan membuka riwayat absensi, memastikan catatan siswa lain tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Ada dua siswa berbeda yang masing-masing punya catatan absensi di bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Login sebagai salah satu siswa, lalu buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Cuma catatan absensi milik siswa yang login yang tampil, punya siswa lain tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Catatan yang tanggalnya persis di hari terakhir bulan tetap ikut tampil</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka riwayat absensi yang berisi catatan tepat di hari terakhir bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; ada catatan absensi yang tanggalnya tepat di hari terakhir bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Catatan absensi di hari terakhir bulan tersebut tetap ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.008</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.008.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Batas bawah angka bulan pada filter (boundary bulan 01)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengganti parameter bulan di address bar jadi 2026-01.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Ubah parameter bulan di address bar jadi 2026-01, lalu buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Halaman menampilkan catatan bulan Januari 2026.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.009</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.009.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Di bawah batas bawah angka bulan pada filter (boundary bulan 00)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengganti parameter bulan di address bar jadi 2026-00.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Ubah parameter bulan di address bar jadi 2026-00, lalu buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Format bulan tidak valid, halaman kembali menampilkan bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.010</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.010.001</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Batas atas angka bulan pada filter (boundary bulan 12)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengganti parameter bulan di address bar jadi 2026-12.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Ubah parameter bulan di address bar jadi 2026-12, lalu buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Halaman menampilkan catatan bulan Desember 2026.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TS.RAS.011</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TC.RAS.011.001</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Di atas batas atas angka bulan pada filter (boundary bulan 13)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Siswa mengganti parameter bulan di address bar jadi 2026-13.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Ubah parameter bulan di address bar jadi 2026-13, lalu buka halaman Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Format bulan tidak valid, halaman kembali menampilkan bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.1" customWidth="1" min="1" max="1"/>
+    <col width="19.7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17.3" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7.9" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Memantau Poin Pelanggaran</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Page : Siswa &gt; Poin Saya</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="31.2" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.001</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa melihat pelanggaran yang sudah disetujui di halaman Poin Saya</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya dan melihat pelanggaran yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; siswa punya 1 pelanggaran yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang sudah disetujui tampil di daftar riwayat pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.002</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang masih menunggu atau ditolak tidak ikut tampil</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat punya pelanggaran berstatus menunggu dan ditolak.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; siswa punya 1 pelanggaran berstatus menunggu dan 1 pelanggaran berstatus ditolak.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Kedua pelanggaran yang belum disetujui itu tidak ikut tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.003</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.003.001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Sisa poin dihitung dari pelanggaran disetujui dan pengajuan poin disetujui</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat punya pelanggaran disetujui dan pengajuan poin disetujui.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; siswa punya 1 pelanggaran disetujui (potongan 30 poin) dan 1 pengajuan poin disetujui (tambahan 10 poin).</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Sisa poin yang ditampilkan 80 (100 dikurangi 30 lalu ditambah 10).</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.004</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.004.001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa yang belum pernah punya pelanggaran melihat sisa poin default 100</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat belum pernah punya catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; siswa belum pernah punya catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 100 dan muncul pesan belum ada catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.005</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.005.001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa cuma melihat pelanggaran miliknya sendiri, bukan siswa lain</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Siswa login dan membuka halaman Poin Saya, memastikan pelanggaran siswa lain tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Ada dua siswa berbeda; salah satu siswa punya 1 pelanggaran yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Login sebagai siswa yang tidak punya pelanggaran, lalu buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Pelanggaran milik siswa lain tidak ikut tampil.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.006</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.006.001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Batas label status poin (boundary 1 poin di atas 75, label Baik)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat sisa poinnya 76.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; sisa poin siswa saat ini 76 (1 di atas batas 75).</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Label status yang tampil "Baik".</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.007</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.007.001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Batas label status poin (boundary tepat 75, label Cukup bukan Baik)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat sisa poinnya tepat 75.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; sisa poin siswa saat ini tepat 75.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Label status yang tampil "Cukup", bukan "Baik".</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.008</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.008.001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Batas label status poin (boundary 1 poin di atas 50, label Cukup)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat sisa poinnya 51.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; sisa poin siswa saat ini 51 (1 di atas batas 50).</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Label status yang tampil "Cukup".</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TS.POS.009</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>TC.POS.009.001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Batas label status poin (boundary tepat 50, label Perhatian bukan Cukup)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Siswa membuka halaman Poin Saya saat sisa poinnya tepat 50.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Siswa sudah login; sisa poin siswa saat ini tepat 50.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Buka halaman Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Label status yang tampil "Perhatian", bukan "Cukup".</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.1" customWidth="1" min="1" max="1"/>
@@ -1781,224 +1781,6 @@
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>TS.LOG.009</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>TC.LOG.009.001</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Login menggunakan akun Google yang sudah terhubung (linked)</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Pengguna login memakai tombol "Masuk dengan Google" dengan akun Google yang sudah terhubung ke akun terdaftar.</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Pengguna punya akun terdaftar dan sudah menghubungkan (link) akun Google-nya sebelumnya.</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>Buka halaman login.</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>Halaman login tampil dengan tombol "Masuk dengan Google".</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Klik tombol "Masuk dengan Google".</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>Pengguna diarahkan ke halaman otorisasi Google.</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>Pilih/otorisasi akun Google yang sudah terhubung.</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Pengguna berhasil login dan diarahkan ke dashboard sesuai perannya.</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>TS.LOG.010</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>TC.LOG.010.001</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Login menggunakan akun Google yang belum terdaftar</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Pengguna login memakai tombol "Masuk dengan Google" dengan akun Google yang belum pernah terhubung/terdaftar di sistem.</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Akun Google yang dipakai tidak cocok dengan id_google atau email manapun di database.</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Buka halaman login.</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Halaman login tampil dengan tombol "Masuk dengan Google".</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Klik tombol "Masuk dengan Google".</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Pengguna diarahkan ke halaman otorisasi Google.</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Otorisasi dengan akun Google yang belum terhubung ke akun manapun.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Akun Google ini belum terdaftar", pengguna diarahkan ke halaman daftar dan tidak berhasil login.</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11614,7 +11396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.1" customWidth="1" min="1" max="1"/>
@@ -14579,197 +14361,6 @@
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>TS.REG.027</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>TC.REG.027.001</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Lengkapi pendaftaran siswa menggunakan tombol Daftar dengan Google</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Siswa melengkapi pendaftaran memakai akun Google alih-alih isi email/password manual.</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah lolos verifikasi identitas (step 1).</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Klik tombol "Daftar dengan Google".</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Siswa diarahkan ke halaman otorisasi Google.</t>
-        </is>
-      </c>
-      <c r="K88" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="n"/>
-      <c r="B89" s="9" t="n"/>
-      <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="9" t="n"/>
-      <c r="F89" s="9" t="n"/>
-      <c r="G89" s="9" t="n"/>
-      <c r="H89" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Otorisasi dengan akun Google.</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>Akun berhasil diaktifkan (status registered), email &amp; id Google akun tersimpan, siswa langsung login dan diarahkan ke dashboard siswa.</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>TS.REG.028</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>TC.REG.028.001</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Lengkapi pendaftaran guru menggunakan tombol Daftar dengan Google</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Guru melengkapi pendaftaran memakai akun Google, lalu diminta melengkapi nomor telepon.</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Guru sudah lolos verifikasi identitas (step 1).</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Klik tombol "Daftar dengan Google".</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>Guru diarahkan ke halaman otorisasi Google.</t>
-        </is>
-      </c>
-      <c r="K90" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="n"/>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="n"/>
-      <c r="H91" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Otorisasi dengan akun Google.</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>Akun berhasil diaktifkan, sistem meminta nomor telepon (karena peran guru).</t>
-        </is>
-      </c>
-      <c r="K91" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="n"/>
-      <c r="B92" s="9" t="n"/>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="9" t="n"/>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
-      <c r="H92" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Isi nomor telepon yang valid dan submit.</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>Nomor telepon tersimpan di profil guru, guru diarahkan ke dashboard wali kelas.</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15890,8 +15481,8 @@
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G23:G24"/>
     <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="D17:D18"/>
@@ -22213,8 +21804,8 @@
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D45:D46"/>
     <mergeCell ref="D9:D11"/>
-    <mergeCell ref="D45:D46"/>
     <mergeCell ref="F45:F46"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="F26:F27"/>
@@ -25127,7 +24718,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E14:E15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="A22:A23"/>
@@ -25139,6 +24729,7 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="G22:G23"/>
+    <mergeCell ref="E9:E11"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="E12:E13"/>
@@ -25155,7 +24746,7 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25973,8 +25564,8 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B14:B15"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F18:F19"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="G9:G11"/>
@@ -25990,7 +25581,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E14:E15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="D24:D25"/>
@@ -26006,6 +25596,7 @@
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E9:E11"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="E12:E13"/>
@@ -26021,7 +25612,7 @@
     <mergeCell ref="F16:F17"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28543,8 +28134,8 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="C26:C27"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F18:F19"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="B26:B27"/>
@@ -30088,8 +29679,8 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F30:F31"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="F26:F27"/>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -21608,8 +21608,8 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="F9:F11"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="D30:D32"/>
-    <mergeCell ref="B45:B47"/>
     <mergeCell ref="C78:C80"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
@@ -21674,8 +21674,8 @@
     <mergeCell ref="E24:E26"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="F30:F32"/>
+    <mergeCell ref="A69:A71"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A69:A71"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="B48:B50"/>
@@ -21690,8 +21690,8 @@
     <mergeCell ref="D78:D80"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C72:C74"/>
     <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C72:C74"/>
     <mergeCell ref="A63:A65"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="G38:G39"/>
@@ -21769,11 +21769,11 @@
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A78:A80"/>
     <mergeCell ref="A75:A77"/>
+    <mergeCell ref="C75:C77"/>
     <mergeCell ref="E69:E71"/>
-    <mergeCell ref="C75:C77"/>
     <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
-    <mergeCell ref="B9:B11"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="D66:D68"/>
@@ -21788,7 +21788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -21898,55 +21898,55 @@
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.GUR.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.GUR.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan data guru baru dengan data valid</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Menambah guru dengan peran wali kelas</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi form tambah guru dengan data lengkap dan valid.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin menambah guru berperan wali kelas dengan data yang benar.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tambah Guru.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form tambah guru tampil (tanpa kolom email/password).</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Guru lalu klik tombol Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -21960,20 +21960,20 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama, NIP, telepon, dan peran yang valid.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Data yang diketik/dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama, NIP, dan Nomor HP, lalu pilih peran Wali Kelas.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Semua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -21987,157 +21987,129 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Guru tersimpan dengan status unregistered dan password default "password", admin diarahkan ke daftar guru.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Guru berhasil ditambahkan." dan nama guru tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>TS.GUR.002</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>TC.GUR.002.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan guru dengan NIP yang sudah dipakai</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi NIP yang sudah terpakai guru lain.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Menambah guru BK beserta tingkat yang dipegang</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Admin menambah guru BK; khusus peran ini, tingkat wajib dipilih.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada guru lain dengan NIP tersebut.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Isi NIP yang sudah dipakai guru lain.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>NIP yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi NIP sudah dipakai, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Pilih peran BK.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pilihan Tingkat yang wajib diisi.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.003</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.003.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan guru dengan nama mengandung angka</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi nama guru yang mengandung karakter angka.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama dengan angka (misal "Guru123").</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Teks yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama dan NIP, lalu pilih tingkat yang dipegang.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Semua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22151,130 +22123,102 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Guru berhasil ditambahkan." dan nama guru tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.003</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.003.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Menambah guru dengan peran kesiswaan</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Admin menambah guru berperan kesiswaan.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format nama tidak valid, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.004</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.004.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan guru dengan peran tidak valid</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengirim nilai peran di luar wali_kelas/bk/kesiswaan.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Kirim data tambah guru dengan peran = "admin" (nilai di luar pilihan form).</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi peran tidak valid, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.005</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.005.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Tingkat yang dikirim saat peran bukan BK dipaksa null</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi tingkat untuk guru berperan wali_kelas (bukan BK), tingkat diabaikan dan tersimpan null.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Isi form tambah guru dengan peran wali_kelas dan tingkat tetap terisi.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Peran wali_kelas dan tingkat yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama dan NIP, lalu pilih peran Kesiswaan.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Semua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22288,130 +22232,102 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Guru berhasil ditambahkan." dan nama guru tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52.8" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.004</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.004.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Menambah wali kelas sekaligus memilihkan kelasnya</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Admin langsung memilihkan kelas untuk wali kelas yang baru ditambahkan.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada kelas yang belum punya wali kelas.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26.4" customHeight="1" s="9">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Guru tersimpan, kolom tingkat tersimpan null (bukan error), karena aturan tingkat hanya berlaku untuk peran BK.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.8" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.006</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.006.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Percobaan mengirim password langsung saat tambah guru diabaikan sistem</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengirim field password tambahan secara manual (bypass form), tetap diabaikan sistem.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Form Tambah Guru di UI sudah tidak memiliki field email/password sama sekali.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Kirim request tambah guru dengan field password tambahan yang tidak ada di form.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Guru tersimpan dengan password default "password", nilai password kiriman diabaikan.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26.4" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.007</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.007.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Admin memperbarui data guru</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengubah nama dan telepon guru yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Data guru sudah ada.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Guru.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil terisi data lama (tanpa kolom email/password).</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih peran Wali Kelas.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pilihan kelas yang belum punya wali kelas.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22425,321 +22341,265 @@
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama dan NIP, lalu pilih salah satu kelas.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Semua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Guru berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Nama guru tersebut tampil sebagai wali kelas pada kelas yang dipilih.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.005</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.005.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK tidak memilih tingkat</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Admin memilih peran BK tetapi tidak mengisi tingkat yang dipegang.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52.8" customHeight="1" s="9">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Ubah nama dan telepon.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Nama dan telepon baru yang diketik tampil di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama dan NIP, pilih peran BK, lalu biarkan Tingkat kosong.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Kolom Tingkat tetap kosong.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26.4" customHeight="1" s="9">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Data guru berhasil diperbarui.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.008</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.008.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Admin menghapus data guru</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Admin menghapus satu data guru dari daftar.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa Tingkat wajib diisi, dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39.6" customHeight="1" s="9">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.006</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.006.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>NIP sudah dipakai guru lain</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Admin memakai NIP yang sudah dimiliki guru lain.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Data guru sudah ada.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris guru.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada guru yang memakai NIP tersebut.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26.4" customHeight="1" s="9">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Data guru terhapus dari sistem.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="52.8" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.009</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.009.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Guru berstatus unregistered diblokir mengakses dashboard</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Akun guru yang belum menyelesaikan pendaftaran mencoba akses dashboard.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Akun guru berstatus unregistered.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung dashboard wali kelas.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Guru diarahkan ke halaman login dengan pesan "Akun belum terdaftar. Silakan daftar terlebih dahulu.", tidak ada sesi login.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.010</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.010.001</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Admin memfilter daftar guru berdasarkan status pendaftaran</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Admin memfilter daftar guru dengan status registered.</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Ada guru dengan status registered dan unregistered.</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Daftar Guru.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Halaman daftar guru tampil menampilkan semua guru.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="39.6" customHeight="1" s="9">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Pilih filter status Registered.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan guru dengan status registered, guru unregistered tidak muncul.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26.4" customHeight="1" s="9">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.011</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.011.001</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum nama guru (boundary di bawah 3 karakter)</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Nama diisi 2 karakter — tepat di bawah batas minimum 3.</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama guru dengan 2 karakter (misal "Ab").</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Isi NIP dengan nomor yang sudah dipakai guru lain.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>NIP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22753,239 +22613,211 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "NIP sudah digunakan." dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26.4" customHeight="1" s="9">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.007</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.007.001</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Nama diisi mengandung angka</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengisi nama guru memakai angka, padahal nama hanya boleh berisi huruf.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26.4" customHeight="1" s="9">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama dengan teks yang mengandung angka.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26.4" customHeight="1" s="9">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nama minimal 3 karakter, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26.4" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.012</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.012.001</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum nama guru (boundary tepat 3 karakter)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Nama diisi tepat 3 karakter — tepat di batas minimum.</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama guru tepat 3 karakter (misal "Abi").</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26.4" customHeight="1" s="9">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n">
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Format Nama tidak valid." dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26.4" customHeight="1" s="9">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.008</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.008.001</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Memilih kelas yang sudah punya wali kelas</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Admin mencoba memilihkan kelas yang wali kelasnya sudah ada.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada kelas yang wali kelasnya terisi.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru lalu pilih peran Wali Kelas.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan kelas hanya berisi kelas yang belum punya wali kelas.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26.4" customHeight="1" s="9">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>Nama lolos validasi minimum, guru tersimpan.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="26.4" customHeight="1" s="9">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.013</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.013.001</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nama guru (boundary tepat 100 karakter)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Nama diisi tepat 100 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama guru tepat 100 karakter.</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26.4" customHeight="1" s="9">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>Nama lolos validasi maksimum, guru tersimpan.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26.4" customHeight="1" s="9">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.014</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.014.001</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nama guru (boundary di atas 100 karakter)</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Nama diisi 101 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama guru dengan 101 karakter.</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih kelas yang wali kelasnya sudah terisi.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22999,239 +22831,211 @@
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas yang dipilih tidak valid." dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26.4" customHeight="1" s="9">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.009</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.009.001</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Mengubah data guru yang sudah ada</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengubah nama guru yang sudah tercatat.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada guru yang tercatat.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Guru lalu klik Edit pada guru yang dituju.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit tampil berisi data guru yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26.4" customHeight="1" s="9">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Ubah Nama menjadi nama yang baru.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Nama baru tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26.4" customHeight="1" s="9">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J35" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nama melebihi batas maksimum, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26.4" customHeight="1" s="9">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.015</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.015.001</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum NIP (boundary tepat 30 karakter)</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Guru berhasil diperbarui." dan nama baru tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="39.6" customHeight="1" s="9">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.010</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.010.001</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus data guru</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>NIP diisi tepat 30 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>Isi NIP dengan tepat 30 karakter.</t>
-        </is>
-      </c>
-      <c r="J36" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom NIP.</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26.4" customHeight="1" s="9">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8" t="n">
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Admin menghapus guru dari daftar.</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada guru yang tercatat.</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Guru.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Daftar guru tampil.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26.4" customHeight="1" s="9">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>NIP lolos validasi maksimum, guru tersimpan.</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26.4" customHeight="1" s="9">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.016</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.016.001</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum NIP (boundary di atas 30 karakter)</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>NIP diisi 31 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>Isi NIP dengan 31 karakter.</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom NIP.</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="39.6" customHeight="1" s="9">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi NIP melebihi batas maksimum, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="26.4" customHeight="1" s="9">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.017</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.017.001</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum telepon guru (boundary di bawah 10 karakter)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Telepon diisi 9 karakter — tepat di bawah batas minimum 10.</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>Isi telepon 9 digit.</t>
-        </is>
-      </c>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom telepon.</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada guru yang dituju lalu setujui konfirmasi.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Kotak konfirmasi tampil dan disetujui.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23245,75 +23049,75 @@
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J41" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi telepon minimal 10 digit, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="H41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Tunggu halaman selesai dimuat.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Guru berhasil dihapus." dan nama guru hilang dari daftar.</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26.4" customHeight="1" s="9">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.018</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.018.001</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum telepon guru (boundary tepat 10 karakter)</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.011</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.011.001</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Mencari guru berdasarkan nama</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Telepon diisi tepat 10 karakter — tepat di batas minimum.</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>Isi telepon tepat 10 digit.</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom telepon.</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Admin mencari guru memakai kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada beberapa guru dengan nama berbeda.</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Guru.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Daftar seluruh guru tampil.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23327,75 +23131,75 @@
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>Telepon lolos validasi minimum, guru tersimpan.</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Ketik nama guru yang dicari di kolom pencarian lalu terapkan.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Daftar menyisakan guru yang namanya cocok, guru lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26.4" customHeight="1" s="9">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.019</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.019.001</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum telepon guru (boundary tepat 15 karakter)</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.012</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.012.001</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring guru berdasarkan peran</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Telepon diisi tepat 15 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>Isi telepon tepat 15 digit.</t>
-        </is>
-      </c>
-      <c r="J44" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom telepon.</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Admin menyaring daftar guru memakai pilihan peran.</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada guru dengan peran berbeda.</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Guru.</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>Daftar seluruh guru tampil.</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23409,233 +23213,1276 @@
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Pilih peran pada penyaring lalu terapkan.</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>Daftar menyisakan guru dengan peran itu saja.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26.4" customHeight="1" s="9">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.013</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.013.001</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nama (minimal 3 karakter)</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>Nama diisi 2 karakter, tepat satu karakter di bawah batas minimum.</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="39.6" customHeight="1" s="9">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama sepanjang 2 karakter.</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J45" s="15" t="inlineStr">
-        <is>
-          <t>Telepon lolos validasi maksimum, guru tersimpan.</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="26.4" customHeight="1" s="9">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>TS.GUR.020</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>TC.GUR.020.001</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum telepon guru (boundary di atas 15 karakter)</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nama minimal 3 karakter."</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.013</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.013.002</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nama (minimal 3 karakter)</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>Nama diisi 3 karakter, tepat di batas minimum.</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama sepanjang 3 karakter.</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>Nama diterima dan muncul pesan "Guru berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.014</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.014.001</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nama (maksimal 100 karakter)</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>Nama diisi 100 karakter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama sepanjang 100 karakter.</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>Nama diterima dan muncul pesan "Guru berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.014</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.014.002</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nama (maksimal 100 karakter)</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Telepon diisi 16 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>Nama diisi 101 karakter, tepat satu karakter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>Isi telepon 16 digit.</t>
-        </is>
-      </c>
-      <c r="J46" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom telepon.</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="39.6" customHeight="1" s="9">
-      <c r="A47" s="7" t="n"/>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="n">
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama sepanjang 101 karakter.</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J47" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi telepon melebihi batas maksimum, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nama maksimal 100 karakter."</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.015</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.015.001</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang NIP (maksimal 30 karakter)</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>NIP diisi 30 karakter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>Isi NIP sepanjang 30 karakter.</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>NIP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>NIP diterima dan muncul pesan "Guru berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.015</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.015.002</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang NIP (maksimal 30 karakter)</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>NIP diisi 31 karakter, tepat satu karakter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>Isi NIP sepanjang 31 karakter.</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>NIP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "NIP maksimal 30 karakter."</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.016</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.016.001</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor HP (minimal 10 karakter)</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>Nomor HP diisi 9 digit, tepat satu digit di bawah batas minimum.</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor HP sepanjang 9 digit.</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="inlineStr">
+        <is>
+          <t>Nomor HP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nomor HP minimal 10 karakter."</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.016</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.016.002</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor HP (minimal 10 karakter)</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>Nomor HP diisi 10 digit, tepat di batas minimum.</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor HP sepanjang 10 digit.</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="inlineStr">
+        <is>
+          <t>Nomor HP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J69" s="14" t="inlineStr">
+        <is>
+          <t>Nomor HP diterima dan muncul pesan "Guru berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.017</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.017.001</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor HP (maksimal 15 karakter)</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>Nomor HP diisi 15 digit, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor HP sepanjang 15 digit.</t>
+        </is>
+      </c>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>Nomor HP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>Nomor HP diterima dan muncul pesan "Guru berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>TS.GUR.017</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>TC.GUR.017.002</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor HP (maksimal 15 karakter)</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>Nomor HP diisi 16 digit, tepat satu digit di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Guru.</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Guru tampil.</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor HP sepanjang 16 digit.</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>Nomor HP yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nomor HP maksimal 15 karakter."</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="124">
+  <mergeCells count="159">
     <mergeCell ref="F44:F45"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B55:B57"/>
     <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="B36:B38"/>
     <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B23:B24"/>
     <mergeCell ref="F9:F11"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="G16:G18"/>
     <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="F24:F26"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="D70:D72"/>
+    <mergeCell ref="F70:F72"/>
+    <mergeCell ref="C52:C54"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="G19:G23"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="C12:C15"/>
     <mergeCell ref="B44:B45"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G70:G72"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="D19:D23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F19:F23"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="C64:C66"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="B61:B63"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="G33:G35"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="C67:C69"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="E42:E43"/>
     <mergeCell ref="G42:G43"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D58:D60"/>
     <mergeCell ref="C44:C45"/>
+    <mergeCell ref="F58:F60"/>
     <mergeCell ref="E44:E45"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="F67:F69"/>
     <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="D52:D54"/>
     <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F55:F57"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="G73:G75"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="D49:D51"/>
     <mergeCell ref="A42:A43"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="B27:B29"/>
     <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="E12:E15"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23647,7 +24494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -23757,55 +24604,55 @@
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.KEL.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.KEL.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan kelas baru dengan wali kelas</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Menambah kelas baru</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi form tambah kelas lengkap dengan wali kelas.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin menambah kelas dengan memilih tingkat dan mengisi nama kelas.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Ada guru berperan wali_kelas yang tersedia.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tambah Kelas.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form tampil dengan kolom identifier, tingkat, wali kelas.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas lalu klik tombol Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23819,20 +24666,20 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi identifier, pilih tingkat, dan pilih wali kelas.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Data yang diketik/dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Tingkat lalu isi Nama Kelas.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Kedua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23846,294 +24693,238 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Kelas tersimpan dengan nama gabungan tingkat+identifier.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas berhasil ditambahkan." dan kelas tampil di daftar dengan nama gabungan tingkat dan namanya.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>TS.KEL.002</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>TC.KEL.002.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan kelas dengan kombinasi nama dan tingkat yang sudah ada</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Admin membuat kelas dengan identifier+tingkat yang sudah dipakai kelas lain.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Menambah kelas sekaligus memilihkan wali kelasnya</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Admin langsung memilihkan wali kelas saat membuat kelas baru.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada kelas dengan kombinasi nama+tingkat yang sama.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Isi identifier dan tingkat yang sama dengan kelas yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Data yang diketik/dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada guru berperan wali kelas.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52.8" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Tingkat, isi Nama Kelas, lalu pilih salah satu wali kelas.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Semua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "Kelas dengan kombinasi ini sudah ada", data tidak tersimpan (bukan error 500).</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas berhasil ditambahkan." dan nama wali kelas tampil di daftar kelas.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.4" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>TS.KEL.003</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TC.KEL.003.001</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan kelas dengan tingkat tidak valid</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengirim nilai tingkat di luar 10/11/12.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Menambah kelas sekaligus memasukkan beberapa siswa</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Admin mencentang beberapa siswa yang belum punya kelas saat membuat kelas baru.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Isi tingkat dengan nilai tidak valid (misal 13).</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang diketik tampil di kolom tingkat.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26.4" customHeight="1" s="9">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada siswa yang belum punya kelas.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Formulir tampil beserta daftar siswa yang belum punya kelas.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Tingkat, isi Nama Kelas, lalu centang beberapa siswa.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Siswa yang dicentang tertandai.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tingkat tidak valid, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.KEL.004</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.KEL.004.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan kelas dengan wali kelas yang tidak ada</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengirim wali_kelas_id yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Kirim data tambah kelas dengan wali_kelas_id yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi wali kelas tidak ditemukan, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.KEL.005</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.KEL.005.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Admin menambahkan kelas tanpa memilih wali kelas</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Admin membuat kelas tanpa mengisi wali kelas (opsional).</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Isi identifier dan tingkat, biarkan wali kelas kosong.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Identifier dan tingkat yang dipilih tampil, kolom wali kelas tetap kosong.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24147,75 +24938,75 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Kelas tersimpan dengan wali_kelas_id bernilai null.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="H18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Siswa dan saring berdasarkan tingkat kelas itu.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Siswa yang tadi dicentang tampil sebagai anggota kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.KEL.006</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.KEL.006.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Admin memperbarui data kelas</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengubah identifier, tingkat, dan wali kelas yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.004</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.004.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Nama kelas sudah ada di tingkat yang sama</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Admin membuat kelas dengan nama dan tingkat yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Data kelas sudah ada.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Kelas.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil terisi data lama.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada kelas dengan nama dan tingkat tersebut.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24229,20 +25020,20 @@
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Ubah identifier, tingkat, dan wali kelas.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Data baru yang diketik/dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Tingkat dan isi Nama Kelas yang sama dengan kelas yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Kedua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24256,239 +25047,211 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Data kelas berhasil diperbarui dengan nama baru.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas dengan kombinasi ini sudah ada." dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TS.KEL.007</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>TC.KEL.007.001</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Admin menghapus data kelas</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Admin menghapus satu data kelas dari daftar.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.005</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.005.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Tingkat yang dipilih tidak tersedia</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengirim tingkat di luar pilihan yang disediakan.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Data kelas sudah ada.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris kelas.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Data kelas terhapus dari sistem.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih tingkat di luar pilihan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26.4" customHeight="1" s="9">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TS.KEL.008</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>TC.KEL.008.001</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum identifier kelas (boundary tepat 20 karakter)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Identifier diisi tepat 20 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Isi identifier dengan tepat 20 karakter.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom identifier.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tingkat yang dipilih tidak valid." dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.006</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.006.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Memasukkan siswa yang sudah punya kelas lain</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Admin mencoba memasukkan siswa yang sudah menjadi anggota kelas lain.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada siswa yang menjadi anggota kelas lain.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Formulir tampil, dan daftar pilihan hanya berisi siswa yang belum punya kelas.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26.4" customHeight="1" s="9">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Identifier lolos validasi maksimum, kelas tersimpan.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TS.KEL.009</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>TC.KEL.009.001</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum identifier kelas (boundary di atas 20 karakter)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Identifier diisi 21 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Isi identifier dengan 21 karakter.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom identifier.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih siswa yang sudah menjadi anggota kelas lain.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24502,88 +25265,1323 @@
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Siswa yang dipilih tidak valid." dan data tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.007</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.007.001</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Mengubah nama kelas</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengubah nama kelas yang sudah ada.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada kelas yang tercatat.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas lalu klik Edit pada kelas yang dituju.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit tampil berisi data kelas yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Ubah Nama Kelas menjadi nama yang baru.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Nama baru tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi identifier melebihi batas maksimum, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas berhasil diperbarui." dan nama baru tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.008</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.008.001</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Mengeluarkan siswa dari kelas</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Admin membuang centang siswa saat mengubah kelas, sehingga siswa itu keluar dari kelas.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Kelas sudah punya anggota.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas lalu klik Edit pada kelas yang dituju.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit tampil beserta daftar anggota kelas yang tercentang.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Buang centang pada siswa yang hendak dikeluarkan.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Centang siswa tersebut hilang.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas berhasil diperbarui."</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman detail kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Siswa yang dikeluarkan tidak lagi tampil sebagai anggota kelas.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.009</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.009.001</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus kelas</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Admin menghapus kelas dari daftar.</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada kelas yang tercatat.</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Daftar kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada kelas yang dituju lalu setujui konfirmasi.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Kotak konfirmasi tampil dan disetujui.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Tunggu halaman selesai dimuat.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kelas berhasil dihapus." dan kelas hilang dari daftar.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.010</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.010.001</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Mencari kelas berdasarkan nama</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Admin mencari kelas memakai kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada beberapa kelas dengan nama berbeda.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Daftar seluruh kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Ketik nama kelas yang dicari di kolom pencarian lalu terapkan.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Daftar menyisakan kelas yang namanya cocok, kelas lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.011</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.011.001</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring kelas berdasarkan tingkat</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Admin menyaring daftar kelas memakai pilihan tingkat.</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada kelas di tingkat yang berbeda.</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Daftar seluruh kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tingkat pada penyaring lalu terapkan.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Daftar menyisakan kelas dari tingkat itu saja.</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.012</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.012.001</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nama kelas (maksimal 20 karakter)</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Nama kelas diisi 20 karakter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama Kelas sepanjang 20 karakter.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>Nama diterima dan muncul pesan "Kelas berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.012</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.012.002</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nama kelas (maksimal 20 karakter)</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Nama kelas diisi 21 karakter, tepat satu karakter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nama Kelas sepanjang 21 karakter.</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>Nama yang diketik tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nama maksimal 20 karakter."</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.013</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.013.001</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan tingkat (10 sampai 12)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>Tingkat diisi 9, tepat satu tingkat di bawah pilihan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih tingkat 9.</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tingkat yang dipilih tidak valid."</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.013</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.013.002</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan tingkat (10 sampai 12)</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>Tingkat diisi 10, tepat di batas bawah pilihan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tingkat 10 lalu isi Nama Kelas.</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>Kedua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>Tingkat diterima dan muncul pesan "Kelas berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.014</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.014.001</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan tingkat (10 sampai 12)</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>Tingkat diisi 12, tepat di batas atas pilihan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tingkat 12 lalu isi Nama Kelas.</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>Kedua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>Tingkat diterima dan muncul pesan "Kelas berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>TS.KEL.014</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>TC.KEL.014.002</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan tingkat (10 sampai 12)</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>Tingkat diisi 13, tepat satu tingkat di atas pilihan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>Buka formulir Tambah Kelas.</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Tambah Kelas tampil.</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih tingkat 13.</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tingkat yang dipilih tidak valid."</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C9:C11"/>
+  <mergeCells count="124">
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="G38:G39"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="F9:F11"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="F15:F18"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="E31:E34"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F57:F59"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B25:B27"/>
     <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G15:G18"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="C42:C44"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="E42:E44"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="F54:F56"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="E28:E30"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G31:G34"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="A25:A27"/>
     <mergeCell ref="E19:E21"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="G19:G21"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -24329,8 +24329,8 @@
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="B19:B23"/>
     <mergeCell ref="B55:B57"/>
+    <mergeCell ref="D55:D57"/>
     <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D55:D57"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="F9:F11"/>
@@ -24362,9 +24362,9 @@
     <mergeCell ref="A6:K7"/>
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="E19:E23"/>
+    <mergeCell ref="E61:E63"/>
     <mergeCell ref="G19:G23"/>
     <mergeCell ref="G55:G57"/>
-    <mergeCell ref="E61:E63"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="E36:E38"/>
     <mergeCell ref="E30:E32"/>
@@ -26463,89 +26463,44 @@
     <mergeCell ref="C51:C53"/>
     <mergeCell ref="C48:C50"/>
     <mergeCell ref="D25:D27"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="B45:B47"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="C28:C30"/>
     <mergeCell ref="C31:C34"/>
     <mergeCell ref="B22:B24"/>
     <mergeCell ref="D22:D24"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="C45:C47"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="E51:E53"/>
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="D15:D18"/>
     <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B44"/>
     <mergeCell ref="C35:C37"/>
     <mergeCell ref="E35:E37"/>
-    <mergeCell ref="D45:D47"/>
     <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="A38:A39"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="C38:C39"/>
     <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="D57:D59"/>
     <mergeCell ref="D38:D39"/>
     <mergeCell ref="F51:F53"/>
-    <mergeCell ref="D57:D59"/>
     <mergeCell ref="G28:G30"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="A40:A41"/>
     <mergeCell ref="C22:C24"/>
-    <mergeCell ref="B28:B30"/>
     <mergeCell ref="A42:A44"/>
-    <mergeCell ref="D28:D30"/>
     <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F22:F24"/>
     <mergeCell ref="F40:F41"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B31:B34"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D31:D34"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="F15:F18"/>
     <mergeCell ref="D42:D44"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="B54:B56"/>
     <mergeCell ref="E22:E24"/>
-    <mergeCell ref="D54:D56"/>
     <mergeCell ref="G22:G24"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="F48:F50"/>
     <mergeCell ref="B35:B37"/>
-    <mergeCell ref="E25:E27"/>
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="D35:D37"/>
-    <mergeCell ref="G25:G27"/>
     <mergeCell ref="E31:E34"/>
     <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="C19:C21"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="E15:E18"/>
@@ -26553,35 +26508,80 @@
     <mergeCell ref="F19:F21"/>
     <mergeCell ref="G15:G18"/>
     <mergeCell ref="E40:E41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="E42:E44"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="E48:E50"/>
-    <mergeCell ref="A48:A50"/>
     <mergeCell ref="F31:F34"/>
     <mergeCell ref="G48:G50"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="A51:A53"/>
     <mergeCell ref="F25:F27"/>
-    <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
-    <mergeCell ref="F54:F56"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A54:A56"/>
-    <mergeCell ref="E28:E30"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G31:G34"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="E19:E21"/>
-    <mergeCell ref="B9:B11"/>
     <mergeCell ref="G19:G21"/>
-    <mergeCell ref="G40:G41"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="F15:F18"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G31:G34"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="G40:G41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26593,7 +26593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -26703,55 +26703,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.WKA.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.WKA.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan konfigurasi waktu absen yang valid</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Menyimpan konfigurasi waktu absen yang sah</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi jam mulai, jam selesai, dan toleransi terlambat yang valid.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengatur jam mulai, jam selesai, toleransi keterlambatan, dan hari aktif dengan benar.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Buka halaman Waktu Absen.</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form konfigurasi tampil.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26765,184 +26765,156 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi jam mulai 06:00, jam selesai 07:00, toleransi 30 menit.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Atur jam mulai 06:00 dan jam selesai 07:00.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Kedua jam terpilih.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Pilih toleransi terlambat 30 menit dan centang hari Senin sampai Jumat.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi dan hari aktif terpilih.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Konfigurasi tersimpan dan tampil pada ringkasan.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Konfigurasi waktu absen berhasil disimpan." beserta ringkasan jam dan toleransi yang baru.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.WKA.002</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.WKA.002.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan waktu absen dengan jam selesai sama dengan jam mulai</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Jam selesai diisi sama persis dengan jam mulai.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Mengatur hari aktif absensi termasuk hari Sabtu</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Admin menambahkan hari Sabtu sebagai hari aktif absensi.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Isi jam mulai dan jam selesai dengan nilai yang sama.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "Jam selesai harus setelah jam mulai", konfigurasi tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.WKA.003</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.WKA.003.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan waktu absen dengan jam selesai sebelum jam mulai</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Jam selesai diisi lebih awal daripada jam mulai.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Isi jam mulai 07:00 dan jam selesai 06:00.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Centang hari Senin sampai Sabtu pada pilihan hari aktif.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Enam hari tercentang.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26956,239 +26928,211 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil, dan ringkasan hari aktif menyebutkan Sabtu.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.003</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.003.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Menyimpan tanpa toleransi keterlambatan</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Admin memilih toleransi 0 menit, sehingga tidak ada zona terlambat.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26.4" customHeight="1" s="9">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Pilih toleransi terlambat 0 menit.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan bahwa tidak ada zona terlambat.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "Jam selesai harus setelah jam mulai", konfigurasi tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil, dan ringkasan menyebutkan toleransi 0 menit.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26.4" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>TS.WKA.004</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>TC.WKA.004.001</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan toleransi terlambat 0 menit</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi 0 menit, salah satu pilihan yang tersedia.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Jam selesai sama dengan jam mulai</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengatur jam selesai persis sama dengan jam mulai.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Pilih toleransi terlambat 0 menit.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Pilihan 0 menit terpilih di kolom toleransi.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26.4" customHeight="1" s="9">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26.4" customHeight="1" s="9">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Konfigurasi tersimpan tanpa zona terlambat.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.WKA.005</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.WKA.005.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan toleransi terlambat di luar pilihan yang tersedia</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi nilai yang bukan salah satu dari 10 pilihan tetap.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Kirim toleransi terlambat = 25 (bukan salah satu opsi).</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Nilai dikirim ke server.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26.4" customHeight="1" s="9">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi pilihan tidak valid, konfigurasi tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26.4" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.WKA.006</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.WKA.006.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan jam di luar rentang 00-23</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Jam mulai diisi nilai di luar rentang 00-23 (misal 24).</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Kirim jam mulai = 24 (di luar pilihan terdaftar).</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Nilai dikirim ke server.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Atur jam mulai dan jam selesai pada jam yang sama.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Kedua jam terpilih sama.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27202,252 +27146,1247 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jam selesai harus setelah jam mulai." dan konfigurasi tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39.6" customHeight="1" s="9">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.005</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.005.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Jam selesai lebih awal dari jam mulai</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengatur jam selesai lebih awal daripada jam mulai.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52.8" customHeight="1" s="9">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Atur jam mulai 08:00 dan jam selesai 07:00.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Kedua jam terpilih.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39.6" customHeight="1" s="9">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi pilihan jam tidak valid, konfigurasi tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="39.6" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jam selesai harus setelah jam mulai." dan konfigurasi tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52.8" customHeight="1" s="9">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.006</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.006.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi melebihi lama waktu absen</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Admin memilih toleransi yang lebih lama daripada rentang waktu absen itu sendiri.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Atur waktu absen 06:00 sampai 07:00, sehingga lamanya 60 menit.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Kedua jam terpilih.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Pilih toleransi terlambat 90 menit.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi terpilih.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Toleransi terlambat tidak boleh lebih besar dari durasi absen."</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>TS.WKA.007</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>TC.WKA.007.001</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Batas toleransi terlambat sama dengan durasi absen (boundary tepat sama)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Tidak memilih satu pun hari aktif</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Admin membuang semua centang pada pilihan hari aktif absensi.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Buang semua centang pada pilihan hari aktif.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Tidak ada hari yang tercentang.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pilih minimal satu hari aktif absensi." dan konfigurasi tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.008</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.008.001</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Jam yang dipilih di luar rentang yang tersedia</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengirim jam di luar pilihan yang disediakan.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih jam di luar pilihan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pilihan jam atau menit tidak valid."</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.009</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.009.001</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Batas toleransi terhadap lama waktu absen (60 menit)</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi 60 menit, tepat sama dengan durasi absen 60 menit (06:00-07:00).</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi 60 menit, tepat sama dengan lama waktu absen.</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Isi jam mulai 06:00, jam selesai 07:00, toleransi 60 menit.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="52.8" customHeight="1" s="9">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n">
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Waktu absen diatur 06:00 sampai 07:00, sehingga lamanya 60 menit.</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Pilih toleransi terlambat 60 menit.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi terpilih.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Toleransi lolos validasi (tepat sama dengan durasi, batas atas diperbolehkan), konfigurasi tersimpan.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39.6" customHeight="1" s="9">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TS.WKA.008</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>TC.WKA.008.001</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Batas toleransi terlambat melebihi durasi absen (boundary di atas durasi)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.009</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.009.002</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas toleransi terhadap lama waktu absen (60 menit)</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi 90 menit, melebihi durasi absen 60 menit (06:00-07:00).</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi 90 menit, melebihi lama waktu absen.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Isi jam mulai 06:00, jam selesai 07:00, toleransi 90 menit.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="52.8" customHeight="1" s="9">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n">
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Waktu absen diatur 06:00 sampai 07:00, sehingga lamanya 60 menit.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Pilih toleransi terlambat 90 menit.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi terpilih.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "Toleransi terlambat tidak boleh lebih besar dari durasi absen", konfigurasi tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Toleransi terlambat tidak boleh lebih besar dari durasi absen."</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.010</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.010.001</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah toleransi keterlambatan</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi 0 menit, tepat di batas bawah pilihan.</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Pilih toleransi terlambat 0 menit.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi terpilih.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.011</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.011.001</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan jam (00 sampai 23)</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Jam mulai diisi 00, tepat di batas bawah pilihan jam.</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Pilih jam mulai 00.</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>Jam mulai terpilih.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>Jam diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.012</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.012.001</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan jam (00 sampai 23)</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>Jam selesai diisi 23, tepat di batas atas pilihan jam.</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Pilih jam mulai 22 dan jam selesai 23.</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>Kedua jam terpilih.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Jam diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>TS.WKA.012</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>TC.WKA.012.002</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Batas pilihan jam (00 sampai 23)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>Jam diisi 24, tepat satu jam di atas batas atas pilihan.</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Waktu Absen.</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Waktu Absen tampil beserta konfigurasi yang berlaku sekarang.</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>Paksa memilih jam 24.</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>Pilihan tersebut terkirim.</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pilihan jam atau menit tidak valid."</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="C16:C17"/>
+  <mergeCells count="103">
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="G25:G28"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A25:A28"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="B25:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30029,7 +30968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -30062,7 +31001,7 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : Admin &gt; Profil</t>
+          <t>Page : Admin &gt; Profil Admin</t>
         </is>
       </c>
     </row>
@@ -30139,246 +31078,246 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.PAD.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.PAD.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin memperbarui profil dengan data valid</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat halaman profil sendiri</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengubah email dan nomor WhatsApp dengan data valid.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin membuka halaman profilnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Profil.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form profil tampil terisi data lama.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Nama dan email admin tampil di halaman profil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26.4" customHeight="1" s="9">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.002</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.002.001</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Mengganti nama sendiri</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengubah namanya sendiri lewat halaman profil.</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Ubah email dan nomor WhatsApp.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Data baru yang diketik tampil di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Ubah Nama menjadi nama yang baru.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Nama baru tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Profil berhasil diperbarui.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.002</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.002.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Admin memperbarui profil dengan email yang sudah dipakai akun lain</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi email yang sudah dipakai akun lain.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Profil admin berhasil diperbarui." dan nama baru tampil di halaman profil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Mengganti email sendiri</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengubah emailnya. Berbeda dari peran lain, admin tidak perlu kode OTP untuk ini.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada akun lain dengan email tersebut.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Isi email yang sudah dipakai akun lain.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Email yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "Email sudah digunakan", profil tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.003</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.003.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah foto profil dengan format tidak diizinkan</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah foto berformat GIF, yang tidak termasuk format diizinkan.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file foto berformat GIF.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Ubah Email menjadi email yang belum dipakai akun lain.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Email baru tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -30392,513 +31331,429 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil dan email baru tampil di halaman profil.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.004</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.004.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Menyimpan nomor WhatsApp bantuan</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengisi nomor WhatsApp yang dipakai calon pengguna untuk meminta bantuan.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor WhatsApp dengan nomor yang benar.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Nomor tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format foto hanya JPG/JPEG/PNG, profil tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.004</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.004.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Admin memperbarui profil dengan format nomor WhatsApp tidak valid</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil dan nomor tampil di halaman profil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52.8" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.005</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.005.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Email sudah dipakai akun lain</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi nomor WhatsApp mengandung huruf.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Admin memakai email yang sudah dimiliki akun lain.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor WhatsApp dengan huruf (misal "abc-nomor-salah").</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Teks yang diketik tampil di kolom nomor WhatsApp.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada akun lain yang memakai email tersebut.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39.6" customHeight="1" s="9">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Isi Email dengan email yang sudah dipakai akun lain.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Email tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52.8" customHeight="1" s="9">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format nomor WhatsApp tidak valid, profil tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.005</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.005.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Mengisi password di form profil tidak berpengaruh pada password sesungguhnya</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Email sudah digunakan." dan perubahan tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39.6" customHeight="1" s="9">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.006</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.006.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Nomor WhatsApp diisi mengandung huruf</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengisi nomor WhatsApp memakai huruf.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor WhatsApp dengan teks yang mengandung huruf.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Teks tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39.6" customHeight="1" s="9">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Format nomor WhatsApp tidak valid."</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39.6" customHeight="1" s="9">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.007</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.007.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah foto profil bertipe yang diizinkan</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi field password pada form edit profil (bukan alur ganti sandi resmi).</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah foto berkas gambar JPG.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Validasi field password ada di request, namun tidak pernah dipakai controller (dead validation).</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Isi field password pada form edit profil.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Password yang diketik tampil masked di kolom, lolos validasi format.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.8" customHeight="1" s="9">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Profil tersimpan, namun password login tetap tidak berubah (field diabaikan sepenuhnya oleh sistem).</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39.6" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.006</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.006.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Admin meminta OTP untuk ganti sandi</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Admin memulai alur ganti sandi resmi lewat OTP.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Ganti Sandi pada halaman profil.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Sistem mengirim kode OTP ke email, admin diarahkan ke halaman verifikasi OTP.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52.8" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.007</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.007.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Submit sandi baru tanpa sesi OTP terverifikasi</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengakses langsung endpoint set sandi baru tanpa melalui verifikasi OTP.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Sesi password_change_verified belum ada.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung endpoint set sandi baru dengan mengirim password baru.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Sesi verifikasi tidak ditemukan, admin diarahkan kembali ke halaman profil, password tidak berubah.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="39.6" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.008</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.008.001</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Submit sandi baru dengan sesi OTP terverifikasi</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah lolos verifikasi OTP lalu mengatur sandi baru yang valid.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Sesi password_change_verified sudah aktif.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Isi sandi baru dan konfirmasi yang sama dan valid.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Sandi baru dan konfirmasi yang diketik tampil masked di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Sandi berhasil diubah, admin diarahkan ke halaman profil.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39.6" customHeight="1" s="9">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.009</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.009.001</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Submit sandi baru dengan konfirmasi tidak cocok</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi sandi baru dan konfirmasi sandi yang berbeda.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Sesi password_change_verified sudah aktif.</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Isi sandi baru dan konfirmasi yang berbeda.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Sandi baru dan konfirmasi yang diketik tampil masked di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="39.6" customHeight="1" s="9">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "Konfirmasi kata sandi tidak sesuai", sandi tidak berubah.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.010</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.010.001</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum nomor WhatsApp (boundary di bawah 10 karakter)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Nomor WhatsApp diisi 9 karakter — tepat di bawah batas minimum 10.</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor WhatsApp 9 digit.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas gambar JPG sebagai foto profil.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom foto.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -30912,321 +31767,293 @@
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil dan foto profil terpasang.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26.4" customHeight="1" s="9">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.008</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.008.001</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah foto profil bertipe yang tidak diizinkan</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas yang bukan gambar.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26.4" customHeight="1" s="9">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang bukan gambar sebagai foto profil.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom foto.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26.4" customHeight="1" s="9">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nomor minimal 10 digit, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26.4" customHeight="1" s="9">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.011</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.011.001</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum nomor WhatsApp (boundary tepat 10 karakter)</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Foto harus berupa gambar." dan foto tidak terpasang.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26.4" customHeight="1" s="9">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.009</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.009.001</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Meminta penggantian kata sandi</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Nomor WhatsApp diisi tepat 10 karakter — tepat di batas minimum.</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Admin meminta ganti kata sandi; sistem mengirim kode OTP ke emailnya lebih dulu.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Ganti Kata Sandi dari profil.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Ganti Kata Sandi tampil beserta email yang akan dikirimi kode.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol kirim kode.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Kode OTP telah dikirim ke email Anda." dan halaman Verifikasi OTP tampil.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="39.6" customHeight="1" s="9">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.010</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.010.001</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor WhatsApp (minimal 10 karakter)</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Nomor WhatsApp diisi 9 digit, tepat satu digit di bawah batas minimum.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor WhatsApp tepat 10 digit.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26.4" customHeight="1" s="9">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n">
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="39.6" customHeight="1" s="9">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Nomor lolos validasi minimum, tersimpan.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26.4" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.012</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.012.001</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nomor WhatsApp (boundary tepat 20 karakter)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Nomor WhatsApp diisi tepat 20 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor WhatsApp tepat 20 digit.</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26.4" customHeight="1" s="9">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>Nomor lolos validasi maksimum, tersimpan.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.013</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.013.001</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nomor WhatsApp (boundary di atas 20 karakter)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Nomor WhatsApp diisi 21 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor WhatsApp 21 digit.</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="39.6" customHeight="1" s="9">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nomor melebihi batas maksimum, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="39.6" customHeight="1" s="9">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.014</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.014.001</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum sandi baru (boundary di bawah 8 karakter)</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Sandi baru diisi 7 karakter — tepat di bawah batas minimum 8.</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Sesi password_change_verified sudah aktif.</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>Isi sandi baru 7 karakter dan konfirmasi yang sama.</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>Sandi baru dan konfirmasi yang diketik tampil masked di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor WhatsApp sepanjang 9 digit.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Nomor tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -31240,239 +32067,211 @@
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nomor WhatsApp minimal 10 digit."</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="39.6" customHeight="1" s="9">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.010</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.010.002</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor WhatsApp (minimal 10 karakter)</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Nomor WhatsApp diisi 10 digit, tepat di batas minimum.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26.4" customHeight="1" s="9">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor WhatsApp sepanjang 10 digit.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Nomor tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26.4" customHeight="1" s="9">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J35" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi sandi minimal 8 karakter, tidak berubah.</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="39.6" customHeight="1" s="9">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.015</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.015.001</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang minimum sandi baru (boundary tepat 8 karakter)</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Nomor diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26.4" customHeight="1" s="9">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.011</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.011.001</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor WhatsApp (maksimal 20 karakter)</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Sandi baru diisi tepat 8 karakter — tepat di batas minimum.</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Nomor WhatsApp diisi 20 karakter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Sesi password_change_verified sudah aktif.</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>Isi sandi baru tepat 8 karakter dan konfirmasi yang sama.</t>
-        </is>
-      </c>
-      <c r="J36" s="15" t="inlineStr">
-        <is>
-          <t>Sandi baru dan konfirmasi yang diketik tampil masked di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26.4" customHeight="1" s="9">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8" t="n">
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26.4" customHeight="1" s="9">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>Sandi lolos validasi minimum, berhasil diubah.</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26.4" customHeight="1" s="9">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.016</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.016.001</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran foto profil (boundary tepat 2048 KB)</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Foto profil berukuran tepat 2048 KB — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>Pilih foto berukuran tepat 2048 KB.</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26.4" customHeight="1" s="9">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>Ukuran foto lolos validasi maksimum, tersimpan.</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="26.4" customHeight="1" s="9">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>TS.PAD.017</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>TC.PAD.017.001</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran foto profil (boundary di atas 2048 KB)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Foto profil berukuran 1 byte di atas 2048 KB — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>Pilih foto berukuran melebihi 2048 KB.</t>
-        </is>
-      </c>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor WhatsApp sepanjang 20 karakter.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Nomor tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -31486,137 +32285,457 @@
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Nomor diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.011</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.011.002</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang nomor WhatsApp (maksimal 20 karakter)</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Nomor WhatsApp diisi 21 karakter, tepat satu karakter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Isi Nomor WhatsApp sepanjang 21 karakter.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Nomor tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J41" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi ukuran foto melebihi maksimum, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nomor WhatsApp maksimal 20 karakter."</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.012</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.012.001</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran foto profil (maksimal 2 MB)</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Foto berukuran tepat 2 MB, di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas gambar berukuran tepat 2 MB.</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom foto.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>Foto diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>TS.PAD.012</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>TC.PAD.012.002</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran foto profil (maksimal 2 MB)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>Foto berukuran sedikit di atas 2 MB, melewati batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Profil Admin lalu klik Edit.</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>Formulir Edit Profil tampil berisi data admin yang sekarang.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas gambar berukuran lebih dari 2 MB.</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom foto.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Ukuran foto maksimal 2 MB." dan foto tidak terpasang.</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="G12:G13"/>
+  <mergeCells count="103">
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="G28:G30"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F19:F21"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="F25:F27"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -28301,8 +28301,8 @@
     <mergeCell ref="B22:B24"/>
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="A41:A43"/>
+    <mergeCell ref="C41:C43"/>
     <mergeCell ref="E25:E28"/>
-    <mergeCell ref="C41:C43"/>
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="G25:G28"/>
     <mergeCell ref="C35:C37"/>
@@ -28398,7 +28398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -28438,7 +28438,7 @@
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis, State Transition Testing</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -28508,55 +28508,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.LKA.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.LKA.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file KML yang valid</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah berkas area absensi</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file KML berisi polygon area absen yang valid.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas area sekolah yang digambar di Google My Maps.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk dan sudah punya berkas area sekolah.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Buka halaman Lokasi Absen.</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form unggah KML tampil.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -28570,20 +28570,20 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file KML dengan polygon minimal 3 titik.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas area sekolah yang akan diunggah.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -28597,376 +28597,320 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Area absen berhasil diimpor dan koordinat tersimpan.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Area absensi berhasil diimpor." dan area sekolah tampil di peta.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>TS.LKA.002</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>TC.LKA.002.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file dengan format bukan KML</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah berkas yang bukan berkas area</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file berisi teks biasa, bukan format KML/XML.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas gambar, bukan berkas area.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file berisi teks biasa (bukan XML/KML).</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "File harus berformat KML", area tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas gambar sebagai berkas area.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File harus berformat KML." dan area tidak berubah.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.4" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>TS.LKA.003</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TC.LKA.003.001</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Admin submit form tanpa memilih file</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Berkas area tidak memuat gambar area</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Admin klik Impor tanpa memilih file KML sama sekali.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Berkas yang diunggah hanya berisi titik, bukan gambar area.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor tanpa memilih file.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi "File KML wajib diunggah", area tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26.4" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas area yang hanya berisi titik.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa area tidak ditemukan di dalam berkas, beserta arahan untuk menggambar area di Google My Maps.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>TS.LKA.004</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>TC.LKA.004.001</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengatur toleransi jarak dalam rentang valid</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi toleransi jarak 50 meter, dalam rentang 0-500.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Berkas area yang titiknya kurang dari tiga</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Area di dalam berkas hanya digambar dengan dua titik, sehingga tidak membentuk bidang.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Isi toleransi jarak 50 meter.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom toleransi.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8" t="n">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26.4" customHeight="1" s="9">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Toleransi jarak berhasil disimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.005</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.005.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Admin menghapus lokasi absen yang tersimpan</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Admin menghapus data area geofence dan toleransi yang sudah tersimpan.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Area geofence dan toleransi sudah tersimpan.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus Lokasi.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Data geofence dikosongkan dan toleransi direset ke 0.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26.4" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.006</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.006.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran file KML (boundary tepat 5120 KB)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>File KML berukuran tepat 5120 KB — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file KML valid berukuran tepat 5120 KB.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas area yang hanya punya dua titik.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -28980,239 +28924,211 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa area harus punya minimal 3 titik.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.005</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.005.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Menyimpan toleransi jarak</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Admin memberi kelonggaran jarak agar siswa yang sedikit di luar garis area tetap bisa absen.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39.6" customHeight="1" s="9">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Ukuran file lolos validasi maksimum, area berhasil diimpor.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.007</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.007.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran file KML (boundary di atas 5120 KB)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Isi toleransi jarak dengan angka meter yang diinginkan.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Angka tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol simpan toleransi.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Toleransi jarak berhasil disimpan."</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26.4" customHeight="1" s="9">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.006</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.006.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi jarak diisi bukan angka</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>File KML berukuran 1 byte di atas 5120 KB — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengisi toleransi jarak memakai huruf.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file KML berukuran melebihi 5120 KB.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="39.6" customHeight="1" s="9">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26.4" customHeight="1" s="9">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi ukuran file melebihi maksimum, area tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.008</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.008.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah toleransi jarak (boundary di bawah 0 meter)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi -1 — tepat di bawah batas minimum 0.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Isi toleransi jarak -1.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom toleransi.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26.4" customHeight="1" s="9">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi toleransi minimal 0 meter, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.009</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.009.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah toleransi jarak (boundary tepat 0 meter)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi tepat 0 — tepat di batas minimum.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Isi toleransi jarak 0.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom toleransi.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Isi toleransi jarak dengan teks yang bukan angka.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Teks tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -29226,540 +29142,1001 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol simpan toleransi.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Toleransi harus berupa angka."</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26.4" customHeight="1" s="9">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.007</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.007.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus area absensi</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Admin menghapus area absensi yang sudah terpasang.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Area absensi sudah terpasang.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tampil beserta area yang sedang terpasang.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26.4" customHeight="1" s="9">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Toleransi lolos validasi minimum, tersimpan.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26.4" customHeight="1" s="9">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol hapus area lalu setujui konfirmasi.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Kotak konfirmasi tampil dan disetujui.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26.4" customHeight="1" s="9">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Tunggu halaman selesai dimuat.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Lokasi absen berhasil dihapus." dan area tidak lagi terpasang.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39.6" customHeight="1" s="9">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.008</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.008.001</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas toleransi jarak (0 sampai 500 meter)</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi -1 meter, tepat satu meter di bawah batas minimum.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39.6" customHeight="1" s="9">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Isi toleransi jarak dengan -1.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Angka tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="39.6" customHeight="1" s="9">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol simpan toleransi.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Toleransi minimal 0 meter."</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26.4" customHeight="1" s="9">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.008</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.008.002</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Batas toleransi jarak (0 sampai 500 meter)</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi 0 meter, tepat di batas minimum.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="66" customHeight="1" s="9">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Isi toleransi jarak dengan 0.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Angka tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26.4" customHeight="1" s="9">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol simpan toleransi.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.009</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.009.001</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas toleransi jarak (0 sampai 500 meter)</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi 500 meter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Isi toleransi jarak dengan 500.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Angka tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol simpan toleransi.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Toleransi diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.009</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.009.002</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Batas toleransi jarak (0 sampai 500 meter)</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Toleransi diisi 501 meter, tepat satu meter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Isi toleransi jarak dengan 501.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Angka tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol simpan toleransi.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Toleransi maksimal 500 meter."</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>TS.LKA.010</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>TC.LKA.010.001</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas toleransi jarak (boundary tepat 500 meter)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Batas jumlah titik area (minimal 3 titik)</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Area digambar dengan 2 titik, tepat satu titik di bawah jumlah minimum.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas area yang digambar dengan 2 titik.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa area harus punya minimal 3 titik.</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>TS.LKA.010</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>TC.LKA.010.002</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Batas jumlah titik area (minimal 3 titik)</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi tepat 500 — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Area digambar dengan 3 titik, tepat di jumlah minimum.</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n">
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Isi toleransi jarak 500.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom toleransi.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26.4" customHeight="1" s="9">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8" t="n">
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>Toleransi lolos validasi maksimum, tersimpan.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26.4" customHeight="1" s="9">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas area yang digambar dengan 3 titik.</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>Area diterima dan muncul pesan "Area absensi berhasil diimpor."</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>TS.LKA.011</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>TC.LKA.011.001</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas toleransi jarak (boundary di atas 500 meter)</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas area (maksimal 5 MB)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Toleransi diisi 501 — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>Berkas area berukuran lebih dari 5 MB, melewati batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="n">
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Isi toleransi jarak 501.</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom toleransi.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="39.6" customHeight="1" s="9">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="8" t="n">
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Lokasi Absen.</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Lokasi Absen tampil.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi toleransi maksimal 500 meter, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="39.6" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.012</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.012.001</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Transisi state Kosong ke Tersimpan setelah unggah KML valid</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi belum ada area (Kosong), admin mengunggah KML valid.</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Belum ada data geofence tersimpan (state Kosong).</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Unggah file KML valid.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>State berpindah menjadi Tersimpan, koordinat area tersedia.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="39.6" customHeight="1" s="9">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.013</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.013.001</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>State tetap Tersimpan dan data digantikan saat unggah ulang</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi sudah Tersimpan, admin mengunggah KML baru.</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>State sudah Tersimpan dengan data area sebelumnya.</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Unggah file KML baru yang valid.</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>State tetap Tersimpan, tapi data koordinat digantikan dengan yang baru.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26.4" customHeight="1" s="9">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.014</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.014.001</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Transisi state Tersimpan ke Kosong setelah hapus</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi Tersimpan, admin menghapus lokasi absen.</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>State sudah Tersimpan.</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Klik Hapus Lokasi.</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>State berpindah menjadi Kosong, toleransi jarak ikut direset ke 0.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="66" customHeight="1" s="9">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.015</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.015.001</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Set toleransi sebelum ada area tetap Kosong tapi toleransi tersimpan</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi Kosong, admin mengatur toleransi jarak sebelum mengunggah KML.</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>State masih Kosong, belum pernah unggah KML.</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>Isi dan simpan toleransi jarak.</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>State tetap Kosong (belum ada polygon), namun nilai toleransi tetap tersimpan — perilaku apa adanya, didokumentasikan sebagai catatan sistem.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26.4" customHeight="1" s="9">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TS.LKA.016</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>TC.LKA.016.001</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Hapus lokasi saat kondisi masih Kosong tetap aman</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi Kosong (belum ada apa pun), admin klik Hapus Lokasi.</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>State masih Kosong.</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>Klik Hapus Lokasi.</t>
-        </is>
-      </c>
-      <c r="J35" s="15" t="inlineStr">
-        <is>
-          <t>State tetap Kosong, tidak terjadi error (no-op aman).</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas area berukuran lebih dari 5 MB.</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Nama berkas tampil pada kolom unggah.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol unggah.</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File maksimal 5 MB." dan area tidak berubah.</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="G19:G20"/>
+  <mergeCells count="103">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B36:B38"/>
     <mergeCell ref="D9:D11"/>
-    <mergeCell ref="B23:B24"/>
     <mergeCell ref="F9:F11"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="D30:D32"/>
     <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="E42:E44"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F30:F32"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B27:B29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="D48:D50"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G33:G35"/>
     <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29772,7 +30149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -29805,14 +30182,14 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : Admin &gt; Pengaturan &gt; WhatsApp API</t>
+          <t>Page : Admin &gt; Pengaturan &gt; WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis, State Transition Testing</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -29882,55 +30259,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.WAP.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.WAP.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin menyimpan token Fonnte baru</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Menyimpan token layanan pengirim WhatsApp</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengisi token Fonnte baru dan menyimpannya.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin menyimpan token layanan yang dipakai sekolah untuk mengirim WhatsApp.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman WhatsApp API.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form konfigurasi token tampil.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -29944,20 +30321,20 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi token Fonnte yang valid.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Token yang diketik tampil masked di kolom.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Isi kolom token dengan token layanan yang sah.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Token tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -29971,75 +30348,75 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Token tersimpan, ringkasan token termasking tampil.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Konfigurasi WhatsApp berhasil disimpan."</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>TS.WAP.002</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>TC.WAP.002.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Mengirim pesan uji tanpa token yang dikonfigurasi</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengirim pesan uji WhatsApp padahal token belum diisi sama sekali.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus token yang tersimpan</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Admin menghapus token yang sudah tersimpan.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte belum pernah dikonfigurasi.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Token layanan sudah tersimpan.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor dan pesan uji.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Nomor dan pesan yang diketik tampil di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -30053,267 +30430,211 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Kirim Uji.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan error "Token Fonnte belum dikonfigurasi", pesan gagal dikirim.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Pilih pilihan hapus token lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil dan token tidak lagi terpasang.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="66" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>TS.WAP.003</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>TC.WAP.003.001</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Pengiriman uji ke nomor yang sama dalam 60 detik terkena batas laju</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim pesan uji setelah token dipasang</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengirim pesan uji untuk memastikan pengiriman berjalan.</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Token layanan sudah terpasang.</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Isi nomor tujuan dan isi pesan uji.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Kedua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol kirim pesan uji.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan bahwa pesan berhasil dikirim.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26.4" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.004</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.004.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim pesan uji tanpa token</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengirim pesan uji dua kali ke nomor yang sama dalam waktu kurang dari 60 detik.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Admin mencoba mengirim pesan uji padahal token belum dipasang.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte sudah dikonfigurasi.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Token layanan belum dipasang.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pesan uji pertama ke suatu nomor, lalu kirim pesan uji kedua ke nomor yang sama sebelum 60 detik berlalu.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Pesan pertama berhasil terkirim; permintaan kedua ditolak dengan pesan "Nomor ini baru saja dipakai untuk test" (429).</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.004</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.004.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Kegagalan koneksi ke penyedia dilaporkan sebagai error</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Koneksi ke Fonnte gagal (timeout) saat mengirim pesan uji.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte sudah dikonfigurasi; koneksi ke server Fonnte gagal.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pesan uji WhatsApp.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Koneksi ke Fonnte timeout atau tidak bisa dijangkau", status gagal.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.005</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.005.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum token (boundary tepat 255 karakter)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Token diisi tepat 255 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Isi token dengan tepat 255 karakter.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil masked di kolom token.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26.4" customHeight="1" s="9">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Token lolos validasi maksimum, tersimpan.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.006</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.006.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum token (boundary di atas 255 karakter)</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Token diisi 256 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Isi token dengan 256 karakter.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil masked di kolom token.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Isi nomor tujuan dan isi pesan uji.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Kedua kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -30327,75 +30648,75 @@
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi token melebihi batas maksimum, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="H19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol kirim pesan uji.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan bahwa token belum dikonfigurasi, dan pesan tidak dikirim.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26.4" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.007</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.007.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nomor pesan uji (boundary tepat 20 karakter)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Nomor pesan uji diisi tepat 20 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte sudah dikonfigurasi.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.005</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.005.001</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim pesan uji berkali-kali ke nomor yang sama</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengirim pesan uji dua kali berturut-turut ke nomor yang sama dalam waktu singkat.</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Token layanan sudah terpasang.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor dengan tepat 20 karakter.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom nomor.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Kirim pesan uji ke sebuah nomor.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Pesan uji pertama berhasil dikirim.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -30409,554 +30730,764 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Kirim Uji.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Nomor lolos validasi maksimum, pesan diproses.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Segera kirim pesan uji lagi ke nomor yang sama.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan bahwa nomor itu baru saja dipakai dan harus menunggu sebelum mengirim ulang.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.006</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.006.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Melihat riwayat pesan yang pernah dikirim</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Admin membuka riwayat pengiriman pesan WhatsApp.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada pesan yang pernah dikirim.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Pengiriman Pesan dari halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Daftar pesan tampil beserta nama penerima dan status pengirimannya.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39.6" customHeight="1" s="9">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.007</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.007.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim ulang pesan dari riwayat</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengirim ulang pesan yang sebelumnya gagal terkirim.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada pesan yang gagal terkirim, dan token layanan terpasang.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Pengiriman Pesan.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Daftar pesan tampil.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26.4" customHeight="1" s="9">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Kirim Ulang pada pesan yang dituju.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pesan sedang diproses ulang."</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26.4" customHeight="1" s="9">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>TS.WAP.008</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>TC.WAP.008.001</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nomor pesan uji (boundary di atas 20 karakter)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring riwayat pesan berdasarkan status</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Admin menyaring riwayat agar hanya pesan gagal yang tampil.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada pesan yang berhasil dan yang gagal.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Riwayat Pengiriman Pesan.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Daftar seluruh pesan tampil.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26.4" customHeight="1" s="9">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih status Gagal pada penyaring lalu terapkan.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Daftar menyisakan pesan yang gagal saja.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39.6" customHeight="1" s="9">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.009</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.009.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang token (maksimal 255 karakter)</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Token diisi 255 karakter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="39.6" customHeight="1" s="9">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Isi token sepanjang 255 karakter.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Token tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="39.6" customHeight="1" s="9">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Token diterima dan muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39.6" customHeight="1" s="9">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.009</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.009.002</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang token (maksimal 255 karakter)</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Nomor pesan uji diisi 21 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Token diisi 256 karakter, tepat satu karakter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte sudah dikonfigurasi.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Isi nomor dengan 21 karakter.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom nomor.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39.6" customHeight="1" s="9">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n">
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39.6" customHeight="1" s="9">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Kirim Uji.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nomor melebihi batas maksimum, pesan gagal diproses.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26.4" customHeight="1" s="9">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.009</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.009.001</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum isi pesan uji (boundary tepat 500 karakter)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Isi token sepanjang 256 karakter.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Token tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Simpan.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa token tidak boleh lebih dari 255 karakter.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TS.WAP.010</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.010.001</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang pesan uji (maksimal 500 karakter)</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Isi pesan diisi tepat 500 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Pesan uji diisi 500 karakter, tepat di batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte sudah dikonfigurasi.</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Token layanan sudah terpasang.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Isi pesan dengan tepat 500 karakter.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Teks yang diketik tampil di kolom pesan.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n">
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Kirim Uji.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Pesan lolos validasi maksimum, diproses.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Isi pesan uji sepanjang 500 karakter.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Pesan tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol kirim pesan uji.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Pesan diterima dan muncul keterangan berhasil dikirim.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>TS.WAP.010</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.010.001</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum isi pesan uji (boundary di atas 500 karakter)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.WAP.010.002</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang pesan uji (maksimal 500 karakter)</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Isi pesan diisi 501 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Pesan uji diisi 501 karakter, tepat satu karakter di atas batas maksimum.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte sudah dikonfigurasi.</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Token layanan sudah terpasang.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Isi pesan dengan 501 karakter.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Teks yang diketik tampil di kolom pesan.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="39.6" customHeight="1" s="9">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n">
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman WhatsApp.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman WhatsApp tampil.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Kirim Uji.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi pesan melebihi batas maksimum, gagal diproses.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="39.6" customHeight="1" s="9">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.011</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.011.001</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Transisi state TokenKosong ke TokenTersimpan setelah menyimpan</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi belum ada token (TokenKosong), admin menyimpan token baru.</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Token Fonnte belum pernah diisi (state TokenKosong).</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Isi dan simpan token baru.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>State berpindah menjadi TokenTersimpan.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="39.6" customHeight="1" s="9">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.012</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.012.001</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>State tetap TokenTersimpan saat submit kosong tanpa centang hapus</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi TokenTersimpan, admin submit form dengan token dikosongkan tapi tidak mencentang hapus token.</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>State sudah TokenTersimpan.</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Submit form dengan field token kosong dan checkbox hapus tidak dicentang.</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>State tetap TokenTersimpan, token lama tidak berubah (no-op).</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="39.6" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.013</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.013.001</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Transisi state TokenTersimpan ke TokenKosong saat centang hapus</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi TokenTersimpan, admin mencentang opsi hapus token.</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>State sudah TokenTersimpan.</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Centang opsi hapus token dan submit.</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>State berpindah menjadi TokenKosong.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="39.6" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TS.WAP.014</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>TC.WAP.014.001</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>State tetap TokenKosong saat submit kosong tanpa token sama sekali</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi TokenKosong, admin submit form dengan token tetap dikosongkan.</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>State masih TokenKosong, belum pernah ada token tersimpan.</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Submit form dengan field token kosong.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>State tetap TokenKosong (cabang overwrite eksplisit dengan nilai kosong).</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Isi pesan uji sepanjang 501 karakter.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Pesan tampil di kolomnya.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol kirim pesan uji.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Pesan maksimal 500 karakter." dan pesan tidak dikirim.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A24:A25"/>
+  <mergeCells count="82">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A17:A19"/>
     <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C17:C19"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E23:E24"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B36:B38"/>
     <mergeCell ref="D9:D11"/>
+    <mergeCell ref="B23:B24"/>
     <mergeCell ref="F9:F11"/>
+    <mergeCell ref="D30:D32"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="F26:F27"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="D12:D13"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
     <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B24:B25"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="E9:E11"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -1689,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -1722,14 +1722,14 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : Admin &gt; Data Siswa &gt; Impor</t>
+          <t>Page : Admin &gt; Data Siswa &gt; Impor Siswa</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -1799,137 +1799,109 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file xlsx valid lalu mengimpor siswa baru</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mengimpor siswa dari berkas yang benar</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah template xlsx berisi baris siswa yang lengkap dan valid, lalu menjalankan impor.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas berisi data siswa yang benar, meninjaunya, lalu menyetujui impor.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk dan sudah menyusun berkas dari templat.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Impor Siswa, unggah file xlsx sesuai template.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>File diterima, diarahkan ke halaman pratinjau berisi baris yang akan diimpor.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Siswa baru tersimpan sesuai data pada file, diarahkan ke daftar siswa.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas impor lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil berisi daftar siswa yang akan diimpor.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.IMS.002</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.IMS.002.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file dengan format bukan xlsx/xls</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file PDF sebagai file impor siswa.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file berformat PDF pada form unggah impor siswa.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Periksa isi tinjauan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Nama-nama siswa dari berkas tampil di daftar tinjauan.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1943,431 +1915,824 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Impor berhasil!" beserta jumlah siswa baru yang dibuat, dan nama siswa tampil di daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.IMS.002</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.IMS.002.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Mengimpor siswa sekaligus menempatkannya ke kelas</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Berkas impor memuat kolom kelas, sehingga siswa langsung menjadi anggota kelas itu.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kelas yang dituju sudah ada.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1" s="9">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Unggah.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format file harus xlsx/xls, file tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas impor yang kolom kelasnya terisi, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52.8" customHeight="1" s="9">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52.8" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Siswa lalu saring berdasarkan tingkat kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Siswa yang diimpor tampil sebagai anggota kelas itu.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.003</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.003.001</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Admin submit unggah impor siswa tanpa memilih file</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah berkas yang bukan berkas Excel</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Admin klik Unggah tanpa memilih file sama sekali.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas teks biasa, bukan berkas Excel.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Unggah tanpa memilih file.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi file wajib diisi, tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="66" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang bukan Excel lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File harus bertipe: xlsx, xls." dan impor tidak dilanjutkan.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52.8" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.004</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.004.001</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan nama kosong dilewati saat impor siswa</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan kolom Nama kosong.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Baris tanpa nama dilewati</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Berkas memuat satu baris tanpa nama; baris itu dilewati, baris lain tetap diimpor.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>File sudah diunggah dan masuk tahap pratinjau, salah satu baris bernama kosong.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Baris bernama kosong dilewati dan dicatat sebagai error "Nama kosong", tidak ada siswa yang tersimpan dari baris ini; baris valid lainnya tetap tersimpan.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52.8" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang salah satu barisnya tidak berisi nama, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil, jumlah siswa yang dibuat tidak menghitung baris bermasalah, dan rincian baris yang dilewati menyebutkan "Nama kosong".</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.005</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.005.001</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan NISN kosong dilewati saat impor siswa</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan kolom NISN kosong.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Baris tanpa NISN dilewati</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Berkas memuat baris yang tidak berisi NISN; baris itu dilewati.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>File sudah diunggah dan masuk tahap pratinjau, salah satu baris ber-NISN kosong.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Baris ber-NISN kosong dilewati dan dicatat sebagai error "NISN kosong", tidak ada siswa yang tersimpan dari baris ini.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52.8" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang salah satu barisnya tidak berisi NISN, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Rincian baris yang dilewati menyebutkan "NISN kosong".</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.006</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.006.001</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan NIS kosong dilewati saat impor siswa</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan kolom NIS kosong.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Baris yang NIS-nya mengandung huruf dilewati</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>NIS hanya boleh berisi angka; baris yang memakai huruf dilewati.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>File sudah diunggah dan masuk tahap pratinjau, salah satu baris ber-NIS kosong.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Baris ber-NIS kosong dilewati dan dicatat sebagai error "NIS kosong", tidak ada siswa yang tersimpan dari baris ini.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang NIS-nya mengandung huruf, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Rincian baris yang dilewati menyebutkan bahwa NIS harus berupa angka.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.007</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.007.001</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan NISN yang sudah ada dianggap data lama, bukan duplikat baru</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Siswa yang NISN-nya sudah ada tidak dibuat ulang</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan NISN yang sudah dipakai siswa yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Berkas memuat siswa yang datanya sudah ada; siswa itu tidak dibuat dua kali.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada siswa dengan NISN tersebut di database.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada siswa dengan NISN tersebut.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Data profil siswa yang sudah ada diperbarui (NIS/kelas), tidak membuat akun siswa baru/duplikat.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang memuat siswa yang sudah ada, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil, dan jumlah siswa baru yang dibuat tetap nol.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>TS.IMS.008</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>TC.IMS.008.001</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Impor siswa otomatis membuat kelas yang belum ada</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh templat berkas impor</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan nama kelas yang belum terdaftar di sistem.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunduh templat agar susunan kolomnya benar.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Kelas pada baris tersebut belum ada di database.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Kelas baru otomatis tercipta dan siswa terhubung ke kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.8" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.IMS.009</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.IMS.009.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Akses halaman pratinjau impor siswa tanpa mengunggah file terlebih dahulu</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengakses langsung halaman pratinjau tanpa proses unggah file.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Belum ada file yang diunggah pada sesi berjalan.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung halaman pratinjau impor siswa.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Admin diarahkan kembali ke halaman impor siswa karena tidak ada file pada sesi.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Siswa.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Siswa tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Berkas templat impor siswa terunduh.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
+  <mergeCells count="61">
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="F28:F30"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="F25:F27"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="D9:D12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G28:G30"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2379,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -2412,14 +2777,14 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : Admin &gt; Data Guru &gt; Impor</t>
+          <t>Page : Admin &gt; Data Guru &gt; Impor Guru</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -2489,137 +2854,109 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.IMG.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.IMG.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file xlsx valid lalu mengimpor guru baru</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mengimpor guru dari berkas yang benar</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah template xlsx format baru (kolom Tipe) berisi baris guru yang lengkap dan valid, lalu menjalankan impor.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas berisi data guru yang benar, meninjaunya, lalu menyetujui impor.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk dan sudah menyusun berkas dari templat.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Impor Guru, unggah file xlsx sesuai template.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>File diterima, diarahkan ke halaman pratinjau berisi baris yang akan diimpor.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52.8" customHeight="1" s="9">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Guru baru tersimpan dengan peran sesuai kolom Tipe (Wali Kelas/BK/Kesiswaan), diarahkan ke daftar guru.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas impor lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil berisi daftar guru yang akan diimpor.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.IMG.002</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.IMG.002.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file dengan format bukan xlsx/xls</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengunggah file PDF sebagai file impor guru.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Pilih file berformat PDF pada form unggah impor guru.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Nama file yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Periksa isi tinjauan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Nama-nama guru dari berkas tampil di daftar tinjauan.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2633,465 +2970,708 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Impor berhasil!" beserta jumlah guru baru yang dibuat, dan nama guru tampil di daftar guru.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.IMG.002</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.IMG.002.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Guru yang diimpor sebagai wali kelas langsung dipasang ke kelasnya</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Berkas memuat kolom kelas, sehingga guru langsung menjadi wali kelas di kelas itu.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kelas yang dituju sudah ada.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.8" customHeight="1" s="9">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Unggah.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format file harus xlsx/xls, file tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang kolom kelasnya terisi, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1" s="9">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Kelas.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Guru yang diimpor tampil sebagai wali kelas di kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52.8" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>TS.IMG.003</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>TC.IMG.003.001</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Admin submit unggah impor guru tanpa memilih file</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah berkas yang bukan berkas Excel</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Admin klik Unggah tanpa memilih file sama sekali.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunggah berkas teks biasa, bukan berkas Excel.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Admin sudah login.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Unggah tanpa memilih file.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi file wajib diisi, tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52.8" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang bukan Excel lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File harus bertipe: xlsx, xls." dan impor tidak dilanjutkan.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>TS.IMG.004</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>TC.IMG.004.001</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan nama kosong dilewati saat impor guru</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan kolom Nama kosong.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Baris guru tanpa nama dilewati</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Berkas memuat satu baris tanpa nama; baris itu dilewati, baris lain tetap diimpor.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>File sudah diunggah dan masuk tahap pratinjau, salah satu baris bernama kosong.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Baris bernama kosong dilewati dan dicatat sebagai error "Nama kosong", tidak ada guru yang tersimpan dari baris ini.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="66" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52.8" customHeight="1" s="9">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang salah satu barisnya tidak berisi nama, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil, dan rincian baris yang dilewati menyebutkan "Nama kosong".</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>TS.IMG.005</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>TC.IMG.005.001</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan NIP kosong dilewati saat impor guru</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan kolom NIP kosong.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Baris guru tanpa NIP dilewati</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Guru tanpa NIP tidak bisa diimpor otomatis dan harus didaftarkan admin secara manual.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>File sudah diunggah dan masuk tahap pratinjau, salah satu baris ber-NIP kosong.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Baris ber-NIP kosong dilewati dan dicatat sebagai error "NIP kosong, guru harus didaftarkan manual oleh admin", tidak ada guru yang tersimpan dari baris ini.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang salah satu barisnya tidak berisi NIP, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Rincian baris yang dilewati menyebutkan bahwa guru tanpa NIP harus didaftarkan manual oleh admin.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>TS.IMG.006</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>TC.IMG.006.001</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Baris dengan NIP yang sudah ada dianggap data lama, bukan duplikat baru</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Guru yang NIP-nya sudah ada tidak dibuat ulang</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris dengan NIP yang sudah dipakai guru yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Berkas memuat guru yang datanya sudah ada; guru itu tidak dibuat dua kali.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada guru dengan NIP tersebut di database.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Sudah ada guru dengan NIP tersebut.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Guru dianggap sudah ada (existing), tidak membuat akun guru baru/duplikat.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52.8" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih berkas yang memuat guru yang sudah ada, lalu klik unggah.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tinjauan tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol setujui impor.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan berhasil, jumlah guru baru tetap nol, dan jumlah guru yang sudah ada bertambah satu.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>TS.IMG.007</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>TC.IMG.007.001</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Baris wali kelas otomatis menjadikan guru sebagai wali kelas terkait</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh templat berkas impor</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>File impor berisi baris guru bertipe Wali Kelas dengan nama kelas.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Admin mengunduh templat agar susunan kolomnya benar.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>File sudah diunggah dan masuk tahap pratinjau, salah satu baris bertipe Wali Kelas dengan nama kelas yang belum ada.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Admin sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor pada halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Kelas baru otomatis tercipta, guru tersimpan dan otomatis diset sebagai wali_kelas_id pada kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.IMG.008</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.IMG.008.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Format kolom lama (Walas) tetap dikenali sistem</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>File impor menggunakan format lama dengan kolom "Walas" alih-alih "Nama"/"Tipe".</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>File memakai heading kolom format lama (Walas, NIP, Kelas).</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Unggah file dengan format kolom lama.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Sistem mendeteksi format lama secara otomatis, diarahkan ke halaman pratinjau.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Buka halaman Impor Guru.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Impor Guru tampil beserta tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Impor.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Guru tersimpan dengan peran wali_kelas, tetap kompatibel dengan format lama.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52.8" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.IMG.009</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.IMG.009.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Akses halaman pratinjau impor guru tanpa mengunggah file terlebih dahulu</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Admin mengakses langsung halaman pratinjau tanpa proses unggah file.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Belum ada file yang diunggah pada sesi berjalan.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung halaman pratinjau impor guru.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Admin diarahkan kembali ke halaman impor guru karena tidak ada file pada sesi.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik tautan unduh templat.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Berkas templat impor guru terunduh.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
+  <mergeCells count="54">
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D25:D27"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="F28:F29"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="D9:D12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E19:E21"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C22:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30035,31 +30615,70 @@
     </row>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="C27:C29"/>
     <mergeCell ref="A21:A23"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="C48:C50"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D18:D20"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="D30:D32"/>
-    <mergeCell ref="G9:G11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E48:E50"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="G9:G11"/>
     <mergeCell ref="A36:A38"/>
-    <mergeCell ref="E18:E20"/>
     <mergeCell ref="A30:A32"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="A45:A47"/>
@@ -30068,76 +30687,37 @@
     <mergeCell ref="G21:G23"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F24:F26"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
-    <mergeCell ref="F12:F14"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="F45:F47"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
-    <mergeCell ref="A6:K7"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="G24:G26"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="A12:A14"/>
     <mergeCell ref="D15:D17"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="E45:E47"/>
-    <mergeCell ref="G45:G47"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="B30:B32"/>
     <mergeCell ref="A33:A35"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="D42:D44"/>
     <mergeCell ref="F48:F50"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E21:E23"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="G27:G29"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="D48:D50"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31406,21 +31986,51 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="C27:C29"/>
     <mergeCell ref="F17:F19"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="E20:E21"/>
     <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="C12:C13"/>
@@ -31430,7 +32040,6 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C14:C16"/>
-    <mergeCell ref="A20:A21"/>
     <mergeCell ref="E14:E16"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D20:D21"/>
@@ -31438,56 +32047,27 @@
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="F36:F38"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="C36:C38"/>
     <mergeCell ref="A27:A29"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="B30:B32"/>
     <mergeCell ref="A33:A35"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D12:D13"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G27:G29"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="E17:E19"/>
     <mergeCell ref="G17:G19"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A5:E5"/>
     <mergeCell ref="D17:D19"/>
-    <mergeCell ref="G25:G26"/>
     <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D23:D24"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -3641,8 +3641,8 @@
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="D19:D21"/>
+    <mergeCell ref="B28:B29"/>
     <mergeCell ref="F19:F21"/>
-    <mergeCell ref="B28:B29"/>
     <mergeCell ref="D28:D29"/>
     <mergeCell ref="B22:B24"/>
     <mergeCell ref="A3:E3"/>
@@ -3683,7 +3683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -3723,7 +3723,7 @@
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning, State Transition Testing</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -3793,165 +3793,137 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.MOA.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.MOA.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas melihat status absensi dan daftar siswa kelas sendiri hari ini</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat kehadiran kelas hari ini</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas membuka halaman Kelas Saya, sistem menampilkan ringkasan status absensi hari ini dan daftar siswa.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka Kelas Saya untuk melihat siapa saja yang sudah hadir hari ini.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Hari ini termasuk hari absensi dan seorang siswa sudah absen hadir.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Kelas Saya.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Halaman tampil dengan ringkasan status absensi dan daftar siswa hari ini.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Kelas Saya tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan baris siswa yang sudah absen.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama kelas, nama siswa, dan status kehadirannya Hadir tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26.4" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.MOA.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.MOA.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas tanpa kelas perwalian tetap melihat halaman kosong</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Menetapkan status absensi siswa secara manual</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Guru berperan wali kelas tapi belum ditugaskan ke kelas manapun membuka halaman Kelas Saya.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Siswa menyerahkan surat sakit, lalu wali kelas menandai kehadirannya sebagai Sakit.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Guru belum punya kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Hari ini termasuk hari absensi.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Kelas Saya.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Halaman tampil kosong (bukan error), tidak ada data siswa.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.003</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.003.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengisi status absensi siswa yang belum ada record hari ini</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengisi status absensi manual untuk siswa yang belum tercatat hari ini.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Belum ada record absensi untuk siswa tsb hari ini.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Pilih status absensi (misal Hadir) untuk siswa.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Status yang dipilih tampil di kolom siswa tersebut.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Kelas Saya tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3965,75 +3937,75 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Simpan.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Record absensi baru berhasil dibuat dengan status yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Pada baris siswa yang dituju, klik tombol status Sakit.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Status absensi hari ini berhasil diperbarui." dan status siswa itu berubah menjadi Sakit.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.004</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.004.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengubah status absensi siswa yang recordnya sudah ada hari ini</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengubah status absensi siswa yang sudah tercatat hari ini ke status lain.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOA.003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOA.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Menetapkan status absensi di luar hari absensi</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba menandai kehadiran pada hari yang bukan hari absensi.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada record absensi untuk siswa tsb hari ini.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Hari ini bukan hari absensi, misalnya hari Minggu.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Ubah status absensi siswa yang sudah tercatat ke status lain.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Status baru yang dipilih tampil di kolom siswa tersebut.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Kelas Saya tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4047,731 +4019,381 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Simpan.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Record yang sudah ada ter-update (bukan bikin record baru/duplikat).</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pada baris siswa yang dituju, klik tombol status Hadir.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa absensi hanya tersedia pada hari absensi yang ditentukan sekolah, dan status siswa tidak berubah.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOA.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOA.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Menetapkan status absensi siswa dari kelas lain</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba menandai kehadiran siswa yang bukan anggota kelasnya.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Ada siswa lain yang menjadi anggota kelas milik wali kelas berbeda.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Kelas Saya tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi daftar.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa dari kelas yang diampu yang tampil; siswa kelas lain tidak ada di daftar sehingga status absensinya tidak bisa diubah dari halaman ini.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>TS.MOA.005</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>TC.MOA.005.001</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas tidak bisa mengubah absensi siswa dari kelas lain</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Melihat rincian seorang siswa</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka rincian seorang siswa untuk melihat riwayat kehadirannya.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Kelas Saya tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa yang dituju.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian siswa tampil berisi nama siswa beserta bagian Riwayat Kehadiran.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26.4" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOA.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOA.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Mencari siswa berdasarkan nama</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mengetik sebagian nama siswa di kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Kelas berisi lebih dari satu siswa.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Kelas Saya tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52.8" customHeight="1" s="9">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Ketik sebagian nama siswa di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang namanya cocok yang tampil di daftar; siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOA.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOA.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Membuka Kelas Saya tanpa punya kelas</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mencoba mengubah status absensi siswa yang bukan dari kelas perwaliannya.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Guru yang belum ditugaskan sebagai wali kelas membuka Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa target berada di kelas yang berbeda.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Guru sedang masuk tetapi belum ditugaskan sebagai wali kelas mana pun.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Kirim permintaan ubah status absensi untuk siswa kelas lain.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403), status absensi tidak berubah.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.006</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.006.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas tidak bisa mengubah absensi pada hari akhir pekan</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mencoba mengubah status absensi pada hari Sabtu/Minggu.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal saat ini jatuh pada akhir pekan.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Kirim permintaan ubah status absensi saat akhir pekan.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Absensi hanya tersedia pada hari Senin sampai Jumat", status tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.007</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.007.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Status absensi yang bukan salah satu dari 5 pilihan ditolak</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengirim nilai status yang tidak termasuk hadir/terlambat/izin/sakit/alpha.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Kirim status absensi dengan nilai tidak valid.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi status tidak valid, tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.008</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.008.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas melihat detail siswa kelas sendiri</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas membuka detail salah satu siswa di kelas perwaliannya.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik salah satu siswa di daftar Kelas Saya.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Halaman detail siswa tampil lengkap (biodata, pelanggaran disetujui, riwayat absensi).</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26.4" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.009</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.009.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas tidak bisa melihat detail siswa kelas lain</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mencoba membuka detail siswa yang bukan dari kelas perwaliannya.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Siswa target berada di kelas yang berbeda.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung halaman detail siswa kelas lain.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403).</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52.8" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.010</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.010.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint status absensi (polling) mengembalikan data yang benar</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Sistem memanggil endpoint status-absensi untuk polling data terbaru.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Ada siswa dengan status absensi tercatat hari ini.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Panggil endpoint status-absensi.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Sistem mengembalikan JSON berisi ringkasan statistik dan daftar status per siswa yang sesuai data terbaru.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.011</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.011.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Transisi state Kosong ke Ada setelah update absensi valid</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi belum ada record absensi hari ini (Kosong), wali kelas mengisi status valid.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Belum ada record absensi untuk siswa hari ini (state Kosong).</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Pastikan belum ada record absensi siswa hari ini.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>State Kosong.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Isi dan simpan status absensi valid.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>State berpindah menjadi Ada, record baru tercipta.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.012</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.012.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>State tetap Ada dan status ter-replace saat diupdate ulang</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi sudah Ada dengan status A, wali kelas mengubah ke status B.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>State sudah Ada dengan status tertentu.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Pastikan record absensi siswa hari ini sudah Ada.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>State Ada.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26.4" customHeight="1" s="9">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Ubah status ke nilai lain dan simpan.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>State tetap Ada, tapi status ter-replace (bukan record baru).</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.013</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.013.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>State tetap Ada saat percobaan update di akhir pekan diblokir</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi Ada, wali kelas mencoba update saat akhir pekan.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>State sudah Ada; hari ini akhir pekan.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Pastikan record absensi siswa hari ini sudah Ada.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>State Ada.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Coba ubah status saat akhir pekan.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>State tetap Ada tidak berubah, permintaan diblokir (no-op aman).</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26.4" customHeight="1" s="9">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOA.014</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOA.014.001</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>State tetap Kosong saat percobaan update di akhir pekan diblokir</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Dari kondisi Kosong, wali kelas mencoba update saat akhir pekan.</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>State masih Kosong; hari ini akhir pekan.</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Pastikan belum ada record absensi siswa hari ini.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>State Kosong.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26.4" customHeight="1" s="9">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Coba isi status saat akhir pekan.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>State tetap Kosong, permintaan diblokir (no-op aman).</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Kelas Saya.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tampil tanpa daftar siswa, disertai keterangan bahwa guru belum ditugaskan sebagai wali kelas.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26.4" customHeight="1" s="9"/>
+    <row r="23" ht="26.4" customHeight="1" s="9"/>
+    <row r="24" ht="26.4" customHeight="1" s="9"/>
+    <row r="25" ht="26.4" customHeight="1" s="9"/>
+    <row r="26" ht="26.4" customHeight="1" s="9"/>
+    <row r="27" ht="26.4" customHeight="1" s="9"/>
+    <row r="28" ht="26.4" customHeight="1" s="9"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
     <mergeCell ref="E13:E14"/>
+    <mergeCell ref="B17:B18"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="D21:D22"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="F17:F18"/>
     <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C17:C18"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="G25:G26"/>
     <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
     <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
     <mergeCell ref="A6:K7"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B21:B22"/>
     <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4784,7 +4406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -4894,741 +4516,629 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.REA.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.REA.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas melihat rekap absensi dengan rentang tanggal default</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat rekap kehadiran kelas</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas membuka halaman rekap absensi tanpa filter, sistem pakai rentang default (awal bulan sampai hari ini).</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka rekap untuk melihat rangkuman kehadiran seluruh siswa kelasnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Seorang siswa sudah punya beberapa catatan kehadiran.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Rekap Absensi tanpa mengisi filter.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Rekap tampil dengan rentang tanggal awal bulan berjalan sampai hari ini.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal mulai dan tanggal selesai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama kelas, nama siswa, jumlah hadir, terlambat, izin, sakit, alpha, dan persentase kehadirannya tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26.4" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.REA.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.REA.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Filter bulan meng-override rentang mulai/selesai</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Persentase kehadiran dihitung dari hari yang sudah punya keputusan</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengisi filter bulan sekaligus mulai/selesai, filter bulan yang dipakai.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Persentase dihitung dari hari hadir dan terlambat dibagi seluruh hari yang tercatat.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa tercatat dua hari hadir dan dua hari alpha.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi filter bulan dan filter mulai/selesai yang berbeda bulan.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Nilai yang dipilih tampil pada kolom filter masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Rekap mengikuti rentang bulan, bukan mulai/selesai.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang memuat keempat hari itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Persentase kehadiran siswa tersebut tampil 50%.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.REA.003</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.REA.003.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Filter berdasarkan siswa tertentu</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran di luar hari absensi tidak dihitung</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas memfilter rekap ke satu siswa spesifik.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Catatan di hari yang bukan hari absensi diabaikan dari perhitungan rekap.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu catatan hadir di hari absensi dan satu catatan alpha di hari libur.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Pilih satu siswa pada filter.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Rekap hanya menampilkan siswa yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang memuat kedua hari itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Alpha di hari libur diabaikan sehingga persentase kehadiran siswa tetap 100%.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.4" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>TS.REA.004</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TC.REA.004.001</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Filter berdasarkan status absensi</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring rekap untuk seorang siswa</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas memfilter rekap berdasarkan status tertentu (misal alpha).</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memilih satu siswa di kolom penyaring agar rekap hanya menampilkan siswa itu.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Kelas berisi lebih dari satu siswa.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Pilih filter status alpha.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Rekap hanya menampilkan siswa dengan status tsb dalam rentang yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih seorang siswa di kolom Siswa, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang dipilih yang tampil di tabel; siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>TS.REA.005</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>TC.REA.005.001</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Ekspor Excel ditolak untuk wali kelas tanpa kelas perwalian</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring rekap berdasarkan status</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas menyaring rekap agar hanya menampilkan siswa yang pernah alpha.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Satu siswa pernah alpha dan satu siswa lain selalu hadir.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Alpha di kolom Status, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang pernah alpha yang tampil; siswa yang selalu hadir tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring rekap per bulan</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memilih bulan tertentu agar rekap hanya menghitung kehadiran di bulan itu.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya catatan kehadiran di dua bulan berbeda.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26.4" customHeight="1" s="9">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih bulan yang dituju di kolom Bulan, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Rekap hanya menghitung kehadiran di bulan yang dipilih; catatan di bulan lain tidak ikut dihitung.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai lebih awal daripada tanggal mulai</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Guru berperan wali kelas tanpa kelas perwalian mencoba ekspor Excel.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memilih tanggal selesai yang jatuh sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Guru belum punya kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung endpoint ekspor Excel.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403).</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26.4" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.006</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.006.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Ekspor PDF ditolak untuk wali kelas tanpa kelas perwalian</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Guru berperan wali kelas tanpa kelas perwalian mencoba ekspor PDF.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26.4" customHeight="1" s="9">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai yang lebih awal daripada tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan rekap tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.008</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh rekap dalam berkas Excel</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mengunduh rekap kehadiran untuk diarsipkan.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Guru belum punya kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Akses langsung endpoint ekspor PDF.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403).</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.007</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.007.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal selesai sebelum mulai ditolak</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengisi tanggal selesai yang lebih awal dari tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai lebih akhir dari tanggal selesai.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal selesai harus setelah/sama dengan mulai, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.008</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.008.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Format tanggal yang salah ditolak</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengisi tanggal dengan format selain YYYY-MM-DD.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai dengan format salah (misal DD-MM-YYYY).</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Teks yang diketik tampil di kolom tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format tanggal tidak valid, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26.4" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.009</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.009.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Filter siswa dengan identitas yang tidak ada ditolak</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengirim filter siswa dengan NISN yang tidak terdaftar.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Kirim filter siswa dengan NISN yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi siswa tidak valid, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.010</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.010.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Ekspor Excel berhasil</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengekspor rekap absensi ke Excel untuk rentang yang dipilih.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Ekspor Excel.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>File Excel rekap berhasil diunduh.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.011</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.011.001</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Ekspor PDF berhasil</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengekspor rekap absensi ke PDF untuk rentang yang dipilih.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Ekspor PDF.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>File PDF rekap berhasil diunduh.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.012</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.012.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Batas tanggal selesai sama dengan mulai (boundary tepat sama)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal selesai diisi tepat sama dengan tanggal mulai — tepat di batas yang diperbolehkan.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai dan selesai dengan nilai yang sama.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5642,75 +5152,75 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal lolos validasi (batas atas diperbolehkan), rekap tampil.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal, lalu klik tombol Ekspor Excel.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Berkas Excel rekap absensi kelas tersebut terunduh, dengan nama berkas memuat nama kelas dan rentang tanggalnya.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.REA.013</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.REA.013.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Batas tanggal selesai satu hari sebelum mulai (boundary di bawah batas)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal selesai diisi tepat 1 hari sebelum tanggal mulai — tepat di bawah batas yang diperbolehkan.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh rekap dalam berkas PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mengunduh rekap kehadiran dalam bentuk PDF.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal selesai 1 hari sebelum tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5724,67 +5234,684 @@
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal selesai tidak valid, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal, lalu klik tombol Ekspor PDF.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Berkas PDF rekap absensi kelas tersebut terunduh, dengan nama berkas memuat nama kelas dan rentang tanggalnya.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.010</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.010.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Membuka rekap tanpa punya kelas</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Guru yang belum ditugaskan sebagai wali kelas membuka Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Guru sedang masuk tetapi belum ditugaskan sebagai wali kelas mana pun.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tampil tanpa tabel rekap, disertai keterangan "Belum Ada Kelas" dan anjuran menghubungi administrator.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.011</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.011.001</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh tepat pada tanggal mulai ikut dihitung.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu catatan alpha tepat pada tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal mulainya sama dengan tanggal alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Alpha tersebut ikut dihitung sehingga persentase kehadiran siswa tampil 0%.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.011</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.011.002</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh sehari sebelum tanggal mulai tidak dihitung.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya catatan alpha sehari sebelum tanggal mulai dan catatan hadir di dalam rentang.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tidak memuat hari alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Alpha di luar rentang diabaikan sehingga persentase kehadiran siswa tampil 100%.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.012</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.012.001</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh tepat pada tanggal selesai ikut dihitung.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu catatan alpha tepat pada tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal selesainya sama dengan tanggal alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Alpha tersebut ikut dihitung sehingga persentase kehadiran siswa tampil 0%.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.012</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.012.002</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh sehari setelah tanggal selesai tidak dihitung.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya catatan hadir di dalam rentang dan catatan alpha sehari setelah tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tidak memuat hari alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Alpha di luar rentang diabaikan sehingga persentase kehadiran siswa tampil 100%.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.013</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.013.001</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai boleh sama dengan tanggal mulai, menghasilkan rekap satu hari.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu catatan hadir pada tanggal itu.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal mulai dan tanggal selesai yang sama, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Rekap satu hari tampil tanpa pesan kesalahan, dengan persentase kehadiran siswa 100%.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.REA.013</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.REA.013.002</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai sehari lebih awal daripada tanggal mulai ditolak.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Rekap Absensi.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai satu hari sebelum tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan rekap tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="110">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E38:E39"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C32:C33"/>
     <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="A15:A16"/>
     <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5796,7 +5923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -5829,14 +5956,14 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : Wali Kelas &gt; Poin Pelanggaran</t>
+          <t>Page : Wali Kelas &gt; Riwayat Pelanggaran</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -5906,452 +6033,1224 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.001</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.001.001</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas melihat pelanggaran yang disetujui untuk kelas sendiri</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat riwayat pelanggaran kelas</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas membuka halaman Poin Pelanggaran kelasnya.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memantau pelanggaran yang sudah dicatat kesiswaan untuk siswa kelasnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran siswa berstatus disetujui di kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Seorang siswa di kelas itu punya catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Daftar pelanggaran siswa yang sudah disetujui tampil.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.002</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.002.001</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas tanpa kelas perwalian tetap melihat halaman kosong</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, nama pelanggaran, dan kategorinya tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26.4" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.002</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran siswa kelas lain tidak tampil</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas hanya boleh melihat pelanggaran siswa di kelas yang diampunya.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Ada siswa dari kelas lain yang punya catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran siswa dari kelas lain tidak tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring riwayat untuk seorang siswa</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Guru berperan wali kelas tanpa kelas perwalian membuka halaman Poin Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memilih satu siswa agar riwayat hanya menampilkan pelanggaran siswa itu.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Guru belum punya kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Dua siswa di kelas itu sama-sama punya catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Halaman tampil kosong (bukan error).</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.003</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.003.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Filter berdasarkan siswa tertentu</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.8" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pilih seorang siswa di kolom Siswa, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran milik siswa yang dipilih yang tampil; pelanggaran siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring riwayat berdasarkan kategori</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas memfilter daftar pelanggaran ke satu siswa spesifik.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas menyaring riwayat agar hanya menampilkan pelanggaran kategori berat.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran siswa berstatus disetujui di kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu pelanggaran ringan dan satu pelanggaran berat.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Pilih satu siswa pada filter.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran siswa yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.004.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Filter berdasarkan kategori pelanggaran</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52.8" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Berat di kolom Kategori, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran kategori berat yang tampil; pelanggaran ringan tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring riwayat berdasarkan rentang tanggal</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas memfilter daftar pelanggaran berdasarkan kategori.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas membatasi riwayat pada rentang tanggal tertentu.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran siswa berstatus disetujui di kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya pelanggaran di dua bulan berbeda.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Pilih filter kategori (misal ringan).</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran kategori tsb.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Filter berdasarkan rentang tanggal pelanggaran</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang hanya memuat salah satu pelanggaran, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran di dalam rentang yang tampil; pelanggaran di luar rentang tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai lebih awal daripada tanggal mulai</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memilih tanggal selesai yang jatuh sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai yang lebih awal daripada tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan riwayat tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Kelas belum punya pelanggaran</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas memfilter daftar pelanggaran berdasarkan rentang tanggal.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas membuka riwayat pada kelas yang belum punya catatan pelanggaran sama sekali.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran siswa berstatus disetujui di kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Belum ada satu pun pelanggaran yang tercatat untuk kelas itu.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Isi filter dari tanggal dan sampai tanggal.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran dalam rentang tsb.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52.8" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Pelanggaran berstatus menunggu/ditolak tidak ikut ditampilkan</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum ada riwayat pelanggaran untuk kelas ini."</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.008</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Membuka riwayat tanpa punya kelas</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Guru yang belum ditugaskan sebagai wali kelas membuka Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Guru sedang masuk tetapi belum ditugaskan sebagai wali kelas mana pun.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tampil tanpa tabel riwayat, disertai keterangan "Belum Ada Kelas" dan anjuran menghubungi administrator.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.009</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.009.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal riwayat</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran berstatus menunggu ACC dan ditolak untuk siswa yang sama, keduanya tidak boleh muncul.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran berstatus disetujui, menunggu ACC, dan ditolak untuk kelas yang sama.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi tepat pada tanggal mulai ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya pelanggaran tepat pada tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Cuma pelanggaran berstatus disetujui yang muncul; yang menunggu ACC dan ditolak tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Pelanggaran kelas lain tidak ikut ditampilkan</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal mulainya sama dengan tanggal pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.009</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.009.002</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal riwayat</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi sehari sebelum tanggal mulai tidak tampil.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya pelanggaran sehari sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang dimulai sehari setelah pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tidak tampil, dan muncul keterangan "Belum ada riwayat pelanggaran untuk kelas ini."</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.010</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.010.001</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal riwayat</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran disetujui milik siswa dari kelas lain, tidak boleh ikut tampil di kelas sendiri.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran disetujui di kelas lain.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi tepat pada tanggal selesai ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya pelanggaran tepat pada tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Hanya pelanggaran kelas sendiri yang tampil, pelanggaran kelas lain tidak ikut muncul.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52.8" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.PPW.008</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.PPW.008.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Daftar pelanggaran dipaginasi 25 per halaman</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal selesainya sama dengan tanggal pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.010</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.010.002</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal riwayat</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi sehari setelah tanggal selesai tidak tampil.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya pelanggaran sehari setelah tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang berakhir sehari sebelum pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tidak tampil, dan muncul keterangan "Belum ada riwayat pelanggaran untuk kelas ini."</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.011</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.011.001</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal riwayat</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Ada lebih dari 25 data pelanggaran disetujui di kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Ada 26 data pelanggaran disetujui di kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai boleh sama dengan tanggal mulai, menghasilkan riwayat satu hari.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya pelanggaran pada tanggal itu.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Halaman pertama menampilkan tepat 25 data, total keseluruhan tetap 26 (bisa lanjut ke halaman berikutnya).</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal mulai dan tanggal selesai yang sama, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran pada tanggal itu tampil tanpa pesan kesalahan.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.RIP.011</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.RIP.011.002</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal riwayat</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai sehari lebih awal daripada tanggal mulai ditolak.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pelanggaran tampil.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai satu hari sebelum tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan riwayat tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="96">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6363,7 +7262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -6473,631 +7372,491 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.001</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.001.001</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengajukan penambahan poin untuk siswa kelas sendiri</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim pengajuan penambahan poin</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengajukan penambahan poin dengan alasan untuk siswa di kelas perwaliannya.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mengajukan penambahan poin untuk siswa berprestasi di kelasnya. Jumlah poinnya nanti ditentukan kesiswaan.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa terdaftar di kelas perwalian wali kelas.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka form Ajukan Penambahan Poin, pilih siswa dan isi alasan.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Siswa yang dipilih dan alasan yang diketik tampil pada form.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52.8" customHeight="1" s="9">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Pengajuan tersimpan berstatus menunggu ACC, jumlah poin masih kosong (diisi kesiswaan nanti), saldo poin siswa belum berubah.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.002</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.002.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas tidak bisa mengajukan untuk siswa kelas lain</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa lalu tulis alasan pengajuan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Siswa dan alasan terisi.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil dikirim ke kesiswaan." dan pengajuan itu tampil di daftar dengan status Menunggu.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.002</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.002.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Pilihan siswa hanya dari kelas sendiri</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Kolom pilihan siswa hanya memuat anggota kelas yang diampu wali kelas itu.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Ada siswa lain yang menjadi anggota kelas berbeda.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.4" customHeight="1" s="9">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Buka kolom pilihan siswa.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa dari kelas yang diampu yang muncul sebagai pilihan; siswa kelas lain tidak ada.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.003</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.003.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Mengajukan poin untuk siswa kelas lain</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mencoba mengajukan penambahan poin untuk siswa yang bukan dari kelas perwaliannya.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mencoba mengajukan poin untuk siswa yang bukan anggota kelasnya.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa target berada di kelas yang berbeda.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Ada siswa yang menjadi anggota kelas milik wali kelas berbeda.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan untuk siswa kelas lain.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403), pengajuan tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.003</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.003.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Alasan pengajuan kosong ditolak</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Cari siswa dari kelas lain di kolom pilihan siswa.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Siswa itu tidak tersedia sebagai pilihan, sehingga pengajuan untuknya tidak bisa dibuat.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.004</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.004.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim pengajuan tanpa alasan</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengirim pengajuan tanpa mengisi alasan.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mengosongkan kolom alasan lalu mengirim pengajuan.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa terdaftar di kelas perwalian wali kelas.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Pilih siswa, biarkan kolom alasan kosong.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Kolom alasan tetap kosong.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="79.2" customHeight="1" s="9">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi alasan wajib diisi, pengajuan tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.004</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.004.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Identitas siswa yang tidak ada ditolak</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, biarkan kolom alasan kosong, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Alasan wajib diisi." dan pengajuan tidak terkirim.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.005</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.005.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim pengajuan tanpa memilih siswa</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengirim NISN siswa yang tidak terdaftar di database.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas mengisi alasan tetapi belum memilih siswa.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Kirim NISN yang tidak ada di database beserta alasan.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi siswa tidak valid, pengajuan tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26.4" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.005</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.005.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Identitas siswa kosong ditolak</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas mengirim pengajuan tanpa memilih siswa.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Biarkan kolom siswa kosong, isi alasan.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Kolom siswa tetap kosong.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi siswa wajib dipilih, pengajuan tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.006</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.006.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Daftar pengajuan hanya menampilkan milik wali kelas sendiri</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Ada pengajuan milik wali kelas lain, tidak boleh ikut tampil di daftar wali kelas ini.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Ada pengajuan poin dari wali kelas lain.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman daftar pengajuan poin.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Hanya pengajuan yang diajukan sendiri yang tampil.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.007</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.007.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Daftar pengajuan bisa difilter berdasarkan status</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas memfilter daftar pengajuan berdasarkan status menunggu ACC.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Ada pengajuan dengan status berbeda-beda.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Pilih filter status Menunggu ACC.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pengajuan berstatus tsb.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.008</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.008.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Form pengajuan tanpa kelas perwalian menampilkan daftar siswa kosong</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Guru berperan wali kelas tanpa kelas perwalian membuka form Ajukan Penambahan Poin.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Guru belum punya kelas perwalian.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Buka form Ajukan Penambahan Poin.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Daftar pilihan siswa kosong (bukan error).</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="79.2" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.009</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.009.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Percobaan mengirim jumlah poin langsung diabaikan sistem</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Form pengajuan memang tidak punya field jumlah poin; percobaan mengirimnya lewat bypass tetap diabaikan.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Form Ajukan Penambahan Poin di UI tidak memiliki field jumlah poin sama sekali.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan dengan field jumlah poin tambahan yang tidak ada di form.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Pengajuan tersimpan berstatus menunggu ACC, jumlah poin tetap kosong — nilai kiriman diabaikan sepenuhnya (kesiswaan yang menentukan nanti, bukan wali kelas).</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.010</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.010.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum alasan (boundary di atas 1000 karakter)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Alasan diisi 1001 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Pilih siswa, isi alasan dengan 1001 karakter.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom alasan.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7111,75 +7870,75 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi alasan maksimal 1000 karakter, pengajuan tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Tulis alasan tanpa memilih siswa, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Siswa wajib dipilih." dan pengajuan tidak terkirim.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.PGP.011</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.PGP.011.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum alasan (boundary tepat 1000 karakter)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.006</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.006.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Melihat daftar pengajuan sendiri</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Alasan diisi tepat 1000 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Wali kelas punya kelas perwalian dengan siswa terdaftar.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas memantau pengajuan yang pernah dikirimnya beserta statusnya.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Wali kelas pernah mengirim sebuah pengajuan yang masih menunggu.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Pilih siswa, isi alasan dengan tepat 1000 karakter.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom alasan.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7193,67 +7952,752 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Kirim pengajuan.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Alasan lolos validasi maksimum, pengajuan berhasil tersimpan.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, alasan pengajuan, dan status Menunggu tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.007</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.007.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring daftar pengajuan berdasarkan status</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas menyaring daftar agar hanya menampilkan pengajuan yang masih menunggu.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Wali kelas punya satu pengajuan menunggu dan satu pengajuan yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih status Menunggu di kolom penyaring, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pengajuan berstatus Menunggu yang tampil; pengajuan yang sudah disetujui tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.008</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.008.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Pengajuan wali kelas lain tidak tampil</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Setiap wali kelas hanya melihat pengajuan yang dikirimnya sendiri.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Wali kelas lain pernah mengirim sebuah pengajuan.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Pengajuan milik wali kelas lain tidak tampil, dan muncul keterangan "Belum ada pengajuan."</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.009</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.009.001</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Mengajukan poin tanpa punya kelas</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Guru yang belum ditugaskan sebagai wali kelas membuka halaman pengajuan baru.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Guru sedang masuk tetapi belum ditugaskan sebagai wali kelas mana pun.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil tanpa satu pun pilihan siswa, sehingga pengajuan tidak bisa dibuat.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.010</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.010.001</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah panjang alasan</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Alasan sepanjang 0 karakter, tepat di bawah batas terendah.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, biarkan kolom alasan kosong, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Alasan wajib diisi." dan pengajuan tidak terkirim.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.010</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.010.002</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah panjang alasan</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Alasan sepanjang 1 karakter, tepat di batas terendah.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, tulis alasan sepanjang 1 karakter, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil dikirim ke kesiswaan."</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.011</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.011.001</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas panjang alasan</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Alasan sepanjang 999 karakter, tepat di bawah batas tertinggi.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, tulis alasan sepanjang 999 karakter, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil dikirim ke kesiswaan."</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.011</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.011.002</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas panjang alasan</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Alasan sepanjang 1000 karakter, tepat di batas tertinggi.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, tulis alasan sepanjang 1000 karakter, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil dikirim ke kesiswaan."</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.PPW.011</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.PPW.011.003</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas panjang alasan</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Alasan sepanjang 1001 karakter, tepat di atas batas tertinggi.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pengajuan Poin lalu klik tombol Ajukan Poin.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman pengajuan baru tampil berisi pilihan siswa dan kolom alasan.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, tulis alasan sepanjang 1001 karakter, lalu klik Kirim Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Alasan maksimal 1000 karakter." dan pengajuan tidak terkirim.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:F13"/>
+  <mergeCells count="96">
+    <mergeCell ref="C30:C31"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="D36:D37"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C13:C15"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
     <mergeCell ref="C21:C22"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D19:D20"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C16:C18"/>
     <mergeCell ref="D23:D24"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -5805,17 +5805,64 @@
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="G38:G39"/>
-    <mergeCell ref="D36:D37"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B23:B24"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="B13:B14"/>
     <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="C21:C22"/>
@@ -5823,44 +5870,22 @@
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B28:B29"/>
     <mergeCell ref="C36:C37"/>
     <mergeCell ref="D28:D29"/>
-    <mergeCell ref="B15:B16"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="G30:G31"/>
     <mergeCell ref="C23:C24"/>
-    <mergeCell ref="G30:G31"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B36:B37"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="E25:E26"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="G36:G37"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D11:D12"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="G19:G20"/>
@@ -5869,48 +5894,23 @@
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="E38:E39"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="F38:F39"/>
-    <mergeCell ref="C17:C18"/>
     <mergeCell ref="E36:E37"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B30:B31"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D30:D31"/>
     <mergeCell ref="D19:D20"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="A4:E4"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B32:B33"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C34:C35"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="D23:D24"/>
     <mergeCell ref="C15:C16"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8605,21 +8605,59 @@
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="G38:G39"/>
     <mergeCell ref="D36:D37"/>
-    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="F21:F22"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F21:F22"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="E9:E12"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="G16:G18"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="B16:B18"/>
@@ -8631,72 +8669,34 @@
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="F16:F18"/>
-    <mergeCell ref="C27:C28"/>
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="F9:F12"/>
-    <mergeCell ref="E25:E26"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="G9:G12"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
     <mergeCell ref="B13:B15"/>
-    <mergeCell ref="E21:E22"/>
     <mergeCell ref="D13:D15"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="F36:F37"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G34:G35"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="F32:F33"/>
-    <mergeCell ref="E38:E39"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E27:E28"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="F27:F28"/>
-    <mergeCell ref="B9:B12"/>
     <mergeCell ref="F38:F39"/>
     <mergeCell ref="E36:E37"/>
-    <mergeCell ref="D25:D26"/>
     <mergeCell ref="G13:G15"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D30:D31"/>
     <mergeCell ref="D19:D20"/>
-    <mergeCell ref="A4:E4"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B32:B33"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A16:A18"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D23:D24"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8709,7 +8709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -8819,55 +8819,55 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.001</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.001.001</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menambahkan jenis pelanggaran baru dengan data valid</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Menambah jenis pelanggaran baru</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi form tambah jenis pelanggaran dengan nama, kategori, dan poin yang valid.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menambah satu jenis pelanggaran beserta kategori dan poinnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tambah Jenis Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form tampil dengan kolom nama, kategori, poin, keterangan, status aktif.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Jenis Pelanggaran tampil berisi daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8881,129 +8881,129 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama, pilih kategori Ringan, isi poin 10.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Data yang diketik/dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama pelanggaran, pilih kategori Sanksi Ringan, isi poin 10, lalu isi keterangan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Seluruh kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran berhasil tersimpan, diarahkan ke daftar jenis pelanggaran.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.002</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.002.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menambahkan jenis pelanggaran dengan nama yang sudah dipakai</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil ditambahkan." dan jenis pelanggaran itu tampil di daftar beserta kategorinya.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.002</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.002.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Nama pelanggaran sudah dipakai</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi nama jenis pelanggaran yang sudah ada di database.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan memakai nama yang sudah dipakai jenis pelanggaran lain.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Sudah ada jenis pelanggaran lain dengan nama tersebut.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada jenis pelanggaran dengan nama tersebut.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tambah Jenis Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Form tampil.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama yang sudah dipakai jenis pelanggaran lain.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Nama yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9017,157 +9017,157 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nama sudah digunakan, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama yang sudah dipakai, lengkapi kolom lain, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Nama pelanggaran sudah digunakan." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52.8" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.003</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.003.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menambahkan jenis pelanggaran dengan kategori tidak valid</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.003</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.003.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Poin di luar rentang kategori</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengirim kategori di luar 4 pilihan yang tersedia (ringan/sedang/berat/sangat_berat).</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan memilih kategori Sanksi Ringan tetapi mengisi poin di luar rentang kategori itu.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Kirim data tambah jenis pelanggaran dengan kategori = "extreme" (nilai di luar pilihan form).</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi kategori tidak valid, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.004</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.004.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menambahkan jenis pelanggaran dengan poin di luar rentang kategori</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Ringan, isi poin 60, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Poin untuk kategori ini harus berada di antara 5 sampai 25." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26.4" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.004</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.004.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Poin diisi huruf</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi poin 60 untuk kategori Ringan yang seharusnya bernilai 5-25.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengisi kolom poin dengan huruf, bukan angka.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tambah Jenis Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Form tampil.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26.4" customHeight="1" s="9">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Pilih kategori Ringan, isi poin 60.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Kategori dan poin yang diisi tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9181,75 +9181,75 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi poin harus berada di antara 5 sampai 25, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori, isi kolom poin dengan huruf, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Poin pelanggaran harus berupa angka." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26.4" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.005</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.005.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memperbarui jenis pelanggaran</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.005</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.005.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Mengubah jenis pelanggaran</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengubah nama dan poin jenis pelanggaran yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan memperbaiki nama dan poin sebuah jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Data jenis pelanggaran sudah ada.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Jenis pelanggaran yang akan diubah sudah ada.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Jenis Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil terisi data lama.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Jenis Pelanggaran tampil berisi daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9263,20 +9263,20 @@
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Ubah nama dan poin.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Data baru yang diketik tampil di kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Ubah pada baris jenis pelanggaran yang dituju.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Halaman ubah tampil berisi data lama.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9290,567 +9290,567 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran berhasil diperbarui.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Ganti nama dan poinnya, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil diperbarui." dan nama barunya tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.006</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.006.001</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memperbarui nama jenis pelanggaran menjadi nama milik jenis lain</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.006</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.006.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus jenis pelanggaran yang belum dipakai</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran yang belum pernah dipakai mencatat pelanggaran siswa boleh dihapus.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Jenis pelanggaran itu belum pernah dipakai.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Jenis Pelanggaran tampil berisi daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris jenis pelanggaran itu, lalu setujui konfirmasinya.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil dihapus." dan jenis pelanggaran itu hilang dari daftar.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26.4" customHeight="1" s="9">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.007</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.007.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus jenis pelanggaran yang sudah dipakai</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengubah nama jenis pelanggaran menjadi nama yang sudah dipakai jenis pelanggaran lain.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran yang sudah dipakai mencatat pelanggaran siswa tidak boleh dihapus.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Ada 2 jenis pelanggaran berbeda di database.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Jenis pelanggaran itu sudah dipakai pada catatan pelanggaran seorang siswa.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Jenis Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="8" t="n">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Jenis Pelanggaran tampil berisi daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26.4" customHeight="1" s="9">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Ubah nama menjadi nama milik jenis pelanggaran lain.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Nama yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26.4" customHeight="1" s="9">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris jenis pelanggaran itu, lalu setujui konfirmasinya.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa jenis pelanggaran sudah dipakai dan sebaiknya dinonaktifkan saja, dan jenis pelanggaran itu tetap ada di daftar.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26.4" customHeight="1" s="9">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.008</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.008.001</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Menonaktifkan jenis pelanggaran</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran yang tidak dipakai lagi dinonaktifkan supaya tidak muncul saat mencatat pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Jenis pelanggaran itu masih aktif.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Ubah pada baris jenis pelanggaran itu.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Halaman ubah tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39.6" customHeight="1" s="9">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Matikan penanda Aktif, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil diperbarui."</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26.4" customHeight="1" s="9">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nama sudah digunakan, data tidak diperbarui.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.007</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.007.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menonaktifkan jenis pelanggaran lewat update, bukan menghapus</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Saring daftar dengan status Nonaktif.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran itu tampil di daftar yang nonaktif.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26.4" customHeight="1" s="9">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.009</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.009.001</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Mencari jenis pelanggaran berdasarkan nama</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengubah status aktif menjadi nonaktif tanpa menghapus data.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengetik sebagian nama di kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran berstatus aktif.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada lebih dari satu jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Jenis Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="8" t="n">
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Jenis Pelanggaran tampil berisi daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39.6" customHeight="1" s="9">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Matikan toggle status aktif.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Toggle tampil dalam posisi nonaktif.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="39.6" customHeight="1" s="9">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Status berubah menjadi nonaktif, data tetap ada di database (tidak terhapus).</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26.4" customHeight="1" s="9">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.008</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.008.001</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus jenis pelanggaran yang belum pernah dipakai</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Ketik sebagian nama jenis pelanggaran di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Hanya jenis pelanggaran yang namanya cocok yang tampil; yang lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52.8" customHeight="1" s="9">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.010</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.010.001</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring jenis pelanggaran berdasarkan kategori</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus jenis pelanggaran yang belum pernah dicatat di data pelanggaran siswa manapun.</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menyaring daftar agar hanya menampilkan kategori tertentu.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran belum pernah dipakai.</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n">
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada jenis pelanggaran kategori ringan dan kategori berat.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris jenis pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26.4" customHeight="1" s="9">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n">
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Jenis Pelanggaran tampil berisi daftar jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="39.6" customHeight="1" s="9">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran berhasil terhapus dari database.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="39.6" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.009</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.009.001</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus jenis pelanggaran yang sudah dipakai pada catatan pelanggaran siswa</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Pilih kategori Sanksi Berat di kolom penyaring.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Hanya jenis pelanggaran kategori berat yang tampil; kategori lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52.8" customHeight="1" s="9">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.011</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.011.001</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Daftar jenis pelanggaran masih kosong</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka daftar sebelum satu pun jenis pelanggaran dibuat.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Belum ada satu pun jenis pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum ada data jenis pelanggaran."</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26.4" customHeight="1" s="9">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.012</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.012.001</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas terendah poin pelanggaran</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencoba menghapus jenis pelanggaran yang sudah pernah dicatat pada pelanggaran siswa.</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran sudah dipakai minimal satu catatan pelanggaran siswa.</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Poin 4, tepat di bawah batas terendah yang diterima sistem.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris jenis pelanggaran yang sudah dipakai.</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="52.8" customHeight="1" s="9">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan error jenis pelanggaran sudah dipakai dan disarankan dinonaktifkan, data tidak terhapus.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="39.6" customHeight="1" s="9">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.010</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.010.001</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar jenis pelanggaran berdasarkan kategori</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar jenis pelanggaran dengan kategori Ringan.</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Ada jenis pelanggaran dengan kategori berbeda-beda.</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Daftar Jenis Pelanggaran, pilih filter kategori Ringan.</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan jenis pelanggaran kategori ringan.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="52.8" customHeight="1" s="9">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.011</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.011.001</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar jenis pelanggaran berdasarkan status aktif/nonaktif</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar jenis pelanggaran dengan status nonaktif.</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Ada jenis pelanggaran aktif dan nonaktif.</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Daftar Jenis Pelanggaran, pilih filter status Nonaktif.</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan jenis pelanggaran yang berstatus nonaktif.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26.4" customHeight="1" s="9">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.012</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.012.001</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah poin kategori Ringan (boundary di bawah 5)</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Poin diisi 4 untuk kategori Ringan — tepat di bawah batas bawah 5.</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>Isi poin 4 untuk kategori Ringan.</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom poin.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9864,75 +9864,75 @@
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J35" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi poin harus 5-25, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Ringan, isi poin 4, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Poin pelanggaran minimal 5." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26.4" customHeight="1" s="9">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.013</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.013.001</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah poin kategori Ringan (boundary tepat 5)</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.012</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.012.002</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas terendah poin pelanggaran</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Poin diisi tepat 5 untuk kategori Ringan — tepat di batas bawah.</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Poin 5, tepat pada batas terendah.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>Isi poin tepat 5 untuk kategori Ringan.</t>
-        </is>
-      </c>
-      <c r="J36" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom poin.</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9946,75 +9946,75 @@
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>Poin lolos validasi minimum, jenis pelanggaran tersimpan.</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Ringan, isi poin 5, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26.4" customHeight="1" s="9">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.014</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.014.001</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas poin kategori Ringan (boundary tepat 25)</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.013</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.013.001</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas kategori Sanksi Ringan</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Poin diisi tepat 25 untuk kategori Ringan — tepat di batas atas.</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Poin 25, tepat pada batas atas kategori Sanksi Ringan.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>Isi poin tepat 25 untuk kategori Ringan.</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom poin.</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10028,75 +10028,75 @@
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>Poin lolos validasi maksimum, jenis pelanggaran tersimpan.</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Ringan, isi poin 25, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26.4" customHeight="1" s="9">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.015</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.015.001</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas poin kategori Ringan (boundary di atas 25)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.013</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.013.002</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas kategori Sanksi Ringan</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Poin diisi 26 untuk kategori Ringan — tepat di atas batas atas 25.</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Poin 26, tepat di atas batas atas kategori Sanksi Ringan.</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>Isi poin 26 untuk kategori Ringan.</t>
-        </is>
-      </c>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>Angka yang diketik tampil di kolom poin.</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10110,75 +10110,75 @@
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J41" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi poin harus 5-25, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Ringan, isi poin 26, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Poin untuk kategori ini harus berada di antara 5 sampai 25." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26.4" customHeight="1" s="9">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.016</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.016.001</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nama jenis pelanggaran (boundary tepat 255 karakter)</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.014</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.014.001</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah kategori Sanksi Sedang</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Nama diisi tepat 255 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Poin 26, tepat pada batas bawah kategori Sanksi Sedang.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="n">
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama jenis pelanggaran tepat 255 karakter.</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10192,75 +10192,75 @@
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>Nama lolos validasi maksimum, jenis pelanggaran tersimpan.</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Sedang, isi poin 26, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26.4" customHeight="1" s="9">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>TS.JNP.017</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>TC.JNP.017.001</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum nama jenis pelanggaran (boundary di atas 255 karakter)</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.014</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.014.002</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah kategori Sanksi Sedang</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Nama diisi 256 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Poin 25, tepat di bawah batas bawah kategori Sanksi Sedang.</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>Isi nama jenis pelanggaran 256 karakter.</t>
-        </is>
-      </c>
-      <c r="J44" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom nama.</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10274,130 +10274,322 @@
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J45" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi nama melebihi batas maksimum, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Sedang, isi poin 25, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Poin untuk kategori ini harus berada di antara 26 sampai 50." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.015</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.015.001</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>Batas tertinggi poin pelanggaran</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>Poin 100, tepat pada batas tertinggi yang diterima sistem.</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Sangat Berat, isi poin 100, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran berhasil ditambahkan."</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>TS.JEP.015</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>TC.JEP.015.002</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Batas tertinggi poin pelanggaran</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>Poin 101, tepat di atas batas tertinggi.</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Jenis Pelanggaran lalu klik tombol Tambah Jenis Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>Halaman jenis pelanggaran baru tampil berisi kolom nama, kategori, poin, dan keterangan.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Isi nama, pilih kategori Sanksi Sangat Berat, isi poin 101, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Poin pelanggaran maksimal 100." dan jenis pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="131">
     <mergeCell ref="F44:F45"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="C29:C30"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="G40:G41"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G9:G12"/>
     <mergeCell ref="D38:D39"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D16:D18"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="F34:F35"/>
-    <mergeCell ref="C22:C24"/>
     <mergeCell ref="G36:G37"/>
     <mergeCell ref="D40:D41"/>
     <mergeCell ref="F40:F41"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="E13:E14"/>
     <mergeCell ref="F36:F37"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C46:C47"/>
     <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="C40:C41"/>
     <mergeCell ref="F19:F21"/>
+    <mergeCell ref="E46:E47"/>
     <mergeCell ref="E40:E41"/>
     <mergeCell ref="B44:B45"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="C26:C28"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A16:A18"/>
     <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="E19:E21"/>
     <mergeCell ref="G19:G21"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="E42:E43"/>
     <mergeCell ref="G42:G43"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="G38:G39"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C22:C23"/>
     <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="G24:G25"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="B36:B37"/>
-    <mergeCell ref="F16:F18"/>
     <mergeCell ref="D42:D43"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="F9:F12"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="C38:C39"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
     <mergeCell ref="E34:E35"/>
+    <mergeCell ref="B38:B39"/>
     <mergeCell ref="G34:G35"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="D48:D49"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="G29:G30"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="F38:F39"/>
     <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A29:A30"/>
     <mergeCell ref="A44:A45"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="A9:A12"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
     <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -10467,8 +10467,8 @@
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="E26:E28"/>
+    <mergeCell ref="B29:B30"/>
     <mergeCell ref="G26:G28"/>
-    <mergeCell ref="B29:B30"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="F42:F43"/>
@@ -11003,7 +11003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -11113,55 +11113,55 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.001</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.001.001</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencatat pelanggaran siswa manapun tanpa batas kelas, langsung berstatus disetujui</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mencatat pelanggaran seorang siswa</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencatat pelanggaran baru untuk siswa dari kelas manapun.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencatat pelanggaran seorang siswa. Poin yang dipotong mengikuti jenis pelanggaran yang dipilih, tidak diisi manual.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Data siswa dan jenis pelanggaran aktif sudah ada.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada siswa terdaftar dan jenis pelanggaran yang aktif.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Catat Pelanggaran, pilih siswa dari kelas manapun.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Siswa yang dipilih tampil pada form, tanpa batasan kelas kesiswaan sendiri.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11175,267 +11175,211 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Pilih jenis pelanggaran aktif dan isi tanggal.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran dan tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Cari lalu pilih nama siswa, pilih jenis pelanggaran, isi tanggal kejadian, lalu isi catatan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Seluruh kolom terisi.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52.8" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Klik tombol Simpan.</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Pelanggaran tersimpan dengan status langsung disetujui (approved), tanpa alur pengajuan.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52.8" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.002</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.002.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencatat pelanggaran menggunakan jenis pelanggaran yang nonaktif</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pelanggaran siswa berhasil dicatat." dan catatan itu tampil di daftar beserta nama siswa dan nama pelanggarannya.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.002</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.002.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa berkurang sesuai jenis pelanggaran</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa mulai dari 100 dan langsung berkurang begitu pelanggaran dicatat, tanpa perlu persetujuan siapa pun.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya satu catatan pelanggaran yang memotong 10 poin.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Lihat pada baris catatan itu.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil, memuat potongan "10 poin" dan sisa poin siswa 90.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52.8" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.003</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.003.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Mencatat pelanggaran siswa yang belum mendaftarkan akun</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memilih jenis pelanggaran yang statusnya sudah nonaktif.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Siswa yang belum mendaftarkan akunnya belum bisa dicatat pelanggarannya.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Ada jenis pelanggaran berstatus nonaktif.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada siswa yang datanya sudah didaftarkan admin tetapi belum membuat akun.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Kirim data catat pelanggaran dengan jenis pelanggaran nonaktif.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi jenis pelanggaran tidak aktif dan tidak dapat dipilih, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.003</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.003.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencatat pelanggaran dengan jenis pelanggaran yang tidak ada</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengirim jenis_pelanggaran_id yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Kirim data catat pelanggaran dengan jenis_pelanggaran_id yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi jenis pelanggaran tidak valid, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.004</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.004.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencatat pelanggaran untuk siswa (NISN) yang tidak ada</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengirim profil_siswa_id (NISN) yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Kirim data catat pelanggaran dengan NISN yang tidak terdaftar.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi siswa tidak valid, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52.8" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.005</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.005.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencatat pelanggaran dengan tanggal pelanggaran di masa depan</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi tanggal pelanggaran setelah hari ini.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Catat Pelanggaran, isi tanggal pelanggaran besok (setelah hari ini).</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa lalu klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11449,211 +11393,239 @@
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal tidak boleh melebihi hari ini, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa yang belum punya akun, lengkapi kolom lain, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Siswa belum terdaftar, belum bisa dicatat pelanggarannya." dan pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26.4" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.006</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.006.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memperbarui catatan pelanggaran siswa</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.004</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.004.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Memilih jenis pelanggaran yang sudah dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Jenis pelanggaran yang sudah dinonaktifkan tidak boleh dipakai lagi.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada jenis pelanggaran yang statusnya nonaktif.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa lalu klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa, pilih jenis pelanggaran yang nonaktif, lengkapi kolom lain, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Jenis pelanggaran tidak aktif dan tidak dapat dipilih." dan pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26.4" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.005</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.005.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal kejadian melebihi hari ini</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran tidak boleh dicatat untuk kejadian yang belum terjadi.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada siswa terdaftar dan jenis pelanggaran yang aktif.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa lalu klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39.6" customHeight="1" s="9">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa dan jenis pelanggaran, isi tanggal kejadian dengan tanggal setelah hari ini, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal pelanggaran tidak boleh melebihi hari ini." dan pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.006</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.006.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Mencari catatan pelanggaran berdasarkan nama siswa</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengubah catatan pada pelanggaran siswa yang sudah ada.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengetik sebagian nama siswa di kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Data pelanggaran siswa sudah ada.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Dua siswa berbeda sama-sama punya catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Pelanggaran Siswa.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil terisi data lama.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Ubah catatan pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Catatan baru yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26.4" customHeight="1" s="9">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Catatan pelanggaran berhasil diperbarui.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39.6" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.007</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.007.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mempertahankan jenis pelanggaran nonaktif yang sedang dipakai saat update</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memperbarui catatan pelanggaran tanpa mengganti jenis pelanggaran yang kini sudah nonaktif.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Jenis pelanggaran yang sedang dipakai pada catatan ini baru saja dinonaktifkan.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Edit Pelanggaran Siswa.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Form edit tampil, jenis pelanggaran nonaktif yang sedang dipakai tetap muncul sebagai pilihan.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Simpan tanpa mengganti jenis pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Field jenis pelanggaran tetap menunjuk ke jenis yang sama.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11667,75 +11639,75 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Perbarui.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Update berhasil meski jenis pelanggaran berstatus nonaktif, karena itu adalah jenis yang sedang dipakai catatan ini.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Ketik sebagian nama siswa di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Hanya catatan milik siswa yang namanya cocok yang tampil; catatan siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.008</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.008.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus catatan pelanggaran siswa</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.007</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.007.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring catatan pelanggaran berdasarkan kategori</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus satu catatan pelanggaran siswa.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menyaring daftar agar hanya menampilkan pelanggaran kategori berat.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Data pelanggaran siswa sudah ada.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya satu pelanggaran ringan (10 poin) dan satu pelanggaran berat (60 poin).</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris catatan pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11749,361 +11721,848 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Catatan pelanggaran berhasil terhapus dari database.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Pilih kategori Sanksi Berat di kolom penyaring lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Hanya baris pelanggaran berat yang tampil, ditandai potongan 60 poin; baris pelanggaran ringan 10 poin tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="25" ht="39.6" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.009</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.009.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar catatan pelanggaran berdasarkan kelas, kategori, jenis, tanggal, dan status</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.008</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.008.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring catatan pelanggaran berdasarkan tanggal kejadian</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menerapkan filter kelas, kategori, jenis pelanggaran, tanggal, dan status pada daftar catatan pelanggaran.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membatasi daftar pada satu tanggal kejadian.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Ada catatan pelanggaran dari kelas dan kategori yang berbeda-beda.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya dua pelanggaran di dua tanggal berbeda.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Daftar Pelanggaran Siswa, terapkan filter kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan catatan dari kelas yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="8" t="n">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Ganti filter ke kategori tertentu.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan catatan dengan kategori yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Pilih salah satu tanggal kejadian di kolom penyaring lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Hanya catatan yang terjadi pada tanggal itu yang tampil; catatan di tanggal lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="27" ht="39.6" customHeight="1" s="9">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Ganti filter ke jenis pelanggaran, tanggal, dan status tertentu satu per satu.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Daftar ter-filter sesuai masing-masing kriteria yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.009</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.009.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Melihat rincian sebuah catatan pelanggaran</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka rincian sebuah catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26.4" customHeight="1" s="9">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.010</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.010.001</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas tanggal pelanggaran (boundary tepat hari ini)</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Lihat pada baris catatan itu.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi nama siswa, kelasnya, nama pelanggaran, poin yang dipotong, dan sisa poinnya.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26.4" customHeight="1" s="9">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.010</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.010.001</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus catatan pelanggaran yang salah dicatat</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal pelanggaran diisi tepat hari ini — tepat di batas atas yang diperbolehkan.</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus catatan yang keliru supaya poin siswa kembali seperti semula.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26.4" customHeight="1" s="9">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris catatan itu, lalu setujui konfirmasinya.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pelanggaran siswa berhasil dihapus." dan catatan itu hilang dari daftar.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39.6" customHeight="1" s="9">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.011</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.011.001</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Daftar pelanggaran siswa masih kosong</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka daftar sebelum satu pun pelanggaran dicatat.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Belum ada satu pun catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum ada catatan pelanggaran siswa."</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.012</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.012.001</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas tanggal kejadian paling akhir</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal kejadian hari ini, tepat pada batas paling akhir yang diterima.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n">
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada siswa terdaftar dan jenis pelanggaran yang aktif.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal pelanggaran dengan tanggal hari ini.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26.4" customHeight="1" s="9">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n">
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa lalu klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal lolos validasi batas atas, pelanggaran tersimpan.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26.4" customHeight="1" s="9">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>TS.PSK.011</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>TC.PSK.011.001</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas tanggal pelanggaran (boundary 1 hari setelah hari ini)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa dan jenis pelanggaran, isi tanggal kejadian dengan tanggal hari ini, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pelanggaran siswa berhasil dicatat."</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.012</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.012.002</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas tanggal kejadian paling akhir</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal kejadian kemarin, sehari di bawah batas.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada siswa terdaftar dan jenis pelanggaran yang aktif.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa lalu klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa dan jenis pelanggaran, isi tanggal kejadian dengan tanggal kemarin, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pelanggaran siswa berhasil dicatat."</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.012</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.012.003</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas tanggal kejadian paling akhir</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal pelanggaran diisi besok — tepat 1 hari di atas batas atas.</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal kejadian besok, sehari di atas batas.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada siswa terdaftar dan jenis pelanggaran yang aktif.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal pelanggaran dengan tanggal besok.</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="39.6" customHeight="1" s="9">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n">
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa lalu klik tombol Catat Pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman catat pelanggaran tampil berisi kolom siswa, jenis pelanggaran, tanggal, dan catatan.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Simpan.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal tidak boleh melebihi hari ini, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Pilih siswa dan jenis pelanggaran, isi tanggal kejadian dengan tanggal besok, lalu klik Simpan.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal pelanggaran tidak boleh melebihi hari ini." dan pelanggaran tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.013</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.013.001</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah sisa poin siswa</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Potongan yang pas menghabiskan poin membuat sisa poin siswa nol.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Poin siswa masih penuh 100, lalu dicatat pelanggaran yang memotong 100 poin.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Lihat pada baris catatan itu.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil dan sisa poin siswa 0.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TS.PLS.013</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>TC.PLS.013.002</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah sisa poin siswa</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Potongan yang melebihi poin tersisa tidak membuat sisa poin menjadi minus.</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Poin siswa sudah habis karena potongan 100 poin, lalu dicatat lagi pelanggaran yang memotong 10 poin.</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Pelanggaran Siswa.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Pelanggaran Siswa tampil berisi daftar catatan pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Lihat pada baris catatan yang terakhir.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil dan sisa poin siswa tetap 0, bukan angka minus.</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="110">
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="D40:D41"/>
     <mergeCell ref="F15:F16"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G17:G18"/>
     <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A29:A30"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B9:B11"/>
     <mergeCell ref="C15:C16"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="G40:G41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -12455,21 +12455,67 @@
   <mergeCells count="110">
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D23:D24"/>
     <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E23:E24"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="G38:G39"/>
-    <mergeCell ref="D36:D37"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B23:B24"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="D32:D33"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="E9:E12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="E15:E16"/>
@@ -12477,90 +12523,44 @@
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:D16"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="B40:B41"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="F29:F30"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="F9:F12"/>
-    <mergeCell ref="E25:E26"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="G9:G12"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="F34:F35"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="D40:D41"/>
     <mergeCell ref="F15:F16"/>
-    <mergeCell ref="B27:B28"/>
     <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="D27:D28"/>
     <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G34:G35"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="F32:F33"/>
-    <mergeCell ref="E38:E39"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="E40:E41"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="G29:G30"/>
-    <mergeCell ref="E27:E28"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="F27:F28"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="F38:F39"/>
-    <mergeCell ref="C17:C18"/>
     <mergeCell ref="E36:E37"/>
-    <mergeCell ref="D25:D26"/>
     <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
-    <mergeCell ref="A4:E4"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B32:B33"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="G27:G28"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C34:C35"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="D23:D24"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="G40:G41"/>
   </mergeCells>
@@ -12574,7 +12574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -12614,7 +12614,7 @@
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis, State Transition Testing</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -12684,410 +12684,410 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.TTK.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.TTK.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah berkas PDF tata tertib baru</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah tata tertib sebagai draft</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi judul dan mengunggah berkas PDF tata tertib.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas tata tertib tanpa langsung mengaktifkannya, sehingga siswa belum bisa membacanya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Berkas tata tertib berbentuk PDF sudah disiapkan.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Form unggah tata tertib tampil.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="8" t="n">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Isi judul dan pilih berkas PDF.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Judul yang diketik dan nama berkas yang dipilih tampil pada form.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF, biarkan penanda aktif tidak dicentang, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah." dan tata tertib itu tampil di daftar dengan status Draft.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Berkas tata tertib berhasil tersimpan dan tampil di daftar.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.002</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah tata tertib dan langsung mengaktifkannya</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas sekaligus mengaktifkannya, sehingga langsung bisa dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Berkas tata tertib berbentuk PDF sudah disiapkan.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.002</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.002.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah tata tertib tanpa mengisi judul</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF, centang penanda aktif, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah." dan tata tertib itu tampil di daftar dengan status Aktif.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah berkas yang bukan PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah berkas PDF tanpa mengisi judul.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib hanya boleh diunggah dalam bentuk PDF.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib, biarkan judul kosong.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Kolom judul tetap kosong.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Pilih berkas PDF dan klik Upload.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi judul wajib diisi, berkas tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.003</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.003.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah berkas yang bukan PDF</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas yang bukan PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File tata tertib harus berupa PDF." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah tanpa mengisi judul</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memilih berkas berformat selain PDF (misal .docx).</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengosongkan judul lalu mengunggah berkas.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib, isi judul.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Judul yang diketik tampil di kolom.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Pilih berkas berformat .docx dan klik Upload.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi berkas harus PDF, berkas tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.004</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.004.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah tata tertib tanpa memilih berkas</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengirim form tanpa memilih berkas PDF sama sekali.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Kosongkan judul, pilih berkas PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Judul tata tertib wajib diisi." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mengaktifkan tata tertib menonaktifkan yang lama</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Hanya satu tata tertib yang boleh aktif pada satu waktu, supaya siswa tidak bingung membaca versi mana.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu tata tertib yang aktif dan satu lagi yang masih draft.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib, isi judul, jangan pilih berkas.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Judul yang diketik tampil di kolom, kolom berkas tetap kosong.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8" t="n">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi berkas PDF wajib diunggah, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.005</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.005.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus tata tertib beserta berkasnya di storage</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus satu tata tertib dari daftar.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Tata tertib dengan berkas PDF sudah ada.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris tata tertib.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Muncul konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Aktifkan pada baris tata tertib yang masih draft.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil dipublikasikan."</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13101,376 +13101,404 @@
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi daftar.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Tata tertib yang baru diaktifkan berstatus Aktif, sedangkan tata tertib yang sebelumnya aktif berubah menjadi Draft.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39.6" customHeight="1" s="9">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.006</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.006.001</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Menonaktifkan tata tertib yang sedang aktif</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menonaktifkan tata tertib supaya tidak lagi dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada tata tertib yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Konfirmasi hapus.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Data tata tertib terhapus dari database beserta berkas PDF-nya di storage.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39.6" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.006</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.006.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan melihat daftar tata tertib yang sudah diunggah</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Nonaktifkan pada baris tata tertib itu.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil dinonaktifkan." dan statusnya berubah menjadi Draft.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26.4" customHeight="1" s="9">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.007</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.007.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus tata tertib</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan membuka halaman daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus berkas tata tertib yang tidak dipakai lagi.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Ada tata tertib yang sudah diunggah sebelumnya.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu tata tertib di daftar.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Daftar tata tertib yang pernah diunggah tampil lengkap dengan status draft/aktif.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.007</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.007.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum judul tata tertib (boundary tepat 200 karakter)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris tata tertib itu, lalu setujui konfirmasinya.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil dihapus." dan tata tertib itu hilang dari daftar.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39.6" customHeight="1" s="9">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.008</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.008.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Daftar tata tertib masih kosong</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Judul diisi tepat 200 karakter — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka halaman sebelum satu pun tata tertib diunggah.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Belum ada satu pun tata tertib.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum ada file tata tertib."</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26.4" customHeight="1" s="9">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Siswa membaca tata tertib yang aktif</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib yang aktif itulah yang dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ada tata tertib yang statusnya aktif.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tata tertib tampil berisi judul tata tertib yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26.4" customHeight="1" s="9">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.010</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.010.001</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib draft tidak dibaca siswa</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib yang masih draft belum boleh dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Tata tertib yang ada statusnya masih draft.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Judul tata tertib yang masih draft tidak tampil di halaman siswa.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26.4" customHeight="1" s="9">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.011</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.011.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas PDF</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Berkas berukuran tepat di bawah batas 10 MB.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Isi judul tepat 200 karakter, pilih berkas PDF.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom judul.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Judul lolos validasi maksimum, tata tertib tersimpan.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.008</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.008.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Batas panjang maksimum judul tata tertib (boundary di atas 200 karakter)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Judul diisi 201 karakter — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Isi judul 201 karakter, pilih berkas PDF.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Karakter yang diketik tampil di kolom judul.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39.6" customHeight="1" s="9">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi judul melebihi batas maksimum, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.009</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.009.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran maksimum berkas PDF (boundary tepat 10240 KB)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Berkas PDF berukuran tepat 10240 KB (10 MB) — tepat di batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF berukuran tepat 10240 KB.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Nama berkas yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Ukuran berkas lolos validasi maksimum, tata tertib tersimpan.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26.4" customHeight="1" s="9">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.010</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.010.001</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran maksimum berkas PDF (boundary di atas 10240 KB)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Berkas PDF berukuran 10241 KB — tepat di atas batas maksimum.</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF berukuran 10241 KB.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Nama berkas yang dipilih tampil di form.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13484,75 +13512,75 @@
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi ukuran PDF melebihi 10 MB, data tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran sedikit di bawah 10 MB, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="29" ht="39.6" customHeight="1" s="9">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>TS.TTK.011</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.011.001</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Mengunggah tata tertib baru sebagai aktif otomatis menonaktifkan tata tertib yang sebelumnya aktif</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.011.002</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas PDF</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah tata tertib baru dengan opsi publikasikan dicentang, sementara ada tata tertib lain yang sedang aktif.</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Ada satu tata tertib berstatus aktif (published).</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="n">
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Berkas berukuran tepat 10 MB, pas pada batas.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib, isi judul dan berkas baru, centang Publikasikan.</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Data yang diisi tampil pada form, checkbox Publikasikan tercentang.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13566,185 +13594,157 @@
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>Tata tertib baru langsung berstatus aktif, tata tertib lama yang sebelumnya aktif otomatis berubah menjadi draft.</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran tepat 10 MB, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="31" ht="52.8" customHeight="1" s="9">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.011</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.011.003</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas PDF</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Berkas berukuran sedikit di atas 10 MB.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="39.6" customHeight="1" s="9">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran sedikit di atas 10 MB, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Ukuran PDF maksimal 10 MB." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="39.6" customHeight="1" s="9">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>TS.TTK.012</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>TC.TTK.012.001</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Mempublikasikan tata tertib berstatus draft membuatnya aktif dan menonaktifkan yang lain</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang judul</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menekan tombol Publikasikan pada tata tertib berstatus draft, sementara ada tata tertib lain yang sedang aktif.</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Ada satu tata tertib aktif dan satu tata tertib draft.</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Judul sepanjang 200 karakter, tepat pada batas.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Publikasikan pada tata tertib berstatus draft.</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>Tata tertib yang dipilih berubah menjadi aktif, tata tertib yang sebelumnya aktif otomatis berubah menjadi draft.</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="39.6" customHeight="1" s="9">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.013</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.013.001</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Menonaktifkan tata tertib yang aktif mengembalikannya menjadi draft</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan menekan tombol Nonaktifkan pada tata tertib yang sedang berstatus aktif.</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Tata tertib berstatus aktif (published).</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Nonaktifkan pada tata tertib yang sedang aktif.</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>Status tata tertib berubah kembali menjadi draft.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="39.6" customHeight="1" s="9">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TS.TTK.014</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>TC.TTK.014.001</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Mengunggah tata tertib baru sebagai draft tidak mengganggu tata tertib yang sedang aktif</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah tata tertib baru tanpa mencentang opsi publikasikan, sementara ada tata tertib lain yang sedang aktif.</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>State Transition Testing</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Ada satu tata tertib berstatus aktif.</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Tata Tertib, isi judul dan berkas baru, jangan centang Publikasikan.</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>Data yang diisi tampil pada form, checkbox Publikasikan tidak tercentang.</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13758,109 +13758,198 @@
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Upload.</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>Tata tertib baru tersimpan berstatus draft, tata tertib lama yang sedang aktif tetap aktif tanpa perubahan.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul sepanjang 200 karakter, pilih berkas PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.012</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.012.002</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang judul</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Judul sepanjang 201 karakter, sekarakter di atas batas.</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul sepanjang 201 karakter, pilih berkas PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Judul tata tertib maksimal 200 karakter." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="B12:B13"/>
+  <mergeCells count="89">
+    <mergeCell ref="F17:F19"/>
     <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B14:B15"/>
     <mergeCell ref="B29:B30"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F9:F11"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F31:F32"/>
     <mergeCell ref="G33:G34"/>
-    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="C27:C28"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B35:B36"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="F33:F34"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G27:G28"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="B33:B34"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
     <mergeCell ref="D29:D30"/>
-    <mergeCell ref="F14:F15"/>
     <mergeCell ref="F29:F30"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F12:F13"/>
     <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G20:G21"/>
     <mergeCell ref="G29:G30"/>
     <mergeCell ref="D33:D34"/>
     <mergeCell ref="F27:F28"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="G17:G19"/>
     <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -10601,7 +10601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -10641,7 +10641,7 @@
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -10711,287 +10711,1080 @@
       </c>
     </row>
     <row r="9" ht="52.8" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.MOS.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.MOS.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan melihat daftar monitoring siswa dari seluruh sekolah tanpa batas kelas/tingkat</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Memantau seluruh siswa beserta kehadiran hari ini</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan membuka halaman monitoring dan melihat siswa dari semua tingkat kelas.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan memantau kehadiran hari ini untuk seluruh siswa sekolah.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Ada siswa terdaftar di kelas tingkat 10 dan tingkat 12.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Hari ini termasuk hari absensi dan seorang siswa sudah absen hadir.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring Siswa.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Daftar siswa dari seluruh tingkat kelas tampil sekaligus, tidak dibatasi tingkat/kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, kelasnya, dan status kehadirannya Hadir tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39.6" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.MOS.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.MOS.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar monitoring berdasarkan nama siswa</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Melihat sisa poin siswa setelah dipotong pelanggaran</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mencari siswa berdasarkan kata kunci nama.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa mulai dari 100 dan berkurang sesuai pelanggaran yang tercatat.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Ada beberapa siswa dengan nama berbeda.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya satu pelanggaran yang memotong 10 poin.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring Siswa, isi kata kunci pencarian nama.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan siswa yang namanya cocok dengan kata kunci.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52.8" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi nama siswa, riwayat pelanggarannya, dan sisa poinnya 90.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.MOS.003</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.MOS.003.001</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar monitoring berdasarkan kelas</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa bertambah setelah pengajuan poin disetujui</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter daftar monitoring dengan memilih satu kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Sisa poin siswa dihitung dari poin awal 100, dikurangi pelanggaran, ditambah pengajuan poin yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Ada siswa dari lebih dari satu kelas.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran yang memotong 20 poin dan pengajuan poin yang sudah disetujui sebesar 5 poin.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring Siswa, pilih filter kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan siswa dari kelas yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52.8" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi alasan penambahan poin dan sisa poin siswa 85.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>TS.MOS.004</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TC.MOS.004.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan melihat detail monitoring siswa berisi agregat poin dan absensi</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Siswa yang belum mendaftarkan akun tidak dipantau</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Siswa yang datanya sudah didaftarkan admin tetapi belum membuat akun belum ikut dipantau.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada siswa yang belum membuat akun.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang sudah punya akun yang tampil; siswa yang belum membuat akun tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mencari siswa berdasarkan nama</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan membuka detail seorang siswa untuk melihat ringkasan poin dan riwayat absensi.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengetik sebagian nama siswa di kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Data siswa sudah ada.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada lebih dari satu siswa terdaftar.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Klik nama siswa pada daftar monitoring.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Halaman detail siswa tampil berisi biodata, agregat poin pelanggaran/pengajuan poin, dan 30 riwayat absensi terakhir.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.MOS.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.MOS.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Halaman detail monitoring menyediakan tautan untuk mencatat pelanggaran baru</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Ketik sebagian nama siswa di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang namanya cocok yang tampil; siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Mencari siswa berdasarkan NIS</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan melihat tombol/tautan catat pelanggaran baru pada halaman detail siswa.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Pencarian juga menerima NIS, bukan hanya nama.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Data siswa sudah ada.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada lebih dari satu siswa terdaftar.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman detail monitoring siswa.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Tersedia tautan menuju form catat pelanggaran baru untuk siswa yang sedang dilihat.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Ketik NIS seorang siswa di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa dengan NIS itu yang tampil; siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring siswa berdasarkan kelas</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membatasi daftar pada satu kelas.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada siswa di dua kelas berbeda.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Pilih sebuah kelas di kolom penyaring lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa dari kelas itu yang tampil; siswa kelas lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.008</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Melihat riwayat kehadiran seorang siswa</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka rincian siswa untuk menelusuri kehadirannya.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya satu catatan kehadiran berstatus alpha.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi bagian Riwayat Kehadiran, dan catatan alpha siswa itu tampil di dalamnya.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Pencarian tidak menemukan siswa</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mencari nama yang tidak ada.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Ketik nama yang tidak ada di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Tidak ada data siswa ditemukan."</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.010</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.010.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Batas ambang peringatan alpha</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Alpha dua kali, sekali di bawah ambang peringatan.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya dua catatan alpha pada semester berjalan.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Siswa tampil di tabel tanpa penanda peringatan alpha.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.010</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.010.002</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Batas ambang peringatan alpha</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Alpha tiga kali, tepat pada ambang peringatan.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya tiga catatan alpha pada semester berjalan.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Siswa tampil dengan penanda "Peringatan alpha 3x".</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.MOS.011</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.MOS.011.001</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Batas semester penghitungan alpha</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Alpha dari semester sebelumnya tidak ikut dihitung ke ambang peringatan.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya tiga catatan alpha, tetapi seluruhnya jatuh di semester sebelumnya.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil berisi daftar siswa.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Siswa tampil di tabel tanpa penanda peringatan alpha, karena alpha yang dihitung hanya yang jatuh di semester berjalan.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="89">
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16435,7 +17228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -16468,7 +17261,7 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : Kesiswaan &gt; Laporan Pelanggaran</t>
+          <t>Page : Kesiswaan &gt; Laporan</t>
         </is>
       </c>
     </row>
@@ -16545,495 +17338,383 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.LAP.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.LAP.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan melihat laporan pelanggaran dari seluruh sekolah tanpa batas tingkat</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat laporan pelanggaran seluruh sekolah</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan membuka halaman laporan dan melihat pelanggaran dari semua tingkat kelas.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menyusun laporan pelanggaran seluruh siswa.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Ada catatan pelanggaran dari siswa tingkat 10 dan tingkat 12.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Seorang siswa punya pelanggaran yang memotong 10 poin.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Daftar pelanggaran dari seluruh tingkat kelas tampil sekaligus.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan tabel pelanggaran.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, kelasnya, nama pelanggaran, dan potongan poinnya tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39.6" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.LAP.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.LAP.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan berdasarkan rentang tanggal mulai dan selesai</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Laporan memuat penambahan poin yang disetujui</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi filter tanggal mulai dan selesai pada halaman laporan.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Selain pelanggaran, laporan juga memuat penambahan poin yang sudah disetujui kesiswaan.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran di dalam dan di luar rentang tanggal yang akan difilter.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin yang sudah disetujui sebesar 5 poin.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, isi tanggal mulai dan selesai.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran dalam rentang tanggal yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan tabel Penambahan Poin (Disetujui).</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, alasan pengajuan, dan penambahan poinnya tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.LAP.003</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.LAP.003.001</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan berdasarkan kelas</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring laporan berdasarkan rentang tanggal</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan memilih satu kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membatasi laporan pada rentang tanggal tertentu.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran dari lebih dari satu kelas.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran di dua bulan berbeda.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, pilih filter kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran dari kelas yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang hanya memuat salah satu pelanggaran, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran di dalam rentang yang tampil; pelanggaran di luar rentang tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>TS.LAP.004</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TC.LAP.004.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan berdasarkan tingkat</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring laporan berdasarkan kelas</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan memilih satu tingkat kelas tertentu.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membatasi laporan pada satu kelas.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran dari tingkat kelas yang berbeda-beda.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada pelanggaran dari siswa di dua kelas berbeda.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, pilih filter tingkat tertentu.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran dari siswa tingkat yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih sebuah kelas di kolom penyaring, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran siswa dari kelas itu yang tampil; pelanggaran kelas lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52.8" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>TS.LAP.005</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>TC.LAP.005.001</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan berdasarkan kategori pelanggaran</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring laporan berdasarkan tingkat</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan memilih kategori pelanggaran tertentu.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membatasi laporan pada satu tingkat kelas.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran dari kategori yang berbeda-beda.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada pelanggaran dari siswa di tingkat 10 dan tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, pilih filter kategori tertentu.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran dengan kategori yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan berdasarkan status</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan memilih status disetujui.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Ada pelanggaran dengan status berbeda-beda.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, pilih filter status Disetujui.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Daftar hanya menampilkan pelanggaran berstatus disetujui.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan kelas_id yang tidak ada</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengirim kelas_id yang tidak ada di database sebagai filter.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Kirim request laporan dengan kelas_id yang tidak ada di database.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi kelas tidak ditemukan, laporan tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.008</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.008.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan tingkat yang tidak valid</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengirim nilai tingkat di luar pilihan 10/11/12.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Kirim request laporan dengan tingkat = "13" (nilai di luar pilihan form).</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tingkat tidak valid, laporan tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52.8" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.009</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.009.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan memfilter laporan dengan tanggal selesai sebelum tanggal mulai</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengisi tanggal selesai yang lebih awal daripada tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, isi tanggal mulai dan tanggal selesai yang lebih awal.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17047,185 +17728,157 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal selesai tidak boleh sebelum tanggal mulai, laporan tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tingkat 11 di kolom penyaring, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran siswa tingkat 11 yang tampil; pelanggaran tingkat lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.010</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.010.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengekspor laporan pelanggaran ke Excel</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring laporan berdasarkan kategori</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunduh laporan pelanggaran dalam format Excel beserta sisa poin per siswa.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membatasi laporan pada kategori sanksi tertentu.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Ada data pelanggaran yang sesuai dengan filter aktif.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya satu pelanggaran ringan dan satu pelanggaran berat.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, klik tombol Export Excel.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Berkas Excel berhasil terunduh berisi data pelanggaran dan sisa poin tiap siswa.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="20" ht="39.6" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.011</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.011.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengekspor laporan pelanggaran ke PDF</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunduh laporan pelanggaran dalam format PDF.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih kategori Sanksi Berat di kolom penyaring, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pelanggaran kategori berat yang tampil; pelanggaran ringan tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39.6" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai lebih awal daripada tanggal mulai</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan memilih tanggal selesai yang jatuh sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Ada data pelanggaran yang sesuai dengan filter aktif.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Laporan Pelanggaran, klik tombol Export PDF.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Berkas PDF berhasil terunduh berisi ringkasan data pelanggaran.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="39.6" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.012</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.012.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah rentang tanggal (boundary tanggal selesai sama dengan tanggal mulai)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal selesai diisi sama persis dengan tanggal mulai — tepat di batas yang diperbolehkan.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai dan tanggal selesai dengan tanggal yang sama.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17239,75 +17892,75 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Filter lolos validasi, laporan tampil tanpa error.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai yang lebih awal daripada tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan laporan tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="23" ht="39.6" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.LAP.013</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.LAP.013.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah rentang tanggal (boundary tanggal selesai 1 hari sebelum tanggal mulai)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Tanggal selesai diisi 1 hari sebelum tanggal mulai — tepat di bawah batas yang diperbolehkan.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Kesiswaan sudah login.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.008</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh laporan dalam berkas Excel</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunduh laporan untuk diarsipkan.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai, lalu isi tanggal selesai 1 hari sebelumnya.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Tanggal yang dipilih tampil pada kolom masing-masing.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17321,53 +17974,766 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Terapkan filter.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal selesai tidak boleh sebelum tanggal mulai, laporan tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Export Excel.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Berkas Excel laporan pelanggaran terunduh.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh laporan dalam berkas PDF</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunduh laporan dalam bentuk PDF.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu pelanggaran tercatat.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Export PDF.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Berkas PDF laporan pelanggaran terunduh.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.010</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.010.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Laporan tidak menemukan data</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka laporan sebelum ada satu pun pelanggaran maupun penambahan poin.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Belum ada satu pun pelanggaran maupun penambahan poin.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Tidak ada data laporan." pada tabel pelanggaran, dan keterangan bahwa belum ada penambahan poin yang disetujui pada rentang itu.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.011</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.011.001</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal laporan</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi tepat pada tanggal mulai ikut masuk laporan.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran tepat pada tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal mulainya sama dengan tanggal pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.011</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.011.002</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal laporan</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi sehari sebelum tanggal mulai tidak masuk laporan.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran sehari sebelum tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang dimulai sehari setelah pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tidak tampil, dan muncul keterangan "Tidak ada data laporan."</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.012</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.012.001</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal laporan</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi tepat pada tanggal selesai ikut masuk laporan.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran tepat pada tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal selesainya sama dengan tanggal pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.012</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.012.002</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal laporan</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran yang terjadi sehari setelah tanggal selesai tidak masuk laporan.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran sehari setelah tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang berakhir sehari sebelum pelanggaran itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran tersebut tidak tampil, dan muncul keterangan "Tidak ada data laporan."</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.013</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.013.001</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal laporan</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai boleh sama dengan tanggal mulai, menghasilkan laporan satu hari.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran pada tanggal itu.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal mulai dan tanggal selesai yang sama, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran pada tanggal itu tampil tanpa pesan kesalahan.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.LAP.013</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.LAP.013.002</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal laporan</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai sehari lebih awal daripada tanggal mulai ditolak.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Laporan Kesiswaan tampil berisi tabel pelanggaran dan tabel penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai satu hari sebelum tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan laporan tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="E17:E18"/>
+  <mergeCells count="110">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G36:G37"/>
     <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F36:F37"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E38:E39"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C34:C35"/>
     <mergeCell ref="D23:D24"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
     <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -21,17 +21,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Wali" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poin Pelanggaran Wali" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pengajuan Poin Wali" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jenis Pelanggaran" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Siswa" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pelanggaran Siswa Kesiswaan" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tata Tertib Kesiswaan" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan Pelanggaran" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Absensi Bk" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Poin Bk" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Bk" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absensi Siswa" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riwayat Absensi Siswa" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poin Siswa" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persetujuan Poin" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jenis Pelanggaran" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Siswa" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pelanggaran Siswa Kesiswaan" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tata Tertib Kesiswaan" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan Pelanggaran" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Absensi Bk" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Poin Bk" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap Absensi Bk" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absensi Siswa" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riwayat Absensi Siswa" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poin Siswa" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -8709,6 +8710,1221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
+    <col width="19.6640625" customWidth="1" style="9" min="2" max="2"/>
+    <col width="26" customWidth="1" style="9" min="3" max="3"/>
+    <col width="12" customWidth="1" style="9" min="4" max="4"/>
+    <col width="40" customWidth="1" style="9" min="5" max="5"/>
+    <col width="17.33203125" customWidth="1" style="9" min="6" max="6"/>
+    <col width="30" customWidth="1" style="9" min="7" max="7"/>
+    <col width="7.88671875" customWidth="1" style="9" min="8" max="8"/>
+    <col width="26" customWidth="1" style="9" min="9" max="9"/>
+    <col width="30" customWidth="1" style="9" min="10" max="10"/>
+    <col width="16" customWidth="1" style="9" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1" s="9">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Mengajukan Penambahan Poin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1" s="9">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" s="9">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Persetujuan Poin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1" s="9">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1" s="9">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="9"/>
+    <row r="8" ht="31.2" customHeight="1" s="9">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="39.6" customHeight="1" s="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat pengajuan poin yang menunggu keputusan</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan memeriksa pengajuan penambahan poin yang dikirim wali kelas.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Persetujuan Poin tampil berisi pengajuan yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.8" customHeight="1" s="9">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi daftar.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, kelasnya, alasan pengajuan, dan nama wali kelas yang mengajukan tampil di daftar.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39.6" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.002</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Menyetujui pengajuan sambil menentukan besar poinnya</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Wali kelas hanya mengirim alasannya; besar poinnya ditentukan kesiswaan saat menyetujui.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Persetujuan Poin tampil berisi pengajuan yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Terima pada baris pengajuan itu.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul jendela Terima Pengajuan Poin berisi kolom jumlah poin.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Isi jumlah poin, lalu klik Terima Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil diterima." dan pengajuan itu hilang dari daftar yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.003</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.003.001</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa bertambah setelah pengajuan disetujui</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Sisa poin siswa dihitung dari poin awal 100, dikurangi pelanggaran, ditambah pengajuan yang disetujui.</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Siswa punya pelanggaran yang memotong 20 poin, dan pengajuan poinnya baru saja disetujui sebesar 5 poin.</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring Siswa.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring Siswa tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.4" customHeight="1" s="9">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil dan sisa poin siswa 85.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.004</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.004.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Menolak pengajuan dengan menuliskan alasannya</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Penolakan wajib disertai alasan supaya wali kelas tahu sebabnya.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Persetujuan Poin tampil berisi pengajuan yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Tolak pada baris pengajuan itu.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Muncul jendela Tolak Pengajuan Poin berisi kolom alasan penolakan.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Tulis alasan penolakan, lalu klik Tolak Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil ditolak." dan pengajuan itu hilang dari daftar yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.005</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.005.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Pengajuan yang sudah diputuskan tidak bisa diputuskan lagi</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Satu pengajuan hanya boleh diputuskan sekali.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sebuah pengajuan baru saja disetujui.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Persetujuan Poin tampil berisi pengajuan yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="79.2" customHeight="1" s="9">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Cari pengajuan yang tadi diputuskan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Pengajuan itu tidak ada lagi di daftar yang menunggu keputusan, sehingga tidak ada tombol untuk memutuskannya kedua kali. Muncul keterangan "Tidak ada pengajuan poin yang menunggu persetujuan."</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.006</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.006.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Melihat riwayat keputusan pengajuan poin</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menelusuri kembali pengajuan yang sudah diputuskan.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sebuah pengajuan sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39.6" customHeight="1" s="9">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, alasan pengajuan, dan status Disetujui tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.007</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.007.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring riwayat berdasarkan status</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menyaring riwayat agar hanya menampilkan pengajuan yang ditolak.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan yang disetujui dan satu lagi yang ditolak.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Pengajuan Poin.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26.4" customHeight="1" s="9">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Pilih status Ditolak di kolom penyaring lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Hanya pengajuan yang ditolak yang tampil; pengajuan yang disetujui tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.008</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.008.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Tidak ada pengajuan yang menunggu keputusan</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka halaman saat tidak ada pengajuan yang tertunda.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Tidak ada satu pun pengajuan yang menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Tidak ada pengajuan poin yang menunggu persetujuan."</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.009</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.009.001</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Batas besar poin yang diberikan</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Poin 1, tepat pada batas terendah yang boleh diberikan.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin lalu klik tombol Terima pada baris pengajuan itu.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Jendela Terima Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Isi jumlah poin 1, lalu klik Terima Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil diterima."</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.009</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.009.002</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Batas besar poin yang diberikan</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Poin 100, tepat pada batas tertinggi yang boleh diberikan.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin lalu klik tombol Terima pada baris pengajuan itu.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Jendela Terima Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Isi jumlah poin 100, lalu klik Terima Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil diterima."</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.010</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.010.001</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang alasan penolakan</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Alasan penolakan sepanjang 1000 karakter, tepat pada batas.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin lalu klik tombol Tolak pada baris pengajuan itu.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Jendela Tolak Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Tulis alasan penolakan sepanjang 1000 karakter, lalu klik Tolak Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Pengajuan penambahan poin berhasil ditolak."</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.PSP.010</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.PSP.010.002</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang alasan penolakan</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Alasan penolakan sepanjang 1001 karakter, sekarakter di atas batas.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada satu pengajuan poin dari wali kelas yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Persetujuan Poin lalu klik tombol Tolak pada baris pengajuan itu.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Jendela Tolak Pengajuan Poin tampil.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Tulis alasan penolakan sepanjang 1001 karakter, lalu klik Tolak Pengajuan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Alasan penolakan maksimal 1000 karakter." dan pengajuan tetap menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="82">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="A30:A31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -10595,7 +11811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11790,7 +13006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13356,1393 +14572,6 @@
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="G40:G41"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
-    <col width="19.6640625" customWidth="1" style="9" min="2" max="2"/>
-    <col width="26" customWidth="1" style="9" min="3" max="3"/>
-    <col width="12" customWidth="1" style="9" min="4" max="4"/>
-    <col width="40" customWidth="1" style="9" min="5" max="5"/>
-    <col width="17.33203125" customWidth="1" style="9" min="6" max="6"/>
-    <col width="30" customWidth="1" style="9" min="7" max="7"/>
-    <col width="7.88671875" customWidth="1" style="9" min="8" max="8"/>
-    <col width="26" customWidth="1" style="9" min="9" max="9"/>
-    <col width="30" customWidth="1" style="9" min="10" max="10"/>
-    <col width="16" customWidth="1" style="9" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21" customHeight="1" s="9">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Test Case - Fitur Mengunggah Berkas Tata Tertib Sekolah</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="21" customHeight="1" s="9">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Website : Sentri Siswa (sentrisiswav2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" s="9">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Page : Kesiswaan &gt; Tata Tertib</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1" s="9">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="12.9" customHeight="1" s="9">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Format Test Case</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" s="9"/>
-    <row r="8" ht="31.2" customHeight="1" s="9">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Scenario ID</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Case ID</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>Pre Condition</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>Steps Description</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.001</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.001.001</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Mengunggah tata tertib sebagai draft</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah berkas tata tertib tanpa langsung mengaktifkannya, sehingga siswa belum bisa membacanya.</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk. Berkas tata tertib berbentuk PDF sudah disiapkan.</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF, biarkan penanda aktif tidak dicentang, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil diunggah." dan tata tertib itu tampil di daftar dengan status Draft.</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.002</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.002.001</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Mengunggah tata tertib dan langsung mengaktifkannya</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengunggah berkas sekaligus mengaktifkannya, sehingga langsung bisa dibaca siswa.</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk. Berkas tata tertib berbentuk PDF sudah disiapkan.</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF, centang penanda aktif, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil diunggah." dan tata tertib itu tampil di daftar dengan status Aktif.</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1" s="9">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.003</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.003.001</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Mengunggah berkas yang bukan PDF</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Tata tertib hanya boleh diunggah dalam bentuk PDF.</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1" s="9">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas yang bukan PDF, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "File tata tertib harus berupa PDF." dan tata tertib tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.004</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.004.001</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Mengunggah tanpa mengisi judul</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan mengosongkan judul lalu mengunggah berkas.</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>Kosongkan judul, pilih berkas PDF, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Judul tata tertib wajib diisi." dan tata tertib tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.005</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.005.001</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Mengaktifkan tata tertib menonaktifkan yang lama</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Hanya satu tata tertib yang boleh aktif pada satu waktu, supaya siswa tidak bingung membaca versi mana.</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk. Sudah ada satu tata tertib yang aktif dan satu lagi yang masih draft.</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26.4" customHeight="1" s="9">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>Klik tombol Aktifkan pada baris tata tertib yang masih draft.</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil dipublikasikan."</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>Perhatikan isi daftar.</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
-        <is>
-          <t>Tata tertib yang baru diaktifkan berstatus Aktif, sedangkan tata tertib yang sebelumnya aktif berubah menjadi Draft.</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39.6" customHeight="1" s="9">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.006</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.006.001</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Menonaktifkan tata tertib yang sedang aktif</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan menonaktifkan tata tertib supaya tidak lagi dibaca siswa.</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk. Ada tata tertib yang sedang aktif.</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>Klik tombol Nonaktifkan pada baris tata tertib itu.</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil dinonaktifkan." dan statusnya berubah menjadi Draft.</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.007</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.007.001</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Menghapus tata tertib</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan menghapus berkas tata tertib yang tidak dipakai lagi.</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk. Sudah ada satu tata tertib di daftar.</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>Klik tombol Hapus pada baris tata tertib itu, lalu setujui konfirmasinya.</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil dihapus." dan tata tertib itu hilang dari daftar.</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39.6" customHeight="1" s="9">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.008</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.008.001</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Daftar tata tertib masih kosong</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan membuka halaman sebelum satu pun tata tertib diunggah.</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk. Belum ada satu pun tata tertib.</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>Muncul keterangan "Belum ada file tata tertib."</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.009</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.009.001</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Siswa membaca tata tertib yang aktif</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Tata tertib yang aktif itulah yang dibaca siswa.</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>Siswa sedang masuk. Ada tata tertib yang statusnya aktif.</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>Halaman tata tertib tampil berisi judul tata tertib yang sedang aktif.</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26.4" customHeight="1" s="9">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.010</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.010.001</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Tata tertib draft tidak dibaca siswa</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>Tata tertib yang masih draft belum boleh dibaca siswa.</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>Siswa sedang masuk. Tata tertib yang ada statusnya masih draft.</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>Judul tata tertib yang masih draft tidak tampil di halaman siswa.</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26.4" customHeight="1" s="9">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.011</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.011.001</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Batas ukuran berkas PDF</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Berkas berukuran tepat di bawah batas 10 MB.</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="39.6" customHeight="1" s="9">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF berukuran sedikit di bawah 10 MB, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="39.6" customHeight="1" s="9">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.011</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.011.002</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Batas ukuran berkas PDF</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Berkas berukuran tepat 10 MB, pas pada batas.</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="52.8" customHeight="1" s="9">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF berukuran tepat 10 MB, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="52.8" customHeight="1" s="9">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.011</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.011.003</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Batas ukuran berkas PDF</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>Berkas berukuran sedikit di atas 10 MB.</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="39.6" customHeight="1" s="9">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul, pilih berkas PDF berukuran sedikit di atas 10 MB, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Ukuran PDF maksimal 10 MB." dan tata tertib tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="39.6" customHeight="1" s="9">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.012</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.012.001</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Batas panjang judul</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>Judul sepanjang 200 karakter, tepat pada batas.</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="52.8" customHeight="1" s="9">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul sepanjang 200 karakter, pilih berkas PDF, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>TS.TTK.012</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>TC.TTK.012.002</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>Batas panjang judul</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>Judul sepanjang 201 karakter, sekarakter di atas batas.</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>Kesiswaan sedang masuk.</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Tata Tertib.</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>Isi judul sepanjang 201 karakter, pilih berkas PDF, lalu klik Unggah.</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Judul tata tertib maksimal 200 karakter." dan tata tertib tidak tersimpan.</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A6:K7"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17228,6 +17057,1393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
+    <col width="19.6640625" customWidth="1" style="9" min="2" max="2"/>
+    <col width="26" customWidth="1" style="9" min="3" max="3"/>
+    <col width="12" customWidth="1" style="9" min="4" max="4"/>
+    <col width="40" customWidth="1" style="9" min="5" max="5"/>
+    <col width="17.33203125" customWidth="1" style="9" min="6" max="6"/>
+    <col width="30" customWidth="1" style="9" min="7" max="7"/>
+    <col width="7.88671875" customWidth="1" style="9" min="8" max="8"/>
+    <col width="26" customWidth="1" style="9" min="9" max="9"/>
+    <col width="30" customWidth="1" style="9" min="10" max="10"/>
+    <col width="16" customWidth="1" style="9" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1" s="9">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Test Case - Fitur Mengunggah Berkas Tata Tertib Sekolah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1" s="9">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Website : Sentri Siswa (sentrisiswav2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" s="9">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Page : Kesiswaan &gt; Tata Tertib</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1" s="9">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.9" customHeight="1" s="9">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Format Test Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="9"/>
+    <row r="8" ht="31.2" customHeight="1" s="9">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>Steps Description</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.001.001</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah tata tertib sebagai draft</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas tata tertib tanpa langsung mengaktifkannya, sehingga siswa belum bisa membacanya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Berkas tata tertib berbentuk PDF sudah disiapkan.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39.6" customHeight="1" s="9">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF, biarkan penanda aktif tidak dicentang, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah." dan tata tertib itu tampil di daftar dengan status Draft.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26.4" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.002</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.002.001</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah tata tertib dan langsung mengaktifkannya</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengunggah berkas sekaligus mengaktifkannya, sehingga langsung bisa dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Berkas tata tertib berbentuk PDF sudah disiapkan.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF, centang penanda aktif, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah." dan tata tertib itu tampil di daftar dengan status Aktif.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26.4" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah berkas yang bukan PDF</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib hanya boleh diunggah dalam bentuk PDF.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas yang bukan PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File tata tertib harus berupa PDF." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Mengunggah tanpa mengisi judul</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan mengosongkan judul lalu mengunggah berkas.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Kosongkan judul, pilih berkas PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Judul tata tertib wajib diisi." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mengaktifkan tata tertib menonaktifkan yang lama</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Hanya satu tata tertib yang boleh aktif pada satu waktu, supaya siswa tidak bingung membaca versi mana.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu tata tertib yang aktif dan satu lagi yang masih draft.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1" s="9">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Aktifkan pada baris tata tertib yang masih draft.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil dipublikasikan."</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="9">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi daftar.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Tata tertib yang baru diaktifkan berstatus Aktif, sedangkan tata tertib yang sebelumnya aktif berubah menjadi Draft.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39.6" customHeight="1" s="9">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.006</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.006.001</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Menonaktifkan tata tertib yang sedang aktif</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menonaktifkan tata tertib supaya tidak lagi dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Ada tata tertib yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26.4" customHeight="1" s="9">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Nonaktifkan pada baris tata tertib itu.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil dinonaktifkan." dan statusnya berubah menjadi Draft.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26.4" customHeight="1" s="9">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.007</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.007.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Menghapus tata tertib</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan menghapus berkas tata tertib yang tidak dipakai lagi.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Sudah ada satu tata tertib di daftar.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.4" customHeight="1" s="9">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Hapus pada baris tata tertib itu, lalu setujui konfirmasinya.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil dihapus." dan tata tertib itu hilang dari daftar.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39.6" customHeight="1" s="9">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.008</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.008.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Daftar tata tertib masih kosong</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan membuka halaman sebelum satu pun tata tertib diunggah.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk. Belum ada satu pun tata tertib.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum ada file tata tertib."</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26.4" customHeight="1" s="9">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Siswa membaca tata tertib yang aktif</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib yang aktif itulah yang dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ada tata tertib yang statusnya aktif.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tata tertib tampil berisi judul tata tertib yang sedang aktif.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26.4" customHeight="1" s="9">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.010</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.010.001</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib draft tidak dibaca siswa</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Tata tertib yang masih draft belum boleh dibaca siswa.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Tata tertib yang ada statusnya masih draft.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Judul tata tertib yang masih draft tidak tampil di halaman siswa.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26.4" customHeight="1" s="9">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.011</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.011.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas PDF</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Berkas berukuran tepat di bawah batas 10 MB.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="39.6" customHeight="1" s="9">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran sedikit di bawah 10 MB, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="39.6" customHeight="1" s="9">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.011</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.011.002</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas PDF</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Berkas berukuran tepat 10 MB, pas pada batas.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52.8" customHeight="1" s="9">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran tepat 10 MB, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52.8" customHeight="1" s="9">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.011</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.011.003</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran berkas PDF</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Berkas berukuran sedikit di atas 10 MB.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="39.6" customHeight="1" s="9">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul, pilih berkas PDF berukuran sedikit di atas 10 MB, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Ukuran PDF maksimal 10 MB." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="39.6" customHeight="1" s="9">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.012</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.012.001</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang judul</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Judul sepanjang 200 karakter, tepat pada batas.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52.8" customHeight="1" s="9">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul sepanjang 200 karakter, pilih berkas PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tata tertib berhasil diunggah."</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>TS.TTK.012</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>TC.TTK.012.002</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang judul</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Judul sepanjang 201 karakter, sekarakter di atas batas.</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Kesiswaan sedang masuk.</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Tata Tertib.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Tata Tertib tampil berisi formulir unggah dan daftar tata tertib.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Isi judul sepanjang 201 karakter, pilih berkas PDF, lalu klik Unggah.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Judul tata tertib maksimal 200 karakter." dan tata tertib tidak tersimpan.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="89">
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -18739,7 +19955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19251,7 +20467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19598,7 +20814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20440,7 +21656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21612,7 +22828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22344,7 +23560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -9858,9 +9858,9 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="B11:B13"/>
-    <mergeCell ref="A23:A24"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="A19:A20"/>
@@ -19961,7 +19961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -19994,14 +19994,14 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : BK &gt; Monitoring</t>
+          <t>Page : BK &gt; Monitoring (Kehadiran)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -20071,397 +20071,813 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.MAB.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.MAB.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>BK melihat siswa tingkat sendiri di halaman monitoring</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Memantau kehadiran hari ini siswa di tingkatnya</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka halaman monitoring dan melihat siswa dari tingkat yang dipegangnya.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK memantau kehadiran hari ini untuk siswa di tingkat yang dipegangnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login dan sudah dikaitkan admin ke tingkat 10; ada siswa yang terdaftar di tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Hari ini termasuk hari absensi dan seorang siswa sudah absen hadir.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Daftar siswa tingkat 10 tampil, termasuk siswa yang sudah terdaftar.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa, kelasnya, dan status kehadirannya Hadir tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39.6" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.MAB.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.MAB.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>BK tidak melihat siswa dari tingkat lain di halaman monitoring</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Siswa dari tingkat lain tidak dipantau</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka halaman monitoring dan memastikan siswa tingkat lain tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Tiap guru BK hanya memegang satu tingkat dan hanya boleh memantau siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login dan dikaitkan ke tingkat 10; ada siswa terdaftar di tingkat 10 dan di tingkat 11.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada siswa di tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Daftar cuma menampilkan siswa tingkat 10, siswa tingkat 11 tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa tingkat 10 yang tampil; siswa tingkat 11 tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.MAB.003</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.MAB.003.001</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>BK memfilter daftar monitoring berdasarkan nama siswa</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Membuka rincian siswa dari tingkat lain</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Rincian siswa di luar tingkat yang dipegang tidak boleh dibuka.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada siswa di tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Cari siswa tingkat 11 di daftar.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Siswa itu tidak ada di daftar, sehingga tidak ada tombol Detail untuk membuka rinciannya. Halaman rinciannya pun tidak bisa diakses.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52.8" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.MAB.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.MAB.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Melihat riwayat kehadiran seorang siswa</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BK mencari siswa tingkat sendiri berdasarkan kata kunci nama.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK menelusuri kehadiran seorang siswa di tingkatnya.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada dua siswa tingkat 10 dengan nama berbeda.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya satu catatan kehadiran berstatus alpha.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Ketik sebagian nama salah satu siswa di kolom pencarian, lalu klik Cari.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Daftar cuma menampilkan siswa yang namanya cocok dengan kata kunci.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.MAB.004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.MAB.004.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>BK memfilter daftar monitoring berdasarkan kelas dalam tingkat sendiri</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi bagian Riwayat Kehadiran, dan catatan alpha siswa itu tampil di dalamnya.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.MAB.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.MAB.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mencari siswa berdasarkan nama</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BK memilih satu kelas tertentu dari tingkat sendiri lewat filter kelas.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK mengetik sebagian nama siswa di kolom pencarian.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada dua siswa dari kelas berbeda dalam tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada lebih dari satu siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Pilih salah satu kelas pada filter Kelas, lalu klik Cari.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Daftar cuma menampilkan siswa dari kelas yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.MAB.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.MAB.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>BK melihat detail status dan persentase kehadiran siswa tingkat sendiri</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Ketik sebagian nama siswa di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang namanya cocok yang tampil; siswa lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.MAB.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.MAB.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring siswa berdasarkan kelas</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka detail siswa tingkat sendiri untuk melihat status dan persentase kehadiran.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK membatasi daftar pada satu kelas di tingkatnya.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah absen hadir hari ini.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada dua kelas berbeda di tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Klik tautan Detail pada baris siswa tersebut.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Halaman detail siswa tampil berisi status kehadiran hari ini dan persentase kehadiran.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.MAB.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.MAB.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>BK ditolak akses saat membuka detail siswa dari tingkat lain</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih sebuah kelas di kolom penyaring lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa dari kelas itu yang tampil; siswa kelas lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.MAB.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.MAB.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Pencarian tidak menemukan siswa</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK mencari nama yang tidak ada.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Ketik nama yang tidak ada di kolom pencarian lalu tekan Enter.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Tidak ada data siswa ditemukan."</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.MAB.008</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.MAB.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Batas ambang peringatan alpha</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BK mencoba membuka detail siswa yang berada di tingkat lain.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa yang terdaftar di tingkat 11.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Alpha dua kali, sekali di bawah ambang peringatan.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya dua catatan alpha pada semester berjalan.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Buka langsung tautan detail siswa tingkat 11 tersebut.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403 Forbidden).</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52.8" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.MAB.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.MAB.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>BK yang belum dikaitkan ke tingkat manapun tetap bisa membuka halaman monitoring tanpa error</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BK yang profilnya belum diisi tingkat oleh admin membuka halaman monitoring.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login tapi profilnya belum dikaitkan admin ke tingkat manapun; ada siswa terdaftar di tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Siswa tampil di tabel tanpa penanda peringatan alpha.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.MAB.008</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.MAB.008.002</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Batas ambang peringatan alpha</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Alpha tiga kali, tepat pada ambang peringatan.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya tiga catatan alpha pada semester berjalan.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Halaman tampil tanpa error, tapi daftar siswa kosong.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Siswa tampil dengan penanda "Peringatan alpha 3x".</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="68">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20473,7 +20889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -20506,14 +20922,14 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : BK &gt; Monitoring</t>
+          <t>Page : BK &gt; Monitoring (Poin &amp; Pelanggaran)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Teknik Testing : Equivalence Partitioning</t>
+          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
         </is>
       </c>
     </row>
@@ -20583,232 +20999,546 @@
       </c>
     </row>
     <row r="9" ht="52.8" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.MPB.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.MPB.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>BK melihat sisa poin default siswa yang belum pernah dapat pelanggaran</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat sisa poin siswa</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka halaman monitoring dan melihat sisa poin siswa yang belum pernah dicatat pelanggarannya.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa mulai dari 100 dan berkurang sesuai pelanggaran yang tercatat.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 belum pernah dapat pelanggaran atau pengajuan poin.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya satu pelanggaran yang memotong 10 poin.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Sisa poin siswa tersebut tampil 100.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="79.2" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan kolom poin pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin siswa tampil 90.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39.6" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.MPB.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.MPB.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>BK melihat sisa poin yang sudah dihitung dari pelanggaran dan pengajuan poin disetujui</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Menelusuri riwayat pelanggaran seorang siswa</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka halaman monitoring dan melihat sisa poin siswa yang sudah punya pelanggaran dan pengajuan poin disetujui.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK membuka rincian siswa untuk melihat pelanggaran apa saja yang pernah dicatat.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah punya 1 pelanggaran disetujui (potongan 30 poin) dan 1 pengajuan poin disetujui (tambahan 10 poin).</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya pelanggaran ringan 10 poin dan pelanggaran berat 60 poin.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Monitoring.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Sisa poin siswa tersebut tampil 80 (100 dikurangi 30 lalu ditambah 10).</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi kedua pelanggaran itu, dan sisa poin siswa 30.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.MPB.003</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.MPB.003.001</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>BK melihat detail agregat poin siswa tingkat sendiri</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Poin bertambah setelah pengajuan poin disetujui</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka detail siswa tingkat sendiri untuk melihat riwayat pelanggaran yang sudah disetujui.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Sisa poin dihitung dari poin awal 100, dikurangi pelanggaran, ditambah pengajuan poin yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah punya 1 pelanggaran disetujui.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya pelanggaran yang memotong 20 poin dan pengajuan poin yang sudah disetujui sebesar 5 poin.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Klik tautan Detail pada baris siswa tersebut.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Halaman detail siswa tampil berisi riwayat pelanggaran yang sudah disetujui.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil berisi alasan penambahan poin, dan sisa poin siswa 85.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>TS.MPB.004</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TC.MPB.004.001</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Halaman detail monitoring BK tidak menyediakan tautan catat pelanggaran baru</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Pengajuan poin yang belum disetujui belum menambah poin</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka detail siswa dan memastikan tidak ada tombol untuk mencatat pelanggaran baru (beda dengan kesiswaan).</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Poin baru bertambah setelah kesiswaan menyetujui pengajuannya.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah terdaftar.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya pelanggaran yang memotong 20 poin dan pengajuan poin yang masih menunggu keputusan.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman detail siswa tersebut.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Tidak ada tombol atau tautan Catat Pelanggaran pada halaman detail.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris siswa itu.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin siswa tetap 80, dan pengajuan yang masih menunggu itu belum tampil di rincian penambahan poin.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.MPB.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.MPB.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK tidak bisa mencatat pelanggaran</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Mencatat pelanggaran adalah wewenang kesiswaan, bukan BK. Guru BK hanya memantau.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Detail pada baris seorang siswa.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Halaman rincian tampil tanpa tombol untuk mencatat pelanggaran.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.MPB.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.MPB.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa dari tingkat lain tidak terlihat</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK hanya melihat poin siswa di tingkat yang dipegangnya.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada siswa tingkat 11 yang punya pelanggaran.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Monitoring.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Monitoring BK tampil berisi daftar siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Siswa tingkat 11 beserta poinnya tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="47">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20820,7 +21550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -20853,7 +21583,7 @@
     <row r="4" ht="21" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Page : BK &gt; Rekap Absensi</t>
+          <t>Page : BK &gt; Laporan</t>
         </is>
       </c>
     </row>
@@ -20930,727 +21660,1313 @@
       </c>
     </row>
     <row r="9" ht="66" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.RAB.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.RAB.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>BK melihat rekap absensi siswa dari kelas-kelas dalam tingkat sendiri</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat rekap kehadiran seluruh siswa di tingkatnya</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>BK membuka halaman rekap absensi dan melihat rekap siswa tingkat sendiri.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK menyusun rekap kehadiran seluruh siswa di tingkat yang dipegangnya.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; siswa tingkat 10 sudah absen hadir pada hari kerja dalam rentang tanggal default (awal bulan sampai hari ini).</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Seorang siswa sudah punya beberapa catatan kehadiran.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Rekap absensi siswa tingkat 10 tampil, termasuk siswa tersebut.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52.8" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal mulai dan tanggal selesai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama siswa beserta jumlah hadir, terlambat, izin, sakit, alpha, dan persentase kehadirannya tampil di tabel.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.RAB.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.RAB.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>BK yang belum dikaitkan ke tingkat manapun melihat halaman rekap kosong tanpa error</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Rekap tidak memuat siswa dari tingkat lain</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Rekap hanya memuat siswa di tingkat yang dipegang guru BK itu.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada siswa di tingkat 11.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa tingkat 10 yang tampil; siswa tingkat 11 tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.8" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.003</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.003.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Persentase kehadiran dihitung dari hari yang sudah punya keputusan</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>BK yang profilnya belum diisi tingkat oleh admin membuka halaman rekap absensi.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Persentase dihitung dari hari hadir dan terlambat dibagi seluruh hari yang tercatat.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login tapi profilnya belum dikaitkan admin ke tingkat manapun.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa tercatat dua hari hadir dan dua hari alpha.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Halaman menampilkan pesan bahwa akun BK belum dikaitkan dengan tingkat kelas, bukan pesan error.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="66" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.003</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.003.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>BK memfilter rekap berdasarkan status kehadiran</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.8" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang memuat keempat hari itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Persentase kehadiran siswa tersebut tampil 50%.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring rekap berdasarkan kelas</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BK memfilter rekap absensi supaya cuma menampilkan siswa yang punya catatan alpha.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK membatasi rekap pada satu kelas di tingkatnya.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; satu siswa sudah absen hadir dan satu siswa lain sudah absen alpha pada hari kerja yang sama.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Ada dua kelas berbeda di tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Pilih status Alpha pada filter Status, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Rekap cuma menampilkan siswa yang punya catatan alpha, siswa yang hadir tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.004.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>BK memfilter rekap berdasarkan siswa tertentu</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Pilih sebuah kelas di kolom penyaring lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa dari kelas itu yang tampil; siswa kelas lain tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.005</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.005.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring rekap hanya siswa yang pernah alpha</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BK memilih satu siswa tertentu lewat filter siswa.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK menyaring rekap agar hanya menampilkan siswa yang pernah alpha.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada dua siswa tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Satu siswa pernah alpha dan satu siswa lain selalu hadir.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Pilih salah satu siswa pada filter Siswa, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Rekap cuma menampilkan siswa yang dipilih.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52.8" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>BK memfilter rekap berdasarkan bulan, menggantikan rentang tanggal default</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Pilih Alpha di kolom Status lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Hanya siswa yang pernah alpha yang tampil; siswa yang selalu hadir tidak tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52.8" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.006</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.006.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Menyaring rekap per bulan</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BK memilih bulan tertentu lewat filter bulan, menggantikan rentang mulai/selesai default.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK memilih bulan tertentu agar rekap hanya menghitung kehadiran di bulan itu.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya catatan kehadiran di dua bulan berbeda.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Pilih bulan April 2026 pada filter Bulan, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Rentang tanggal rekap berubah jadi 1 April 2026 sampai 30 April 2026, menggantikan rentang mulai/selesai default.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52.8" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>BK mengisi tanggal selesai sebelum tanggal mulai</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52.8" customHeight="1" s="9">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Pilih bulan yang dituju di kolom Bulan lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Rekap hanya menghitung kehadiran di bulan yang dipilih; catatan di bulan lain tidak ikut dihitung.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52.8" customHeight="1" s="9">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.007</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.007.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh rekap dalam berkas Excel</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK mengunduh rekap kehadiran tingkatnya untuk diarsipkan.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal, lalu klik tombol Ekspor Excel.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Berkas Excel rekap absensi tingkat itu terunduh, dengan nama berkas memuat tingkat dan rentang tanggalnya.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.008</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.008.001</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mengunduh rekap dalam berkas PDF</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK mengunduh rekap kehadiran dalam bentuk PDF.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal, lalu klik tombol Ekspor PDF.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Berkas PDF rekap absensi tingkat itu terunduh, dengan nama berkas memuat tingkat dan rentang tanggalnya.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK belum dipasangi tingkat</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BK mengisi tanggal selesai yang lebih awal daripada tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK yang belum ditentukan tingkatnya belum bisa menyusun rekap.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk tetapi belum dipasangi tingkat mana pun.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai 10 Juni 2026 dan tanggal selesai 5 Juni 2026, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal selesai harus sama dengan atau setelah tanggal mulai, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>BK mengisi tanggal dengan format yang tidak valid</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Halaman tampil tanpa tabel rekap, disertai keterangan "Data Tingkat Tidak Tersedia".</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.010</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.010.001</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh tepat pada tanggal mulai ikut dihitung.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya satu catatan alpha tepat pada tanggal mulai.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal mulainya sama dengan tanggal alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Alpha tersebut ikut dihitung sehingga persentase kehadiran siswa tampil 0%.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.010</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.010.002</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Batas bawah rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BK mengisi tanggal mulai dengan format yang salah.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh sehari sebelum tanggal mulai tidak dihitung.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya catatan alpha sehari sebelum tanggal mulai dan catatan hadir di dalam rentang.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai dengan format yang salah, misal "10-06-2026", lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal mulai tidak valid, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.008</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.008.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>BK mengekspor rekap absensi ke Excel</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tidak memuat hari alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Alpha di luar rentang diabaikan sehingga persentase kehadiran siswa tampil 100%.</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.011</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.011.001</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BK mengunduh rekap absensi tingkat sendiri dalam format Excel.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa tingkat 10 terdaftar.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh tepat pada tanggal selesai ikut dihitung.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya satu catatan alpha tepat pada tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Export Excel.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Berkas Excel berhasil terunduh dengan nama berkas sesuai tingkat BK.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.009</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.009.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>BK mengekspor rekap absensi ke PDF</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tanggal selesainya sama dengan tanggal alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Alpha tersebut ikut dihitung sehingga persentase kehadiran siswa tampil 0%.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.011</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.011.002</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas atas rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran yang jatuh sehari setelah tanggal selesai tidak dihitung.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya catatan hadir di dalam rentang dan catatan alpha sehari setelah tanggal selesai.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Pilih rentang tanggal yang tidak memuat hari alpha itu, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Alpha di luar rentang diabaikan sehingga persentase kehadiran siswa tampil 100%.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.012</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.012.001</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>BK mengunduh rekap absensi tingkat sendiri dalam format PDF.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa tingkat 10 terdaftar.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai boleh sama dengan tanggal mulai, menghasilkan rekap satu hari.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10. Siswa punya satu catatan hadir pada tanggal itu.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Export PDF.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Berkas PDF berhasil terunduh.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.010</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.010.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>BK yang belum dikaitkan ke tingkat manapun ditolak saat mengekspor</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal mulai dan tanggal selesai yang sama, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Rekap satu hari tampil tanpa pesan kesalahan, dengan persentase kehadiran siswa 100%.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAB.012</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAB.012.002</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas panjang rentang tanggal rekap</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>BK yang profilnya belum diisi tingkat oleh admin mencoba mengekspor rekap absensi.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login tapi profilnya belum dikaitkan admin ke tingkat manapun.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Tanggal selesai sehari lebih awal daripada tanggal mulai ditolak.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Guru BK sedang masuk dan memegang tingkat 10.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Export Excel.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Akses ditolak (403 Forbidden).</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.8" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.011</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.011.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>BK mengganti parameter kelas_id di address bar dengan kelas milik tingkat lain</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>BK mencoba melihat rekap kelas dari tingkat lain dengan mengganti parameter kelas_id di address bar.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10; ada siswa terdaftar di kelas tingkat 11.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Ubah parameter kelas_id di address bar jadi id kelas milik tingkat 11, lalu buka halaman Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Rekap tetap cuma menampilkan kelas-kelas tingkat 10 milik sendiri, siswa tingkat 11 tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52.8" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.012</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.012.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah rentang tanggal rekap (boundary tanggal selesai sama dengan tanggal mulai)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>BK mengisi tanggal selesai yang sama persis dengan tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai dan tanggal selesai dengan tanggal yang sama, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Filter lolos validasi, rekap tampil tanpa pesan error.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52.8" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAB.013</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAB.013.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah rentang tanggal rekap (boundary tanggal selesai 1 hari sebelum tanggal mulai)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>BK mengisi tanggal selesai 1 hari sebelum tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>BK sudah login, dikaitkan ke tingkat 10.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Isi tanggal mulai, lalu isi tanggal selesai 1 hari sebelumnya, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi tanggal selesai tidak boleh sebelum tanggal mulai, rekap tidak diproses.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Laporan.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Rekap Absensi Tingkat tampil berisi daftar siswa di tingkat itu.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Pilih tanggal selesai satu hari sebelum tanggal mulai, lalu klik Terapkan.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan rekap tidak diperbarui.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="103">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A36:A37"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -20812,8 +20812,8 @@
   <mergeCells count="68">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E17:E18"/>
+    <mergeCell ref="G23:G24"/>
     <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="G13:G14"/>
@@ -22978,7 +22978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -23088,1057 +23088,1594 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.ABS.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.ABS.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mencoba absen sebelum jendela waktu absensi dimulai</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Absen tepat waktu</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Siswa absen sebelum batas keterlambatan, sehingga tercatat Hadir.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:35.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.8" customHeight="1" s="9">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Muncul jendela pengambilan selfie.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.8" customHeight="1" s="9">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Ambil selfie, lalu klik Absen Sekarang.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen berhasil: Hadir."</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26.4" customHeight="1" s="9">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.002</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.002.001</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Absen setelah batas keterlambatan</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Siswa absen setelah batas keterlambatan tetapi masih di dalam jam absen, sehingga tercatat Terlambat.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:50.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik tombol Absen Sekarang, ambil selfie, lalu kirim.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen tercatat: Terlambat."</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.003</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.003.001</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Absen sebelum jam absen dibuka</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengklik tombol Absen Sekarang sebelum jam mulai absen.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen sebelum jam absen dimulai.</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login dan memiliki profil siswa; jam saat ini sebelum jam mulai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:00.</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Absensi, ambil selfie, lalu klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan waktu absen sudah lewat atau belum dimulai, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52.8" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.002</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.002.001</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mencoba absen setelah jendela waktu absensi berakhir</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Coba kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Waktu absen sudah lewat atau belum dimulai." dan absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.004</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.004.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Absen setelah jam absen berakhir</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengklik tombol Absen Sekarang setelah jam selesai absen.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen setelah jam absen ditutup.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login dan memiliki profil siswa; jam saat ini sudah lewat jam selesai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 07:30.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Absensi, ambil selfie, lalu klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan waktu absen sudah lewat atau belum dimulai, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52.8" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.003</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.003.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa absen setelah lewat batas toleransi telat</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52.8" customHeight="1" s="9">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Coba kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Waktu absen sudah lewat atau belum dimulai." dan absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39.6" customHeight="1" s="9">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.005</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.005.001</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Absen di hari yang bukan hari absensi</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Siswa mencoba absen pada hari libur.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini hari Minggu, bukan hari absensi.</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="9">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Coba kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan bahwa absensi hanya tersedia pada hari absensi yang ditentukan sekolah, dan absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39.6" customHeight="1" s="9">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.006</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.006.001</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Absen dua kali dalam sehari</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Satu siswa hanya boleh absen sekali sehari.</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Siswa sudah absen hari ini.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39.6" customHeight="1" s="9">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Coba kirim absensi sekali lagi.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Anda sudah absen hari ini." dan absensi tidak tercatat dua kali.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39.6" customHeight="1" s="9">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.007</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.007.001</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Mengirim berkas yang bukan gambar sebagai selfie</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Bukti kehadiran harus berupa foto.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:35.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39.6" customHeight="1" s="9">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Kirim absensi dengan berkas yang bukan gambar.</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "File harus berupa gambar." dan absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39.6" customHeight="1" s="9">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.008</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.008.001</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Halaman absensi menampilkan status hari ini</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengklik tombol Absen Sekarang setelah lewat batas toleransi telat tapi masih dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Setelah absen, halaman menampilkan bahwa absensinya sudah tercatat.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; jam saat ini sudah lewat batas toleransi telat tapi masih dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Siswa baru saja absen.</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie, lalu klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Absensi tercatat dengan status Terlambat.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.004.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mencoba absen tanpa mengambil selfie</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Halaman menampilkan keterangan bahwa absensi hari ini sudah tercatat, beserta jam absennya.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39.6" customHeight="1" s="9">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.009</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.009.001</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Pemberitahuan hari ini bukan hari absensi</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Halaman memberi tahu siswa kenapa ia belum bisa absen.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini hari Minggu.</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Absensi hanya tersedia pada hari Senin sampai Jumat."</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="39.6" customHeight="1" s="9">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.010</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.010.001</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Pemberitahuan waktunya belum tiba</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Halaman memberi tahu siswa kapan absen dimulai.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:00.</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum waktunya absen. Absen dimulai pukul 06:30."</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39.6" customHeight="1" s="9">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.011</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.011.001</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Pemberitahuan waktunya sudah berakhir</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Halaman memberi tahu siswa bahwa jam absen sudah lewat.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 07:30.</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Waktu absen sudah berakhir pukul 07:00."</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.012</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.012.001</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Batas jam absen dibuka</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengklik tombol Absen Sekarang tanpa mengambil foto selfie.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login, sedang dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Pukul 06:29, semenit sebelum jam absen dibuka.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:29.</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Klik tombol Absen Sekarang tanpa mengambil foto selfie.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi selfie wajib diambil, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mencoba absen dengan selfie berformat yang tidak diizinkan</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Coba kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Waktu absen sudah lewat atau belum dimulai."</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.012</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.012.002</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Batas jam absen dibuka</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Pukul 06:30, tepat saat jam absen dibuka.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:30.</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Ambil selfie lalu kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen berhasil: Hadir."</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.013</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.013.001</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Batas keterlambatan</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Pukul 06:45, tepat pada batas keterlambatan, masih tercatat Hadir.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:45.</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Ambil selfie lalu kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen berhasil: Hadir."</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.013</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.013.002</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Batas keterlambatan</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Pukul 06:46, semenit setelah batas keterlambatan, tercatat Terlambat.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:46.</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Ambil selfie lalu kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen tercatat: Terlambat."</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.014</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.014.001</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Batas jam absen ditutup</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Pukul 07:00, tepat saat jam absen ditutup, masih diterima.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 07:00.</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Ambil selfie lalu kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen tercatat: Terlambat." karena sudah lewat batas keterlambatan.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.014</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.014.002</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Batas jam absen ditutup</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengunggah berkas selfie berformat PDF, bukan gambar.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login, sedang dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Pukul 07:01, semenit setelah jam absen ditutup.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 07:01.</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Unggah berkas selfie berformat PDF, lalu klik Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi format foto harus JPEG atau WebP, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa yang belum dikaitkan ke profil siswa manapun mencoba absen</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>Coba kirim absensi.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Waktu absen sudah lewat atau belum dimulai."</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.015</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.015.001</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran selfie</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Selfie berukuran tepat 300 KB, pas pada batas.</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:35.</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Kirim absensi dengan foto berukuran tepat 300 KB.</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Absen berhasil: Hadir."</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>TS.ABS.015</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>TC.ABS.015.002</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Batas ukuran selfie</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa yang akunnya belum dikaitkan admin ke profil siswa mencoba mengklik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login tapi akunnya belum dikaitkan admin ke profil siswa manapun.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Selfie berukuran sedikit di atas 300 KB.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Jam absen sekolah dibuka pukul 06:30 sampai 07:00, dengan batas keterlambatan pukul 06:45. Hari ini termasuk hari absensi. Sekarang pukul 06:35.</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Absensi dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan profil siswa tidak ditemukan, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengecek lokasi GPS di dalam area absensi</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengizinkan akses lokasi GPS saat berada di dalam area absensi (geofence).</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa berada di dalam area tersebut.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Izinkan akses lokasi GPS di perangkat saat diminta halaman Absensi.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Lokasi dinyatakan berada di dalam area absensi, tombol Absen Sekarang bisa diklik.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.008</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.008.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengecek lokasi GPS di luar area absensi dan di luar toleransi</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengizinkan akses lokasi GPS saat berada jauh di luar area absensi (geofence).</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa berada jauh di luar area tersebut.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Izinkan akses lokasi GPS di perangkat saat diminta halaman Absensi.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Lokasi dinyatakan di luar area absensi, tombol Absen Sekarang dikunci.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52.8" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.009</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.009.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mencoba absen tanpa mengizinkan lokasi GPS padahal area absensi sudah dikonfigurasi</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengklik tombol Absen Sekarang tanpa mengizinkan akses lokasi GPS.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa tidak mengizinkan akses lokasi GPS.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang tanpa mengizinkan akses lokasi.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi lokasi GPS wajib diaktifkan, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.010</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.010.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mencoba absen dengan lokasi di luar area absensi</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengklik tombol Absen Sekarang saat lokasinya berada di luar area absensi.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Area absensi (geofence) sudah dikonfigurasi admin; siswa berada di luar area tersebut.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie, lalu klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan lokasi di luar area absensi dan tidak bisa absen, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.011</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.011.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Siswa melihat status absensi hari ini yang sesuai</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka atau memuat ulang halaman Absensi setelah sudah absen hari ini.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah absen hari ini dengan status Hadir.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Buka atau muat ulang halaman Absensi.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Status hari ini yang ditampilkan sesuai dengan catatan absensi yang sudah tersimpan (Hadir).</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39.6" customHeight="1" s="9">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.012</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.012.001</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah jendela waktu absensi (boundary tepat di jam mulai)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini tepat sama dengan jam mulai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini tepat sama dengan jam mulai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Absensi berhasil tercatat.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="39.6" customHeight="1" s="9">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.013</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.013.001</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah jendela waktu absensi (boundary 1 menit sebelum jam mulai)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini 1 menit sebelum jam mulai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini 1 menit sebelum jam mulai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan waktu absen belum dimulai, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="39.6" customHeight="1" s="9">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.014</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.014.001</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas jendela waktu absensi (boundary tepat di jam selesai)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini tepat sama dengan jam selesai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini tepat sama dengan jam selesai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Absensi berhasil tercatat.</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39.6" customHeight="1" s="9">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.015</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.015.001</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas jendela waktu absensi (boundary 1 menit setelah jam selesai)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini 1 menit setelah jam selesai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini 1 menit setelah jam selesai jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan waktu absen sudah lewat, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39.6" customHeight="1" s="9">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.016</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.016.001</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Batas toleransi telat (boundary tepat di batas, hasilnya Hadir)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini tepat di batas toleransi telat.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini tepat di batas toleransi telat, masih dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Absensi tercatat dengan status Hadir.</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="39.6" customHeight="1" s="9">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.017</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.017.001</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Batas toleransi telat (boundary 1 menit lewat batas, hasilnya Terlambat)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini 1 menit lewat batas toleransi telat.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Jam saat ini 1 menit lewat batas toleransi telat, masih dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie dan klik tombol Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Absensi tercatat dengan status Terlambat.</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="39.6" customHeight="1" s="9">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.018</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.018.001</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran maksimum selfie (boundary tepat 300 KB)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengambil selfie berukuran tepat 300 KB.</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sedang dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie berukuran tepat 300 KB, lalu klik Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Absensi berhasil tercatat.</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="39.6" customHeight="1" s="9">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TS.ABS.019</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>TC.ABS.019.001</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Batas ukuran maksimum selfie (boundary di atas 300 KB)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengambil selfie berukuran 301 KB.</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sedang dalam jendela waktu absensi.</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Ambil selfie berukuran 301 KB, lalu klik Absen Sekarang.</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan validasi ukuran foto melebihi batas maksimum, absensi tidak tercatat.</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Absensi.</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Absensi Hari Ini tampil.</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Kirim absensi dengan foto berukuran sedikit di atas 300 KB.</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Muncul pesan "Ukuran foto maksimal 300 KB." dan absensi tidak tercatat.</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="110">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="G38:G39"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24150,7 +24687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -24260,617 +24797,698 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.RAS.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.RAS.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa melihat riwayat absensi bulan berjalan tanpa memilih filter bulan</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Melihat riwayat kehadiran bulan berjalan</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman riwayat absensi tanpa mengubah filter bulan.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Siswa menelusuri kehadirannya sendiri di bulan yang sedang berjalan.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; ada catatan absensi pada bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan hadir dan sakit di bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Catatan absensi bulan berjalan tampil.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Absensi tampil.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Nama bulan berjalan tampil, beserta catatan Hadir dan Sakit siswa itu.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39.6" customHeight="1" s="9">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TS.RAS.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>TC.RAS.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa memfilter riwayat absensi berdasarkan bulan tertentu</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Berpindah ke bulan lain</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa memilih bulan April 2026 lewat filter bulan.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Siswa memilih bulan sebelumnya untuk melihat riwayatnya.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; ada catatan absensi di bulan April 2026 dan di bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan alpha di bulan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Pilih bulan April 2026 pada filter bulan, lalu klik Filter.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Cuma catatan absensi bulan April 2026 yang tampil.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39.6" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Absensi tampil.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="9">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Pilih bulan sebelumnya di kolom pilihan bulan.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Nama bulan itu tampil beserta catatan alpha siswa di bulan tersebut.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TS.RAS.003</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TC.RAS.003.001</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Riwayat absensi tetap tampil bulan berjalan saat parameter bulan tidak valid</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Riwayat bulan berjalan tidak memuat bulan lain</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Riwayat yang tampil hanya kehadiran di bulan yang dipilih.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia hanya punya catatan alpha di bulan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Absensi tampil.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Catatan bulan sebelumnya tidak tampil, dan muncul keterangan "Belum ada catatan absensi pada bulan ini."</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAS.004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.004.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Bulan yang belum punya catatan</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengganti parameter bulan di address bar dengan teks yang bukan format bulan valid.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Siswa membuka riwayat sebelum punya satu pun catatan kehadiran.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia belum punya satu pun catatan kehadiran.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Ubah parameter bulan di address bar jadi teks yang bukan format bulan valid.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Halaman tetap menampilkan catatan bulan berjalan tanpa error.</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.004.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa melihat pesan kosong saat belum ada catatan absensi pada bulan tersebut</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Muncul keterangan "Belum ada catatan absensi pada bulan ini."</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52.8" customHeight="1" s="9">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAS.005</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.005.001</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran siswa lain tidak terlihat</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Tiap siswa hanya melihat riwayat kehadirannya sendiri.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Siswa lain di kelasnya punya catatan alpha, tetapi ia sendiri belum punya catatan.</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Riwayat Absensi tampil.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52.8" customHeight="1" s="9">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan isi tabel.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Catatan kehadiran siswa lain tidak tampil, dan muncul keterangan "Belum ada catatan absensi pada bulan ini."</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52.8" customHeight="1" s="9">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAS.006</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.006.001</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Pilihan bulan yang tidak dikenali</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman riwayat absensi saat belum ada catatan pada bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Bila bulan yang dipilih tidak dikenali, riwayat kembali menampilkan bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; belum ada catatan absensi pada bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan hadir di bulan berjalan.</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Muncul pesan belum ada catatan absensi pada bulan ini.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Riwayat absensi ditampilkan terurut dari tanggal terbaru</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Buka Riwayat Absensi dengan pilihan bulan yang tidak dikenali.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Riwayat kembali menampilkan bulan berjalan beserta catatan Hadir siswa itu.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52.8" customHeight="1" s="9">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAS.007</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.007.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Batas awal bulan</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka riwayat absensi yang berisi beberapa catatan dengan tanggal berbeda.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; ada beberapa catatan absensi di bulan berjalan dengan tanggal berbeda.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran pada tanggal pertama bulan itu ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan alpha pada tanggal pertama bulan yang dipilih.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Catatan absensi tampil terurut dari tanggal terbaru ke yang paling lama.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa cuma melihat riwayat absensi miliknya sendiri, bukan siswa lain</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi lalu pilih bulan itu.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Nama bulan itu tampil beserta catatan alpha pada tanggal pertamanya.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAS.007</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.007.002</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Batas awal bulan</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa login dan membuka riwayat absensi, memastikan catatan siswa lain tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Ada dua siswa berbeda yang masing-masing punya catatan absensi di bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran sehari sebelum bulan itu tidak tampil.</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan alpha sehari sebelum bulan yang dipilih.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Login sebagai salah satu siswa, lalu buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Cuma catatan absensi milik siswa yang login yang tampil, punya siswa lain tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Catatan yang tanggalnya persis di hari terakhir bulan tetap ikut tampil</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi lalu pilih bulan itu.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Catatan itu tidak tampil, dan muncul keterangan "Belum ada catatan absensi pada bulan ini."</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.RAS.008</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.008.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Batas akhir bulan</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka riwayat absensi yang berisi catatan tepat di hari terakhir bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; ada catatan absensi yang tanggalnya tepat di hari terakhir bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran pada tanggal terakhir bulan itu ikut tampil.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan alpha pada tanggal terakhir bulan yang dipilih.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Catatan absensi di hari terakhir bulan tersebut tetap ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52.8" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi lalu pilih bulan itu.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Nama bulan itu tampil beserta catatan alpha pada tanggal terakhirnya.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>TS.RAS.008</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.008.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Batas bawah angka bulan pada filter (boundary bulan 01)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengganti parameter bulan di address bar jadi 2026-01.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.RAS.008.002</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Batas akhir bulan</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Kehadiran sehari setelah bulan itu tidak tampil.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya catatan alpha sehari setelah bulan yang dipilih.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Ubah parameter bulan di address bar jadi 2026-01, lalu buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Halaman menampilkan catatan bulan Januari 2026.</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52.8" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.009</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.009.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Di bawah batas bawah angka bulan pada filter (boundary bulan 00)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengganti parameter bulan di address bar jadi 2026-00.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Ubah parameter bulan di address bar jadi 2026-00, lalu buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Format bulan tidak valid, halaman kembali menampilkan bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52.8" customHeight="1" s="9">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.010</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.010.001</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Batas atas angka bulan pada filter (boundary bulan 12)</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengganti parameter bulan di address bar jadi 2026-12.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Ubah parameter bulan di address bar jadi 2026-12, lalu buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>Halaman menampilkan catatan bulan Desember 2026.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.8" customHeight="1" s="9">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TS.RAS.011</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>TC.RAS.011.001</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Di atas batas atas angka bulan pada filter (boundary bulan 13)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Siswa mengganti parameter bulan di address bar jadi 2026-13.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Ubah parameter bulan di address bar jadi 2026-13, lalu buka halaman Riwayat Absensi.</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>Format bulan tidak valid, halaman kembali menampilkan bulan berjalan.</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Riwayat Absensi lalu pilih bulan itu.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Catatan itu tidak tampil, dan muncul keterangan "Belum ada catatan absensi pada bulan ini."</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="33">
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24882,7 +25500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
@@ -24992,507 +25610,719 @@
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TS.POS.001</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TC.POS.001.001</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa melihat pelanggaran yang sudah disetujui di halaman Poin Saya</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Siswa yang belum pernah melanggar</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya dan melihat pelanggaran yang sudah disetujui.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa mulai dari 100 dan belum berkurang sama sekali.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; siswa punya 1 pelanggaran yang sudah disetujui.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia belum pernah dicatat melanggar.</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Pelanggaran yang sudah disetujui tampil di daftar riwayat pelanggaran.</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Poin Saya tampil dengan sisa poin 100, keterangan Baik, dan catatan bahwa belum ada pelanggaran untuknya.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52.8" customHeight="1" s="9">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>TS.POS.002</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>TC.POS.002.001</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Pelanggaran yang masih menunggu atau ditolak tidak ikut tampil</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Poin berkurang setelah pelanggaran dicatat</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Poin siswa berkurang sesuai pelanggaran yang dicatat kesiswaan.</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya satu pelanggaran yang memotong 10 poin.</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Poin Saya tampil.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.8" customHeight="1" s="9">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan kartu poin dan tabel riwayat.</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 90, dan nama pelanggarannya tampil di riwayat.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="9">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.003</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.003.001</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Poin bertambah setelah pengajuan poin disetujui</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Sisa poin dihitung dari poin awal 100, dikurangi pelanggaran, ditambah pengajuan poin yang sudah disetujui.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya pelanggaran yang memotong 20 poin dan pengajuan poin yang sudah disetujui sebesar 5 poin.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Poin Saya tampil dengan sisa poin 85.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="9">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.004</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.004.001</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Melihat seluruh riwayat pelanggaran sendiri</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Siswa menelusuri pelanggaran apa saja yang pernah dicatat untuknya.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Ia punya pelanggaran ringan 10 poin dan pelanggaran berat 60 poin.</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Poin Saya tampil.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="9">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan tabel riwayat.</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Kedua pelanggaran itu tampil, dan sisa poinnya 30.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39.6" customHeight="1" s="9">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.005</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.005.001</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Pelanggaran siswa lain tidak terlihat</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat punya pelanggaran berstatus menunggu dan ditolak.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Tiap siswa hanya melihat pelanggarannya sendiri.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Equivalence Partitioning</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; siswa punya 1 pelanggaran berstatus menunggu dan 1 pelanggaran berstatus ditolak.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Siswa lain di kelasnya punya pelanggaran, tetapi ia sendiri belum pernah melanggar.</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Kedua pelanggaran yang belum disetujui itu tidak ikut tampil di daftar.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52.8" customHeight="1" s="9">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TS.POS.003</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.003.001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Sisa poin dihitung dari pelanggaran disetujui dan pengajuan poin disetujui</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Halaman Poin Saya tampil.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39.6" customHeight="1" s="9">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Perhatikan tabel riwayat.</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Pelanggaran siswa lain tidak tampil, dan muncul keterangan "Belum ada catatan pelanggaran untuk Anda."</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="39.6" customHeight="1" s="9">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.006</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.006.001</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Batas keterangan Baik</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat punya pelanggaran disetujui dan pengajuan poin disetujui.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; siswa punya 1 pelanggaran disetujui (potongan 30 poin) dan 1 pengajuan poin disetujui (tambahan 10 poin).</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Poin 76, tepat pada batas terendah keterangan Baik.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Poinnya dipotong 24 sehingga tersisa 76.</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>Sisa poin yang ditampilkan 80 (100 dikurangi 30 lalu ditambah 10).</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39.6" customHeight="1" s="9">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TS.POS.004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.004.001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa yang belum pernah punya pelanggaran melihat sisa poin default 100</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 76 dengan keterangan Baik.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.006</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.006.002</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Batas keterangan Baik</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat belum pernah punya catatan pelanggaran.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; siswa belum pernah punya catatan pelanggaran.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Poin 75, sepoin di bawah batas Baik, sudah berubah menjadi Cukup.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Poinnya dipotong 25 sehingga tersisa 75.</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Sisa poin tampil 100 dan muncul pesan belum ada catatan pelanggaran.</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>TS.POS.005</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.005.001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa cuma melihat pelanggaran miliknya sendiri, bukan siswa lain</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Siswa login dan membuka halaman Poin Saya, memastikan pelanggaran siswa lain tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Ada dua siswa berbeda; salah satu siswa punya 1 pelanggaran yang sudah disetujui.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 75 dengan keterangan Cukup.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.007</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.007.001</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Batas keterangan Cukup</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Poin 51, tepat pada batas terendah keterangan Cukup.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Boundary Value Analysis</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Poinnya dipotong 49 sehingga tersisa 51.</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>Login sebagai siswa yang tidak punya pelanggaran, lalu buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Pelanggaran milik siswa lain tidak ikut tampil.</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>TS.POS.006</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.006.001</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Batas label status poin (boundary 1 poin di atas 75, label Baik)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 51 dengan keterangan Cukup.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.007</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.007.002</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Batas keterangan Cukup</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat sisa poinnya 76.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Poin 50, sepoin di bawah batas Cukup, sudah berubah menjadi Perhatian.</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; sisa poin siswa saat ini 76 (1 di atas batas 75).</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Poinnya dipotong 50 sehingga tersisa 50.</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Label status yang tampil "Baik".</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39.6" customHeight="1" s="9">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>TS.POS.007</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.007.001</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Batas label status poin (boundary tepat 75, label Cukup bukan Baik)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 50 dengan keterangan Perhatian.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TS.POS.008</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.008.001</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Batas terendah sisa poin</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat sisa poinnya tepat 75.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Potongan yang pas menghabiskan poin membuat sisa poinnya nol.</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; sisa poin siswa saat ini tepat 75.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Poinnya dipotong 100 sekaligus.</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>Label status yang tampil "Cukup", bukan "Baik".</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39.6" customHeight="1" s="9">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tampil 0 dengan keterangan Perhatian, dan tertulis 100 poin terpakai dari 100 poin.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>TS.POS.008</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.008.001</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Batas label status poin (boundary 1 poin di atas 50, label Cukup)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TC.POS.008.002</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Batas terendah sisa poin</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat sisa poinnya 51.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Potongan yang melebihi poin tersisa tidak membuat poinnya minus.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Boundary Value Analysis</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; sisa poin siswa saat ini 51 (1 di atas batas 50).</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Siswa sedang masuk. Poinnya dipotong 100, lalu dipotong 10 lagi.</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Label status yang tampil "Cukup".</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>TS.POS.009</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>TC.POS.009.001</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Batas label status poin (boundary tepat 50, label Perhatian bukan Cukup)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Siswa membuka halaman Poin Saya saat sisa poinnya tepat 50.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Siswa sudah login; sisa poin siswa saat ini tepat 50.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>Buka halaman Poin Saya.</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Label status yang tampil "Perhatian", bukan "Cukup".</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Klik menu Poin Saya.</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Sisa poin tetap 0, bukan angka minus, meski tertulis 110 poin terpakai dari 100 poin.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="26">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
     <mergeCell ref="A6:K7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test_case/Test Case SentriSiswa.xlsx
+++ b/docs/test_case/Test Case SentriSiswa.xlsx
@@ -4355,8 +4355,8 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="G13:G14"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D17:D18"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="G19:G20"/>
@@ -4367,15 +4367,15 @@
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="G15:G16"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D15:D16"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D15:D16"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A17:A18"/>
@@ -4384,8 +4384,8 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="A4:E4"/>
@@ -4402,1523 +4402,6 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="16.109375" customWidth="1" style="9" min="1" max="1"/>
-    <col width="19.6640625" customWidth="1" style="9" min="2" max="2"/>
-    <col width="26" customWidth="1" style="9" min="3" max="3"/>
-    <col width="12" customWidth="1" style="9" min="4" max="4"/>
-    <col width="40" customWidth="1" style="9" min="5" max="5"/>
-    <col width="17.33203125" customWidth="1" style="9" min="6" max="6"/>
-    <col width="30" customWidth="1" style="9" min="7" max="7"/>
-    <col width="7.88671875" customWidth="1" style="9" min="8" max="8"/>
-    <col width="26" customWidth="1" style="9" min="9" max="9"/>
-    <col width="30" customWidth="1" style="9" min="10" max="10"/>
-    <col width="16" customWidth="1" style="9" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21" customHeight="1" s="9">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Test Case - Fitur Merekap Laporan Absensi Kelas Perwalian</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="21" customHeight="1" s="9">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Website : Sentri Siswa (sentrisiswav2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" s="9">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Page : Wali Kelas &gt; Rekap Absensi</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1" s="9">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Teknik Testing : Equivalence Partitioning, Boundary Value Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="12.9" customHeight="1" s="9">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Format Test Case</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" s="9"/>
-    <row r="8" ht="31.2" customHeight="1" s="9">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Scenario ID</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Case ID</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>Pre Condition</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>Steps Description</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="39.6" customHeight="1" s="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.001</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.001.001</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Melihat rekap kehadiran kelas</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas membuka rekap untuk melihat rangkuman kehadiran seluruh siswa kelasnya.</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Seorang siswa sudah punya beberapa catatan kehadiran.</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="39.6" customHeight="1" s="9">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>Pilih tanggal mulai dan tanggal selesai, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>Nama kelas, nama siswa, jumlah hadir, terlambat, izin, sakit, alpha, dan persentase kehadirannya tampil di tabel.</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26.4" customHeight="1" s="9">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.002</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.002.001</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Persentase kehadiran dihitung dari hari yang sudah punya keputusan</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Persentase dihitung dari hari hadir dan terlambat dibagi seluruh hari yang tercatat.</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa tercatat dua hari hadir dan dua hari alpha.</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="9">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Pilih rentang tanggal yang memuat keempat hari itu, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>Persentase kehadiran siswa tersebut tampil 50%.</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39.6" customHeight="1" s="9">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.003</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.003.001</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Kehadiran di luar hari absensi tidak dihitung</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Catatan di hari yang bukan hari absensi diabaikan dari perhitungan rekap.</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu catatan hadir di hari absensi dan satu catatan alpha di hari libur.</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.6" customHeight="1" s="9">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>Pilih rentang tanggal yang memuat kedua hari itu, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>Alpha di hari libur diabaikan sehingga persentase kehadiran siswa tetap 100%.</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26.4" customHeight="1" s="9">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.004</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.004.001</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Menyaring rekap untuk seorang siswa</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas memilih satu siswa di kolom penyaring agar rekap hanya menampilkan siswa itu.</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Kelas berisi lebih dari satu siswa.</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.4" customHeight="1" s="9">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>Pilih seorang siswa di kolom Siswa, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>Hanya siswa yang dipilih yang tampil di tabel; siswa lain tidak tampil.</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39.6" customHeight="1" s="9">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.005</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.005.001</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Menyaring rekap berdasarkan status</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas menyaring rekap agar hanya menampilkan siswa yang pernah alpha.</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Satu siswa pernah alpha dan satu siswa lain selalu hadir.</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39.6" customHeight="1" s="9">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>Pilih Alpha di kolom Status, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>Hanya siswa yang pernah alpha yang tampil; siswa yang selalu hadir tidak tampil.</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39.6" customHeight="1" s="9">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.006</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.006.001</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Menyaring rekap per bulan</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas memilih bulan tertentu agar rekap hanya menghitung kehadiran di bulan itu.</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya catatan kehadiran di dua bulan berbeda.</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26.4" customHeight="1" s="9">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>Pilih bulan yang dituju di kolom Bulan, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
-        <is>
-          <t>Rekap hanya menghitung kehadiran di bulan yang dipilih; catatan di bulan lain tidak ikut dihitung.</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26.4" customHeight="1" s="9">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.007</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.007.001</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Tanggal selesai lebih awal daripada tanggal mulai</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas memilih tanggal selesai yang jatuh sebelum tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26.4" customHeight="1" s="9">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>Pilih tanggal selesai yang lebih awal daripada tanggal mulai, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="inlineStr">
-        <is>
-          <t>Muncul pesan "Tanggal selesai harus sama dengan atau setelah tanggal mulai." dan rekap tidak diperbarui.</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26.4" customHeight="1" s="9">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.008</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.008.001</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Mengunduh rekap dalam berkas Excel</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas mengunduh rekap kehadiran untuk diarsipkan.</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26.4" customHeight="1" s="9">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>Pilih rentang tanggal, lalu klik tombol Ekspor Excel.</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>Berkas Excel rekap absensi kelas tersebut terunduh, dengan nama berkas memuat nama kelas dan rentang tanggalnya.</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26.4" customHeight="1" s="9">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.009</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.009.001</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Mengunduh rekap dalam berkas PDF</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas mengunduh rekap kehadiran dalam bentuk PDF.</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas.</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="39.6" customHeight="1" s="9">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Pilih rentang tanggal, lalu klik tombol Ekspor PDF.</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>Berkas PDF rekap absensi kelas tersebut terunduh, dengan nama berkas memuat nama kelas dan rentang tanggalnya.</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.010</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.010.001</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Membuka rekap tanpa punya kelas</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Guru yang belum ditugaskan sebagai wali kelas membuka Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>Guru sedang masuk tetapi belum ditugaskan sebagai wali kelas mana pun.</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>Halaman tampil tanpa tabel rekap, disertai keterangan "Belum Ada Kelas" dan anjuran menghubungi administrator.</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.011</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.011.001</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Batas bawah rentang tanggal rekap</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Kehadiran yang jatuh tepat pada tanggal mulai ikut dihitung.</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Boundary Value Analysis</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>Wali kelas sedang masuk dan sudah dipasangi sebuah kelas. Siswa punya satu catatan alpha tepat pada tanggal mulai.</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>Klik menu Rekap Absensi.</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
-        <is>
-          <t>Halaman Rekap Absensi tampil berisi daftar siswa kelas tersebut.</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>Pilih rentang tanggal yang tanggal mulainya sama dengan tanggal alpha itu, lalu klik Terapkan.</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>Alpha tersebut ikut dihitung sehingga persentase kehadiran siswa tampil 0%.</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>TS.REA.011</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>TC.REA.011.002</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
- 